--- a/summary_calculator/tests/fixtures/minnesota-ave.xlsx
+++ b/summary_calculator/tests/fixtures/minnesota-ave.xlsx
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="18" t="n">
-        <v>6910</v>
+        <v>2832</v>
       </c>
       <c r="F4" s="18" t="n">
         <v>1097</v>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>170</v>
+        <v>1062</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SDA-2</t>
+          <t>SDA-1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6153,21 +6153,25 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E6" s="18" t="n">
-        <v>6689</v>
+        <v>3186</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>6689</v>
+        <v>0</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="I6" s="19">
         <f>IFERROR(VLOOKUP(C6,PARAMS_Rv,2,FALSE),"")</f>
@@ -6207,25 +6211,21 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Compacted (Open Space)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="18" t="n">
-        <v>349</v>
+        <v>3519</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>349</v>
+        <v>6689</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="I7" s="19">
         <f>IFERROR(VLOOKUP(C7,PARAMS_Rv,2,FALSE),"")</f>
@@ -6255,7 +6255,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SDA-3</t>
+          <t>SDA-2</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -6265,21 +6265,25 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E8" s="18" t="n">
-        <v>6860</v>
+        <v>1408</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>6860</v>
+        <v>349</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I8" s="19">
         <f>IFERROR(VLOOKUP(C8,PARAMS_Rv,2,FALSE),"")</f>
@@ -6309,7 +6313,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SDA-3</t>
+          <t>SDA-2</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -6319,7 +6323,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Compacted (Open Space)</t>
+          <t>Natural (Woods)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -6328,16 +6332,16 @@
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>100</v>
+        <v>2111</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>2083</v>
+        <v>0</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>2083</v>
+        <v>0</v>
       </c>
       <c r="I9" s="19">
         <f>IFERROR(VLOOKUP(C9,PARAMS_Rv,2,FALSE),"")</f>
@@ -6367,7 +6371,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SDA-4</t>
+          <t>SDA-3</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -6382,16 +6386,16 @@
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="18" t="n">
-        <v>5720</v>
+        <v>4176</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>3000</v>
+        <v>120</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>5720</v>
+        <v>6860</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>3000</v>
+        <v>120</v>
       </c>
       <c r="I10" s="19">
         <f>IFERROR(VLOOKUP(C10,PARAMS_Rv,2,FALSE),"")</f>
@@ -6421,7 +6425,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SDA-4</t>
+          <t>SDA-3</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -6440,16 +6444,16 @@
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0</v>
+        <v>2083</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>650</v>
+        <v>100</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0</v>
+        <v>2083</v>
       </c>
       <c r="I11" s="19">
         <f>IFERROR(VLOOKUP(C11,PARAMS_Rv,2,FALSE),"")</f>
@@ -6479,7 +6483,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>SDA-5</t>
+          <t>SDA-3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -6489,18 +6493,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E12" s="18" t="n">
-        <v>6820</v>
+        <v>2088</v>
       </c>
       <c r="F12" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>6820</v>
+        <v>0</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>0</v>
@@ -6533,7 +6541,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SDA-5</t>
+          <t>SDA-4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -6543,25 +6551,21 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Compacted (Open Space)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="18" t="n">
-        <v>1440</v>
+        <v>2230</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>342</v>
+        <v>3000</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>1440</v>
+        <v>5720</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>342</v>
+        <v>3000</v>
       </c>
       <c r="I13" s="19">
         <f>IFERROR(VLOOKUP(C13,PARAMS_Rv,2,FALSE),"")</f>
@@ -6591,7 +6595,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SDA-6</t>
+          <t>SDA-4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -6601,18 +6605,22 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n"/>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E14" s="18" t="n">
-        <v>8441</v>
+        <v>1592</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>8441</v>
+        <v>650</v>
       </c>
       <c r="H14" s="18" t="n">
         <v>0</v>
@@ -6645,7 +6653,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SDA-6</t>
+          <t>SDA-4</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -6655,7 +6663,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Compacted (Open Space)</t>
+          <t>Natural (Woods)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -6664,13 +6672,13 @@
         </is>
       </c>
       <c r="E15" s="18" t="n">
-        <v>240</v>
+        <v>2548</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>0</v>
@@ -6703,7 +6711,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SDA-7</t>
+          <t>SDA-5</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -6718,13 +6726,13 @@
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="18" t="n">
-        <v>6117</v>
+        <v>4543</v>
       </c>
       <c r="F16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>6117</v>
+        <v>6820</v>
       </c>
       <c r="H16" s="18" t="n">
         <v>0</v>
@@ -6757,7 +6765,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>SDA-7</t>
+          <t>SDA-5</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -6776,16 +6784,16 @@
         </is>
       </c>
       <c r="E17" s="18" t="n">
-        <v>304</v>
+        <v>2065</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>304</v>
+        <v>1440</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="I17" s="19">
         <f>IFERROR(VLOOKUP(C17,PARAMS_Rv,2,FALSE),"")</f>
@@ -6815,7 +6823,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>SDA-8</t>
+          <t>SDA-5</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -6825,18 +6833,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n"/>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E18" s="18" t="n">
-        <v>10685</v>
+        <v>1652</v>
       </c>
       <c r="F18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>10685</v>
+        <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
         <v>0</v>
@@ -6869,7 +6881,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SDA-8</t>
+          <t>SDA-6</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -6879,22 +6891,18 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Compacted (Open Space)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="18" t="n">
-        <v>1225</v>
+        <v>6077</v>
       </c>
       <c r="F19" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>1225</v>
+        <v>8441</v>
       </c>
       <c r="H19" s="18" t="n">
         <v>0</v>
@@ -6927,7 +6935,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SDA-9</t>
+          <t>SDA-6</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -6937,18 +6945,22 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n"/>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E20" s="18" t="n">
-        <v>6682</v>
+        <v>868</v>
       </c>
       <c r="F20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>6682</v>
+        <v>240</v>
       </c>
       <c r="H20" s="18" t="n">
         <v>0</v>
@@ -6981,7 +6993,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SDA-10</t>
+          <t>SDA-6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -6991,18 +7003,22 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Impervious Vehicular</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="E21" s="18" t="n">
-        <v>2797</v>
+        <v>1736</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>2797</v>
+        <v>0</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>0</v>
@@ -7035,7 +7051,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SDA-10</t>
+          <t>SDA-7</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -7045,25 +7061,21 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Compacted (Open Space)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
       <c r="E22" s="18" t="n">
+        <v>2889</v>
+      </c>
+      <c r="F22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="18" t="n">
-        <v>1469</v>
-      </c>
       <c r="G22" s="18" t="n">
+        <v>6117</v>
+      </c>
+      <c r="H22" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>1469</v>
       </c>
       <c r="I22" s="19">
         <f>IFERROR(VLOOKUP(C22,PARAMS_Rv,2,FALSE),"")</f>
@@ -7091,14 +7103,38 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SDA-7</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>963</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>304</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I23" s="19">
         <f>IFERROR(VLOOKUP(C23,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7125,14 +7161,38 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="n"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SDA-7</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I24" s="19">
         <f>IFERROR(VLOOKUP(C24,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7159,14 +7219,34 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SDA-8</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
+      <c r="E25" s="18" t="n">
+        <v>5955</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>10685</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I25" s="19">
         <f>IFERROR(VLOOKUP(C25,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7193,14 +7273,38 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SDA-8</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1787</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>1225</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I26" s="19">
         <f>IFERROR(VLOOKUP(C26,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7227,14 +7331,38 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="18" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SDA-8</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>4168</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I27" s="19">
         <f>IFERROR(VLOOKUP(C27,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7261,14 +7389,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SDA-9</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="n"/>
+      <c r="E28" s="18" t="n">
+        <v>4343</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>6682</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I28" s="19">
         <f>IFERROR(VLOOKUP(C28,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7295,14 +7443,38 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>SDA-9</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I29" s="19">
         <f>IFERROR(VLOOKUP(C29,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7329,14 +7501,38 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="18" t="n"/>
-      <c r="H30" s="18" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SDA-9</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I30" s="19">
         <f>IFERROR(VLOOKUP(C30,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7363,14 +7559,34 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>SDA-10</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
+      <c r="E31" s="18" t="n">
+        <v>839</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>2797</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I31" s="19">
         <f>IFERROR(VLOOKUP(C31,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7397,14 +7613,38 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="n"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>SDA-10</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Compacted (Open Space)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>559</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>1469</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>1469</v>
+      </c>
       <c r="I32" s="19">
         <f>IFERROR(VLOOKUP(C32,PARAMS_Rv,2,FALSE),"")</f>
         <v/>
@@ -7431,14 +7671,38 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SDA-10</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Natural (Woods)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I33" s="19">
         <f>IFERROR(VLOOKUP(C33,PARAMS_Rv,2,FALSE),"")</f>
         <v/>

--- a/summary_calculator/tests/fixtures/minnesota-ave.xlsx
+++ b/summary_calculator/tests/fixtures/minnesota-ave.xlsx
@@ -363,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -490,6 +490,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1220,7 +1221,7 @@
         <f>'BMP'!B4</f>
         <v/>
       </c>
-      <c r="C4" s="78">
+      <c r="C4" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$4,'BMP'!B4),"")</f>
         <v/>
       </c>
@@ -1266,7 +1267,7 @@
         <f>'BMP'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="78">
+      <c r="C5" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$5,'BMP'!B5),"")</f>
         <v/>
       </c>
@@ -1312,7 +1313,7 @@
         <f>'BMP'!B6</f>
         <v/>
       </c>
-      <c r="C6" s="78">
+      <c r="C6" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$6,'BMP'!B6),"")</f>
         <v/>
       </c>
@@ -1358,7 +1359,7 @@
         <f>'BMP'!B7</f>
         <v/>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$7,'BMP'!B7),"")</f>
         <v/>
       </c>
@@ -1404,7 +1405,7 @@
         <f>'BMP'!B8</f>
         <v/>
       </c>
-      <c r="C8" s="78">
+      <c r="C8" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$8,'BMP'!B8),"")</f>
         <v/>
       </c>
@@ -1450,7 +1451,7 @@
         <f>'BMP'!B9</f>
         <v/>
       </c>
-      <c r="C9" s="78">
+      <c r="C9" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$9,'BMP'!B9),"")</f>
         <v/>
       </c>
@@ -1496,7 +1497,7 @@
         <f>'BMP'!B10</f>
         <v/>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$10,'BMP'!B10),"")</f>
         <v/>
       </c>
@@ -1542,7 +1543,7 @@
         <f>'BMP'!B11</f>
         <v/>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$11,'BMP'!B11),"")</f>
         <v/>
       </c>
@@ -1588,7 +1589,7 @@
         <f>'BMP'!B12</f>
         <v/>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$12,'BMP'!B12),"")</f>
         <v/>
       </c>
@@ -1634,7 +1635,7 @@
         <f>'BMP'!B13</f>
         <v/>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$13,'BMP'!B13),"")</f>
         <v/>
       </c>
@@ -1680,7 +1681,7 @@
         <f>'BMP'!B14</f>
         <v/>
       </c>
-      <c r="C14" s="78">
+      <c r="C14" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$14,'BMP'!B14),"")</f>
         <v/>
       </c>
@@ -1726,7 +1727,7 @@
         <f>'BMP'!B15</f>
         <v/>
       </c>
-      <c r="C15" s="78">
+      <c r="C15" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$15,'BMP'!B15),"")</f>
         <v/>
       </c>
@@ -1772,7 +1773,7 @@
         <f>'BMP'!B16</f>
         <v/>
       </c>
-      <c r="C16" s="78">
+      <c r="C16" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$16,'BMP'!B16),"")</f>
         <v/>
       </c>
@@ -1818,7 +1819,7 @@
         <f>'BMP'!B17</f>
         <v/>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$17,'BMP'!B17),"")</f>
         <v/>
       </c>
@@ -1864,7 +1865,7 @@
         <f>'BMP'!B18</f>
         <v/>
       </c>
-      <c r="C18" s="78">
+      <c r="C18" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$18,'BMP'!B18),"")</f>
         <v/>
       </c>
@@ -1910,7 +1911,7 @@
         <f>'BMP'!B19</f>
         <v/>
       </c>
-      <c r="C19" s="78">
+      <c r="C19" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$19,'BMP'!B19),"")</f>
         <v/>
       </c>
@@ -1956,7 +1957,7 @@
         <f>'BMP'!B20</f>
         <v/>
       </c>
-      <c r="C20" s="78">
+      <c r="C20" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$20,'BMP'!B20),"")</f>
         <v/>
       </c>
@@ -2002,7 +2003,7 @@
         <f>'BMP'!B21</f>
         <v/>
       </c>
-      <c r="C21" s="78">
+      <c r="C21" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$21,'BMP'!B21),"")</f>
         <v/>
       </c>
@@ -2048,7 +2049,7 @@
         <f>'BMP'!B22</f>
         <v/>
       </c>
-      <c r="C22" s="78">
+      <c r="C22" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$22,'BMP'!B22),"")</f>
         <v/>
       </c>
@@ -2094,7 +2095,7 @@
         <f>'BMP'!B23</f>
         <v/>
       </c>
-      <c r="C23" s="78">
+      <c r="C23" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$23,'BMP'!B23),"")</f>
         <v/>
       </c>
@@ -2140,7 +2141,7 @@
         <f>'BMP'!B24</f>
         <v/>
       </c>
-      <c r="C24" s="78">
+      <c r="C24" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$24,'BMP'!B24),"")</f>
         <v/>
       </c>
@@ -2186,7 +2187,7 @@
         <f>'BMP'!B25</f>
         <v/>
       </c>
-      <c r="C25" s="78">
+      <c r="C25" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$25,'BMP'!B25),"")</f>
         <v/>
       </c>
@@ -2232,7 +2233,7 @@
         <f>'BMP'!B26</f>
         <v/>
       </c>
-      <c r="C26" s="78">
+      <c r="C26" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$26,'BMP'!B26),"")</f>
         <v/>
       </c>
@@ -2278,7 +2279,7 @@
         <f>'BMP'!B27</f>
         <v/>
       </c>
-      <c r="C27" s="78">
+      <c r="C27" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$27,'BMP'!B27),"")</f>
         <v/>
       </c>
@@ -2324,7 +2325,7 @@
         <f>'BMP'!B28</f>
         <v/>
       </c>
-      <c r="C28" s="78">
+      <c r="C28" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$28,'BMP'!B28),"")</f>
         <v/>
       </c>
@@ -2370,7 +2371,7 @@
         <f>'BMP'!B29</f>
         <v/>
       </c>
-      <c r="C29" s="78">
+      <c r="C29" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$29,'BMP'!B29),"")</f>
         <v/>
       </c>
@@ -2416,7 +2417,7 @@
         <f>'BMP'!B30</f>
         <v/>
       </c>
-      <c r="C30" s="78">
+      <c r="C30" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$30,'BMP'!B30),"")</f>
         <v/>
       </c>
@@ -2462,7 +2463,7 @@
         <f>'BMP'!B31</f>
         <v/>
       </c>
-      <c r="C31" s="78">
+      <c r="C31" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$31,'BMP'!B31),"")</f>
         <v/>
       </c>
@@ -2508,7 +2509,7 @@
         <f>'BMP'!B32</f>
         <v/>
       </c>
-      <c r="C32" s="78">
+      <c r="C32" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$32,'BMP'!B32),"")</f>
         <v/>
       </c>
@@ -2554,7 +2555,7 @@
         <f>'BMP'!B33</f>
         <v/>
       </c>
-      <c r="C33" s="78">
+      <c r="C33" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$33,'BMP'!B33),"")</f>
         <v/>
       </c>
@@ -2600,7 +2601,7 @@
         <f>'BMP'!B34</f>
         <v/>
       </c>
-      <c r="C34" s="78">
+      <c r="C34" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$34,'BMP'!B34),"")</f>
         <v/>
       </c>
@@ -2646,7 +2647,7 @@
         <f>'BMP'!B35</f>
         <v/>
       </c>
-      <c r="C35" s="78">
+      <c r="C35" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$35,'BMP'!B35),"")</f>
         <v/>
       </c>
@@ -2692,7 +2693,7 @@
         <f>'BMP'!B36</f>
         <v/>
       </c>
-      <c r="C36" s="78">
+      <c r="C36" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$36,'BMP'!B36),"")</f>
         <v/>
       </c>
@@ -2738,7 +2739,7 @@
         <f>'BMP'!B37</f>
         <v/>
       </c>
-      <c r="C37" s="78">
+      <c r="C37" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$37,'BMP'!B37),"")</f>
         <v/>
       </c>
@@ -2784,7 +2785,7 @@
         <f>'BMP'!B38</f>
         <v/>
       </c>
-      <c r="C38" s="78">
+      <c r="C38" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$38,'BMP'!B38),"")</f>
         <v/>
       </c>
@@ -2830,7 +2831,7 @@
         <f>'BMP'!B39</f>
         <v/>
       </c>
-      <c r="C39" s="78">
+      <c r="C39" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$39,'BMP'!B39),"")</f>
         <v/>
       </c>
@@ -2876,7 +2877,7 @@
         <f>'BMP'!B40</f>
         <v/>
       </c>
-      <c r="C40" s="78">
+      <c r="C40" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$40,'BMP'!B40),"")</f>
         <v/>
       </c>
@@ -2922,7 +2923,7 @@
         <f>'BMP'!B41</f>
         <v/>
       </c>
-      <c r="C41" s="78">
+      <c r="C41" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$41,'BMP'!B41),"")</f>
         <v/>
       </c>
@@ -2968,7 +2969,7 @@
         <f>'BMP'!B42</f>
         <v/>
       </c>
-      <c r="C42" s="78">
+      <c r="C42" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$42,'BMP'!B42),"")</f>
         <v/>
       </c>
@@ -3014,7 +3015,7 @@
         <f>'BMP'!B43</f>
         <v/>
       </c>
-      <c r="C43" s="78">
+      <c r="C43" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$43,'BMP'!B43),"")</f>
         <v/>
       </c>
@@ -3060,7 +3061,7 @@
         <f>'BMP'!B44</f>
         <v/>
       </c>
-      <c r="C44" s="78">
+      <c r="C44" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$44,'BMP'!B44),"")</f>
         <v/>
       </c>
@@ -3106,7 +3107,7 @@
         <f>'BMP'!B45</f>
         <v/>
       </c>
-      <c r="C45" s="78">
+      <c r="C45" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$45,'BMP'!B45),"")</f>
         <v/>
       </c>
@@ -3152,7 +3153,7 @@
         <f>'BMP'!B46</f>
         <v/>
       </c>
-      <c r="C46" s="78">
+      <c r="C46" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$46,'BMP'!B46),"")</f>
         <v/>
       </c>
@@ -3198,7 +3199,7 @@
         <f>'BMP'!B47</f>
         <v/>
       </c>
-      <c r="C47" s="78">
+      <c r="C47" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$47,'BMP'!B47),"")</f>
         <v/>
       </c>
@@ -3244,7 +3245,7 @@
         <f>'BMP'!B48</f>
         <v/>
       </c>
-      <c r="C48" s="78">
+      <c r="C48" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$48,'BMP'!B48),"")</f>
         <v/>
       </c>
@@ -3290,7 +3291,7 @@
         <f>'BMP'!B49</f>
         <v/>
       </c>
-      <c r="C49" s="78">
+      <c r="C49" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$49,'BMP'!B49),"")</f>
         <v/>
       </c>
@@ -3336,7 +3337,7 @@
         <f>'BMP'!B50</f>
         <v/>
       </c>
-      <c r="C50" s="78">
+      <c r="C50" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$50,'BMP'!B50),"")</f>
         <v/>
       </c>
@@ -3382,7 +3383,7 @@
         <f>'BMP'!B51</f>
         <v/>
       </c>
-      <c r="C51" s="78">
+      <c r="C51" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$51,'BMP'!B51),"")</f>
         <v/>
       </c>
@@ -3428,7 +3429,7 @@
         <f>'BMP'!B52</f>
         <v/>
       </c>
-      <c r="C52" s="78">
+      <c r="C52" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$52,'BMP'!B52),"")</f>
         <v/>
       </c>
@@ -3474,7 +3475,7 @@
         <f>'BMP'!B53</f>
         <v/>
       </c>
-      <c r="C53" s="78">
+      <c r="C53" s="79">
         <f>IFERROR(COUNTIF('BMP'!$B$4:$B$53,'BMP'!B53),"")</f>
         <v/>
       </c>
@@ -3555,19 +3556,19 @@
       <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="107" t="inlineStr">
+      <c r="A2" s="108" t="inlineStr">
         <is>
           <t>Note: Pre/Post CN composites and runoff depths use land cover Within LOD per DOEE compliance convention. Physical catchment runoff may also include flow from Outside LOD or existing PROW; project-specific exceptions apply. For projects where Outside-LOD contribution is material (offsite inflow, retrofit along existing ROW, etc.), consult the project's drainage study and adjust detention sizing accordingly.</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n"/>
-      <c r="C2" s="64" t="n"/>
-      <c r="D2" s="64" t="n"/>
-      <c r="E2" s="64" t="n"/>
-      <c r="F2" s="64" t="n"/>
-      <c r="G2" s="64" t="n"/>
-      <c r="H2" s="64" t="n"/>
-      <c r="I2" s="65" t="n"/>
+      <c r="B2" s="65" t="n"/>
+      <c r="C2" s="65" t="n"/>
+      <c r="D2" s="65" t="n"/>
+      <c r="E2" s="65" t="n"/>
+      <c r="F2" s="65" t="n"/>
+      <c r="G2" s="65" t="n"/>
+      <c r="H2" s="65" t="n"/>
+      <c r="I2" s="66" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -4045,21 +4046,21 @@
       <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="107" t="inlineStr">
+      <c r="A2" s="108" t="inlineStr">
         <is>
           <t>Note: Pre/Post CN composites and runoff depths use land cover Within LOD per DOEE compliance convention. Physical catchment runoff may also include flow from Outside LOD or existing PROW; project-specific exceptions apply. For projects where Outside-LOD contribution is material (offsite inflow, retrofit along existing ROW, etc.), consult the project's drainage study and adjust detention sizing accordingly.</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n"/>
-      <c r="C2" s="64" t="n"/>
-      <c r="D2" s="64" t="n"/>
-      <c r="E2" s="64" t="n"/>
-      <c r="F2" s="64" t="n"/>
-      <c r="G2" s="64" t="n"/>
-      <c r="H2" s="64" t="n"/>
-      <c r="I2" s="64" t="n"/>
-      <c r="J2" s="64" t="n"/>
-      <c r="K2" s="65" t="n"/>
+      <c r="B2" s="65" t="n"/>
+      <c r="C2" s="65" t="n"/>
+      <c r="D2" s="65" t="n"/>
+      <c r="E2" s="65" t="n"/>
+      <c r="F2" s="65" t="n"/>
+      <c r="G2" s="65" t="n"/>
+      <c r="H2" s="65" t="n"/>
+      <c r="I2" s="65" t="n"/>
+      <c r="J2" s="65" t="n"/>
+      <c r="K2" s="66" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -4671,7 +4672,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A4)</f>
         <v/>
       </c>
-      <c r="D4" s="108">
+      <c r="D4" s="109">
         <f>IFERROR(C4/B4,0)</f>
         <v/>
       </c>
@@ -4685,27 +4686,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="109">
+      <c r="A5" s="110">
         <f>'DOEE_SDA'!A5</f>
         <v/>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="111">
         <f>'DOEE_SDA'!L5</f>
         <v/>
       </c>
-      <c r="C5" s="110">
+      <c r="C5" s="111">
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A5)</f>
         <v/>
       </c>
-      <c r="D5" s="111">
+      <c r="D5" s="112">
         <f>IFERROR(C5/B5,0)</f>
         <v/>
       </c>
-      <c r="E5" s="109">
+      <c r="E5" s="110">
         <f>IF(B5=0,"—",IF(C5&gt;=B5,"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
-      <c r="F5" s="109">
+      <c r="F5" s="110">
         <f>IF(OR('DOEE_DETENTION'!F5="Yes",'DOEE_DETENTION'!I5="Yes"),"Yes","No")</f>
         <v/>
       </c>
@@ -4723,7 +4724,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A6)</f>
         <v/>
       </c>
-      <c r="D6" s="108">
+      <c r="D6" s="109">
         <f>IFERROR(C6/B6,0)</f>
         <v/>
       </c>
@@ -4737,27 +4738,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="109">
+      <c r="A7" s="110">
         <f>'DOEE_SDA'!A7</f>
         <v/>
       </c>
-      <c r="B7" s="110">
+      <c r="B7" s="111">
         <f>'DOEE_SDA'!L7</f>
         <v/>
       </c>
-      <c r="C7" s="110">
+      <c r="C7" s="111">
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A7)</f>
         <v/>
       </c>
-      <c r="D7" s="111">
+      <c r="D7" s="112">
         <f>IFERROR(C7/B7,0)</f>
         <v/>
       </c>
-      <c r="E7" s="109">
+      <c r="E7" s="110">
         <f>IF(B7=0,"—",IF(C7&gt;=B7,"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
-      <c r="F7" s="109">
+      <c r="F7" s="110">
         <f>IF(OR('DOEE_DETENTION'!F7="Yes",'DOEE_DETENTION'!I7="Yes"),"Yes","No")</f>
         <v/>
       </c>
@@ -4775,7 +4776,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A8)</f>
         <v/>
       </c>
-      <c r="D8" s="108">
+      <c r="D8" s="109">
         <f>IFERROR(C8/B8,0)</f>
         <v/>
       </c>
@@ -4789,27 +4790,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="109">
+      <c r="A9" s="110">
         <f>'DOEE_SDA'!A9</f>
         <v/>
       </c>
-      <c r="B9" s="110">
+      <c r="B9" s="111">
         <f>'DOEE_SDA'!L9</f>
         <v/>
       </c>
-      <c r="C9" s="110">
+      <c r="C9" s="111">
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A9)</f>
         <v/>
       </c>
-      <c r="D9" s="111">
+      <c r="D9" s="112">
         <f>IFERROR(C9/B9,0)</f>
         <v/>
       </c>
-      <c r="E9" s="109">
+      <c r="E9" s="110">
         <f>IF(B9=0,"—",IF(C9&gt;=B9,"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
-      <c r="F9" s="109">
+      <c r="F9" s="110">
         <f>IF(OR('DOEE_DETENTION'!F9="Yes",'DOEE_DETENTION'!I9="Yes"),"Yes","No")</f>
         <v/>
       </c>
@@ -4827,7 +4828,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A10)</f>
         <v/>
       </c>
-      <c r="D10" s="108">
+      <c r="D10" s="109">
         <f>IFERROR(C10/B10,0)</f>
         <v/>
       </c>
@@ -4841,27 +4842,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="109">
+      <c r="A11" s="110">
         <f>'DOEE_SDA'!A11</f>
         <v/>
       </c>
-      <c r="B11" s="110">
+      <c r="B11" s="111">
         <f>'DOEE_SDA'!L11</f>
         <v/>
       </c>
-      <c r="C11" s="110">
+      <c r="C11" s="111">
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A11)</f>
         <v/>
       </c>
-      <c r="D11" s="111">
+      <c r="D11" s="112">
         <f>IFERROR(C11/B11,0)</f>
         <v/>
       </c>
-      <c r="E11" s="109">
+      <c r="E11" s="110">
         <f>IF(B11=0,"—",IF(C11&gt;=B11,"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
-      <c r="F11" s="109">
+      <c r="F11" s="110">
         <f>IF(OR('DOEE_DETENTION'!F11="Yes",'DOEE_DETENTION'!I11="Yes"),"Yes","No")</f>
         <v/>
       </c>
@@ -4879,7 +4880,7 @@
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A12)</f>
         <v/>
       </c>
-      <c r="D12" s="108">
+      <c r="D12" s="109">
         <f>IFERROR(C12/B12,0)</f>
         <v/>
       </c>
@@ -4893,27 +4894,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="109">
+      <c r="A13" s="110">
         <f>'DOEE_SDA'!A13</f>
         <v/>
       </c>
-      <c r="B13" s="110">
+      <c r="B13" s="111">
         <f>'DOEE_SDA'!L13</f>
         <v/>
       </c>
-      <c r="C13" s="110">
+      <c r="C13" s="111">
         <f>SUMIFS('BMP'!$AM$4:$AM$53,'BMP'!$B$4:$B$53,A13)</f>
         <v/>
       </c>
-      <c r="D13" s="111">
+      <c r="D13" s="112">
         <f>IFERROR(C13/B13,0)</f>
         <v/>
       </c>
-      <c r="E13" s="109">
+      <c r="E13" s="110">
         <f>IF(B13=0,"—",IF(C13&gt;=B13,"✓ PASS","✗ FAIL"))</f>
         <v/>
       </c>
-      <c r="F13" s="109">
+      <c r="F13" s="110">
         <f>IF(OR('DOEE_DETENTION'!F13="Yes",'DOEE_DETENTION'!I13="Yes"),"Yes","No")</f>
         <v/>
       </c>
@@ -4928,15 +4929,15 @@
           <t>SITE TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="112">
+      <c r="B15" s="113">
         <f>SUM(B4:B13)</f>
         <v/>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="113">
         <f>SUM(C4:C13)</f>
         <v/>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="114">
         <f>IFERROR(C15/B15,0)</f>
         <v/>
       </c>
@@ -4944,7 +4945,7 @@
         <f>IF(C15&gt;=B15,"✓ PASS","✗ FAIL")</f>
         <v/>
       </c>
-      <c r="F15" s="114" t="n"/>
+      <c r="F15" s="115" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9389,7 +9390,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CDA-5</t>
+          <t>CDA-5-5</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -9433,12 +9434,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>CDA-6</t>
+          <t>CDA-5-6</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SDA-6</t>
+          <t>SDA-5</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -9450,7 +9451,7 @@
       <c r="E9" s="18" t="n"/>
       <c r="F9" s="18" t="n"/>
       <c r="G9" s="40" t="n">
-        <v>675</v>
+        <v>1200</v>
       </c>
       <c r="H9" s="18" t="n"/>
       <c r="I9" s="21">
@@ -9477,12 +9478,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>CDA-7</t>
+          <t>CDA-6</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SDA-7</t>
+          <t>SDA-6</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
@@ -9494,7 +9495,7 @@
       <c r="E10" s="18" t="n"/>
       <c r="F10" s="18" t="n"/>
       <c r="G10" s="40" t="n">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="H10" s="18" t="n"/>
       <c r="I10" s="21">
@@ -9521,12 +9522,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>CDA-8</t>
+          <t>CDA-7</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SDA-8</t>
+          <t>SDA-7</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -9538,7 +9539,7 @@
       <c r="E11" s="18" t="n"/>
       <c r="F11" s="18" t="n"/>
       <c r="G11" s="40" t="n">
-        <v>3000</v>
+        <v>660</v>
       </c>
       <c r="H11" s="18" t="n"/>
       <c r="I11" s="21">
@@ -9563,13 +9564,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="18" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CDA-8</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SDA-8</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Impervious Vehicular</t>
+        </is>
+      </c>
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="18" t="n"/>
       <c r="F12" s="18" t="n"/>
-      <c r="G12" s="40" t="n"/>
+      <c r="G12" s="40" t="n">
+        <v>3000</v>
+      </c>
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="21">
         <f>IFERROR(VLOOKUP(C12,PARAMS_Rv,2,FALSE),"")</f>
@@ -11220,7 +11235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:BE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11262,6 +11277,24 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -11307,7 +11340,25 @@
       <c r="AJ1" s="6" t="n"/>
       <c r="AK1" s="6" t="n"/>
       <c r="AL1" s="6" t="n"/>
-      <c r="AM1" s="2" t="n"/>
+      <c r="AM1" s="6" t="n"/>
+      <c r="AN1" s="6" t="n"/>
+      <c r="AO1" s="6" t="n"/>
+      <c r="AP1" s="6" t="n"/>
+      <c r="AQ1" s="6" t="n"/>
+      <c r="AR1" s="6" t="n"/>
+      <c r="AS1" s="6" t="n"/>
+      <c r="AT1" s="6" t="n"/>
+      <c r="AU1" s="6" t="n"/>
+      <c r="AV1" s="6" t="n"/>
+      <c r="AW1" s="6" t="n"/>
+      <c r="AX1" s="6" t="n"/>
+      <c r="AY1" s="6" t="n"/>
+      <c r="AZ1" s="6" t="n"/>
+      <c r="BA1" s="6" t="n"/>
+      <c r="BB1" s="6" t="n"/>
+      <c r="BC1" s="6" t="n"/>
+      <c r="BD1" s="6" t="n"/>
+      <c r="BE1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="42" t="inlineStr">
@@ -11352,7 +11403,25 @@
       <c r="AJ2" s="43" t="n"/>
       <c r="AK2" s="43" t="n"/>
       <c r="AL2" s="43" t="n"/>
-      <c r="AM2" s="44" t="n"/>
+      <c r="AM2" s="43" t="n"/>
+      <c r="AN2" s="43" t="n"/>
+      <c r="AO2" s="43" t="n"/>
+      <c r="AP2" s="43" t="n"/>
+      <c r="AQ2" s="43" t="n"/>
+      <c r="AR2" s="43" t="n"/>
+      <c r="AS2" s="43" t="n"/>
+      <c r="AT2" s="43" t="n"/>
+      <c r="AU2" s="43" t="n"/>
+      <c r="AV2" s="43" t="n"/>
+      <c r="AW2" s="43" t="n"/>
+      <c r="AX2" s="43" t="n"/>
+      <c r="AY2" s="43" t="n"/>
+      <c r="AZ2" s="43" t="n"/>
+      <c r="BA2" s="43" t="n"/>
+      <c r="BB2" s="43" t="n"/>
+      <c r="BC2" s="43" t="n"/>
+      <c r="BD2" s="43" t="n"/>
+      <c r="BE2" s="44" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -11548,6 +11617,96 @@
       <c r="AM3" s="45" t="inlineStr">
         <is>
           <t>Rv Applied (CF)</t>
+        </is>
+      </c>
+      <c r="AN3" s="17" t="inlineStr">
+        <is>
+          <t>Bio SA_pond_top (SF)</t>
+        </is>
+      </c>
+      <c r="AO3" s="17" t="inlineStr">
+        <is>
+          <t>Bio top_elev (ft)</t>
+        </is>
+      </c>
+      <c r="AP3" s="17" t="inlineStr">
+        <is>
+          <t>Bio overflow_elev (ft)</t>
+        </is>
+      </c>
+      <c r="AQ3" s="17" t="inlineStr">
+        <is>
+          <t>Bio sidewalk_elev (ft)</t>
+        </is>
+      </c>
+      <c r="AR3" s="17" t="inlineStr">
+        <is>
+          <t>Bio curb_cut_elev (ft)</t>
+        </is>
+      </c>
+      <c r="AS3" s="45" t="inlineStr">
+        <is>
+          <t>Bio Freeboard (ft)</t>
+        </is>
+      </c>
+      <c r="AT3" s="17" t="inlineStr">
+        <is>
+          <t>Swale L_s (ft)</t>
+        </is>
+      </c>
+      <c r="AU3" s="17" t="inlineStr">
+        <is>
+          <t>Swale w_s (ft)</t>
+        </is>
+      </c>
+      <c r="AV3" s="17" t="inlineStr">
+        <is>
+          <t>Swale inv_US (ft)</t>
+        </is>
+      </c>
+      <c r="AW3" s="17" t="inlineStr">
+        <is>
+          <t>Swale inv_DS (ft)</t>
+        </is>
+      </c>
+      <c r="AX3" s="17" t="inlineStr">
+        <is>
+          <t>Swale top_US (ft)</t>
+        </is>
+      </c>
+      <c r="AY3" s="17" t="inlineStr">
+        <is>
+          <t>Swale top_DS (ft)</t>
+        </is>
+      </c>
+      <c r="AZ3" s="17" t="inlineStr">
+        <is>
+          <t>Swale H_cd (ft)</t>
+        </is>
+      </c>
+      <c r="BA3" s="17" t="inlineStr">
+        <is>
+          <t>Swale X_cd (ft)</t>
+        </is>
+      </c>
+      <c r="BB3" s="17" t="inlineStr">
+        <is>
+          <t>Swale Slope S (ft/ft)</t>
+        </is>
+      </c>
+      <c r="BC3" s="17" t="inlineStr">
+        <is>
+          <t>Swale N_cd</t>
+        </is>
+      </c>
+      <c r="BD3" s="17" t="inlineStr">
+        <is>
+          <t>Swale Wedge Sv/dam (CF)</t>
+        </is>
+      </c>
+      <c r="BE3" s="45" t="inlineStr">
+        <is>
+          <t>Swale Total Pond Sv (CF)</t>
         </is>
       </c>
     </row>
@@ -11675,6 +11834,49 @@
         <f>IFERROR(IF(AL4=0,AK4,MIN(AK4,AL4)),0)</f>
         <v/>
       </c>
+      <c r="AN4" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="AO4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP4" s="4" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AQ4" s="4" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="AR4" s="4" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AS4" s="47">
+        <f>IFERROR(IF(D4&lt;&gt;"Bioretention","",IF(OR(AO4="",U4=""),"",MIN(IF(AP4="",9E9,AP4),IF(AQ4="",9E9,AQ4),IF(AR4="",9E9,AR4))- (AO4 + U4))),"")</f>
+        <v/>
+      </c>
+      <c r="AT4" s="4" t="n"/>
+      <c r="AU4" s="4" t="n"/>
+      <c r="AV4" s="4" t="n"/>
+      <c r="AW4" s="4" t="n"/>
+      <c r="AX4" s="4" t="n"/>
+      <c r="AY4" s="4" t="n"/>
+      <c r="AZ4" s="4" t="n"/>
+      <c r="BA4" s="4" t="n"/>
+      <c r="BB4" s="34">
+        <f>IFERROR(IF(OR(D4&lt;&gt;"Dry Swale",AT4="",AV4="",AW4=""),"",(AV4-AW4)/AT4),"")</f>
+        <v/>
+      </c>
+      <c r="BC4" s="34">
+        <f>IFERROR(IF(OR(D4&lt;&gt;"Dry Swale",AT4="",BA4="",BA4=0),"",FLOOR(AT4/BA4,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD4" s="34">
+        <f>IFERROR(IF(OR(D4&lt;&gt;"Dry Swale",BB4="",BB4=0,AZ4="",BA4="",AU4=""),"",0.5*MIN(BA4,AZ4/BB4)*AZ4*AU4),"")</f>
+        <v/>
+      </c>
+      <c r="BE4" s="47">
+        <f>IFERROR(IF(OR(BC4="",BD4=""),"",BC4*BD4),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -11794,6 +11996,39 @@
         <f>IFERROR(IF(AL5=0,AK5,MIN(AK5,AL5)),0)</f>
         <v/>
       </c>
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n"/>
+      <c r="AP5" s="4" t="n"/>
+      <c r="AQ5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n"/>
+      <c r="AS5" s="47">
+        <f>IFERROR(IF(D5&lt;&gt;"Bioretention","",IF(OR(AO5="",U5=""),"",MIN(IF(AP5="",9E9,AP5),IF(AQ5="",9E9,AQ5),IF(AR5="",9E9,AR5))- (AO5 + U5))),"")</f>
+        <v/>
+      </c>
+      <c r="AT5" s="4" t="n"/>
+      <c r="AU5" s="4" t="n"/>
+      <c r="AV5" s="4" t="n"/>
+      <c r="AW5" s="4" t="n"/>
+      <c r="AX5" s="4" t="n"/>
+      <c r="AY5" s="4" t="n"/>
+      <c r="AZ5" s="4" t="n"/>
+      <c r="BA5" s="4" t="n"/>
+      <c r="BB5" s="34">
+        <f>IFERROR(IF(OR(D5&lt;&gt;"Dry Swale",AT5="",AV5="",AW5=""),"",(AV5-AW5)/AT5),"")</f>
+        <v/>
+      </c>
+      <c r="BC5" s="34">
+        <f>IFERROR(IF(OR(D5&lt;&gt;"Dry Swale",AT5="",BA5="",BA5=0),"",FLOOR(AT5/BA5,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD5" s="34">
+        <f>IFERROR(IF(OR(D5&lt;&gt;"Dry Swale",BB5="",BB5=0,AZ5="",BA5="",AU5=""),"",0.5*MIN(BA5,AZ5/BB5)*AZ5*AU5),"")</f>
+        <v/>
+      </c>
+      <c r="BE5" s="47">
+        <f>IFERROR(IF(OR(BC5="",BD5=""),"",BC5*BD5),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -11913,6 +12148,39 @@
         <f>IFERROR(IF(AL6=0,AK6,MIN(AK6,AL6)),0)</f>
         <v/>
       </c>
+      <c r="AN6" s="4" t="n"/>
+      <c r="AO6" s="4" t="n"/>
+      <c r="AP6" s="4" t="n"/>
+      <c r="AQ6" s="4" t="n"/>
+      <c r="AR6" s="4" t="n"/>
+      <c r="AS6" s="47">
+        <f>IFERROR(IF(D6&lt;&gt;"Bioretention","",IF(OR(AO6="",U6=""),"",MIN(IF(AP6="",9E9,AP6),IF(AQ6="",9E9,AQ6),IF(AR6="",9E9,AR6))- (AO6 + U6))),"")</f>
+        <v/>
+      </c>
+      <c r="AT6" s="4" t="n"/>
+      <c r="AU6" s="4" t="n"/>
+      <c r="AV6" s="4" t="n"/>
+      <c r="AW6" s="4" t="n"/>
+      <c r="AX6" s="4" t="n"/>
+      <c r="AY6" s="4" t="n"/>
+      <c r="AZ6" s="4" t="n"/>
+      <c r="BA6" s="4" t="n"/>
+      <c r="BB6" s="34">
+        <f>IFERROR(IF(OR(D6&lt;&gt;"Dry Swale",AT6="",AV6="",AW6=""),"",(AV6-AW6)/AT6),"")</f>
+        <v/>
+      </c>
+      <c r="BC6" s="34">
+        <f>IFERROR(IF(OR(D6&lt;&gt;"Dry Swale",AT6="",BA6="",BA6=0),"",FLOOR(AT6/BA6,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD6" s="34">
+        <f>IFERROR(IF(OR(D6&lt;&gt;"Dry Swale",BB6="",BB6=0,AZ6="",BA6="",AU6=""),"",0.5*MIN(BA6,AZ6/BB6)*AZ6*AU6),"")</f>
+        <v/>
+      </c>
+      <c r="BE6" s="47">
+        <f>IFERROR(IF(OR(BC6="",BD6=""),"",BC6*BD6),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -12032,6 +12300,39 @@
         <f>IFERROR(IF(AL7=0,AK7,MIN(AK7,AL7)),0)</f>
         <v/>
       </c>
+      <c r="AN7" s="4" t="n"/>
+      <c r="AO7" s="4" t="n"/>
+      <c r="AP7" s="4" t="n"/>
+      <c r="AQ7" s="4" t="n"/>
+      <c r="AR7" s="4" t="n"/>
+      <c r="AS7" s="47">
+        <f>IFERROR(IF(D7&lt;&gt;"Bioretention","",IF(OR(AO7="",U7=""),"",MIN(IF(AP7="",9E9,AP7),IF(AQ7="",9E9,AQ7),IF(AR7="",9E9,AR7))- (AO7 + U7))),"")</f>
+        <v/>
+      </c>
+      <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="n"/>
+      <c r="AV7" s="4" t="n"/>
+      <c r="AW7" s="4" t="n"/>
+      <c r="AX7" s="4" t="n"/>
+      <c r="AY7" s="4" t="n"/>
+      <c r="AZ7" s="4" t="n"/>
+      <c r="BA7" s="4" t="n"/>
+      <c r="BB7" s="34">
+        <f>IFERROR(IF(OR(D7&lt;&gt;"Dry Swale",AT7="",AV7="",AW7=""),"",(AV7-AW7)/AT7),"")</f>
+        <v/>
+      </c>
+      <c r="BC7" s="34">
+        <f>IFERROR(IF(OR(D7&lt;&gt;"Dry Swale",AT7="",BA7="",BA7=0),"",FLOOR(AT7/BA7,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD7" s="34">
+        <f>IFERROR(IF(OR(D7&lt;&gt;"Dry Swale",BB7="",BB7=0,AZ7="",BA7="",AU7=""),"",0.5*MIN(BA7,AZ7/BB7)*AZ7*AU7),"")</f>
+        <v/>
+      </c>
+      <c r="BE7" s="47">
+        <f>IFERROR(IF(OR(BC7="",BD7=""),"",BC7*BD7),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -12155,6 +12456,39 @@
         <f>IFERROR(IF(AL8=0,AK8,MIN(AK8,AL8)),0)</f>
         <v/>
       </c>
+      <c r="AN8" s="4" t="n"/>
+      <c r="AO8" s="4" t="n"/>
+      <c r="AP8" s="4" t="n"/>
+      <c r="AQ8" s="4" t="n"/>
+      <c r="AR8" s="4" t="n"/>
+      <c r="AS8" s="47">
+        <f>IFERROR(IF(D8&lt;&gt;"Bioretention","",IF(OR(AO8="",U8=""),"",MIN(IF(AP8="",9E9,AP8),IF(AQ8="",9E9,AQ8),IF(AR8="",9E9,AR8))- (AO8 + U8))),"")</f>
+        <v/>
+      </c>
+      <c r="AT8" s="4" t="n"/>
+      <c r="AU8" s="4" t="n"/>
+      <c r="AV8" s="4" t="n"/>
+      <c r="AW8" s="4" t="n"/>
+      <c r="AX8" s="4" t="n"/>
+      <c r="AY8" s="4" t="n"/>
+      <c r="AZ8" s="4" t="n"/>
+      <c r="BA8" s="4" t="n"/>
+      <c r="BB8" s="34">
+        <f>IFERROR(IF(OR(D8&lt;&gt;"Dry Swale",AT8="",AV8="",AW8=""),"",(AV8-AW8)/AT8),"")</f>
+        <v/>
+      </c>
+      <c r="BC8" s="34">
+        <f>IFERROR(IF(OR(D8&lt;&gt;"Dry Swale",AT8="",BA8="",BA8=0),"",FLOOR(AT8/BA8,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD8" s="34">
+        <f>IFERROR(IF(OR(D8&lt;&gt;"Dry Swale",BB8="",BB8=0,AZ8="",BA8="",AU8=""),"",0.5*MIN(BA8,AZ8/BB8)*AZ8*AU8),"")</f>
+        <v/>
+      </c>
+      <c r="BE8" s="47">
+        <f>IFERROR(IF(OR(BC8="",BD8=""),"",BC8*BD8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -12169,7 +12503,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CDA-5</t>
+          <t>CDA-5-1</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -12274,11 +12608,44 @@
         <f>IFERROR(IF(AL9=0,AK9,MIN(AK9,AL9)),0)</f>
         <v/>
       </c>
+      <c r="AN9" s="4" t="n"/>
+      <c r="AO9" s="4" t="n"/>
+      <c r="AP9" s="4" t="n"/>
+      <c r="AQ9" s="4" t="n"/>
+      <c r="AR9" s="4" t="n"/>
+      <c r="AS9" s="47">
+        <f>IFERROR(IF(D9&lt;&gt;"Bioretention","",IF(OR(AO9="",U9=""),"",MIN(IF(AP9="",9E9,AP9),IF(AQ9="",9E9,AQ9),IF(AR9="",9E9,AR9))- (AO9 + U9))),"")</f>
+        <v/>
+      </c>
+      <c r="AT9" s="4" t="n"/>
+      <c r="AU9" s="4" t="n"/>
+      <c r="AV9" s="4" t="n"/>
+      <c r="AW9" s="4" t="n"/>
+      <c r="AX9" s="4" t="n"/>
+      <c r="AY9" s="4" t="n"/>
+      <c r="AZ9" s="4" t="n"/>
+      <c r="BA9" s="4" t="n"/>
+      <c r="BB9" s="34">
+        <f>IFERROR(IF(OR(D9&lt;&gt;"Dry Swale",AT9="",AV9="",AW9=""),"",(AV9-AW9)/AT9),"")</f>
+        <v/>
+      </c>
+      <c r="BC9" s="34">
+        <f>IFERROR(IF(OR(D9&lt;&gt;"Dry Swale",AT9="",BA9="",BA9=0),"",FLOOR(AT9/BA9,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD9" s="34">
+        <f>IFERROR(IF(OR(D9&lt;&gt;"Dry Swale",BB9="",BB9=0,AZ9="",BA9="",AU9=""),"",0.5*MIN(BA9,AZ9/BB9)*AZ9*AU9),"")</f>
+        <v/>
+      </c>
+      <c r="BE9" s="47">
+        <f>IFERROR(IF(OR(BC9="",BD9=""),"",BC9*BD9),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>BMP-05-T</t>
+          <t>BMP-05-S</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -12286,10 +12653,14 @@
           <t>SDA-5</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CDA-5-2</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Planted Trees</t>
+          <t>Dry Swale</t>
         </is>
       </c>
       <c r="E10" s="46" t="inlineStr">
@@ -12320,23 +12691,33 @@
         <f>IFERROR(IF(L10="","",IF(L10&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N10" s="18" t="n"/>
-      <c r="O10" s="18" t="n"/>
+      <c r="N10" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="18" t="n">
+        <v>400</v>
+      </c>
       <c r="P10" s="21">
         <f>IFERROR((N10+O10)/2,0)</f>
         <v/>
       </c>
-      <c r="Q10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="R10" s="19">
         <f>IFERROR(IF(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S10" s="5" t="n"/>
+      <c r="S10" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T10" s="19">
         <f>IFERROR(IF(AND(D10="Permeable Pavement",E10="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D10="Permeable Pavement",E10="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D10="Bioretention",E10="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D10="Bioretention",E10="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D10="Bioretention",E10="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D10="Dry Swale",E10="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D10="Wet Swale",E10="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U10" s="5" t="n"/>
+      <c r="U10" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" s="40">
         <f>IFERROR(IF(OR(E10="Enhanced",E10="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C10,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -12355,24 +12736,12 @@
         <f>IFERROR(Y10+Z10,0)</f>
         <v/>
       </c>
-      <c r="AB10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB10" s="50" t="n"/>
+      <c r="AC10" s="50" t="n"/>
+      <c r="AD10" s="50" t="n"/>
+      <c r="AE10" s="50" t="n"/>
+      <c r="AF10" s="50" t="n"/>
+      <c r="AG10" s="50" t="n"/>
       <c r="AH10" s="49">
         <f>IFERROR(AB10*INDEX(PARAMS_Trees,1,3)+AC10*INDEX(PARAMS_Trees,2,3)+AD10*INDEX(PARAMS_Trees,3,3)+AE10*INDEX(PARAMS_Trees,4,3)+AF10*INDEX(PARAMS_Trees,5,3)+AG10*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -12397,31 +12766,76 @@
         <f>IFERROR(IF(AL10=0,AK10,MIN(AK10,AL10)),0)</f>
         <v/>
       </c>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="n"/>
+      <c r="AP10" s="4" t="n"/>
+      <c r="AQ10" s="4" t="n"/>
+      <c r="AR10" s="4" t="n"/>
+      <c r="AS10" s="47">
+        <f>IFERROR(IF(D10&lt;&gt;"Bioretention","",IF(OR(AO10="",U10=""),"",MIN(IF(AP10="",9E9,AP10),IF(AQ10="",9E9,AQ10),IF(AR10="",9E9,AR10))- (AO10 + U10))),"")</f>
+        <v/>
+      </c>
+      <c r="AT10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW10" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="AX10" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AY10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AZ10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB10" s="34">
+        <f>IFERROR(IF(OR(D10&lt;&gt;"Dry Swale",AT10="",AV10="",AW10=""),"",(AV10-AW10)/AT10),"")</f>
+        <v/>
+      </c>
+      <c r="BC10" s="34">
+        <f>IFERROR(IF(OR(D10&lt;&gt;"Dry Swale",AT10="",BA10="",BA10=0),"",FLOOR(AT10/BA10,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD10" s="34">
+        <f>IFERROR(IF(OR(D10&lt;&gt;"Dry Swale",BB10="",BB10=0,AZ10="",BA10="",AU10=""),"",0.5*MIN(BA10,AZ10/BB10)*AZ10*AU10),"")</f>
+        <v/>
+      </c>
+      <c r="BE10" s="47">
+        <f>IFERROR(IF(OR(BC10="",BD10=""),"",BC10*BD10),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>BMP-06-A</t>
+          <t>BMP-05-T</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SDA-6</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CDA-6</t>
-        </is>
-      </c>
+          <t>SDA-5</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Bioretention</t>
+          <t>Planted Trees</t>
         </is>
       </c>
       <c r="E11" s="46" t="inlineStr">
         <is>
-          <t>Enhanced</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="18" t="n"/>
@@ -12447,33 +12861,23 @@
         <f>IFERROR(IF(L11="","",IF(L11&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N11" s="18" t="n">
-        <v>225</v>
-      </c>
-      <c r="O11" s="18" t="n">
-        <v>225</v>
-      </c>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="18" t="n"/>
       <c r="P11" s="21">
         <f>IFERROR((N11+O11)/2,0)</f>
         <v/>
       </c>
-      <c r="Q11" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q11" s="5" t="n"/>
       <c r="R11" s="19">
         <f>IFERROR(IF(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S11" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="S11" s="5" t="n"/>
       <c r="T11" s="19">
         <f>IFERROR(IF(AND(D11="Permeable Pavement",E11="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D11="Permeable Pavement",E11="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D11="Bioretention",E11="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D11="Bioretention",E11="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D11="Bioretention",E11="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D11="Dry Swale",E11="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D11="Wet Swale",E11="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U11" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="U11" s="5" t="n"/>
       <c r="V11" s="40">
         <f>IFERROR(IF(OR(E11="Enhanced",E11="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C11,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -12492,12 +12896,24 @@
         <f>IFERROR(Y11+Z11,0)</f>
         <v/>
       </c>
-      <c r="AB11" s="50" t="n"/>
-      <c r="AC11" s="50" t="n"/>
-      <c r="AD11" s="50" t="n"/>
-      <c r="AE11" s="50" t="n"/>
-      <c r="AF11" s="50" t="n"/>
-      <c r="AG11" s="50" t="n"/>
+      <c r="AB11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="50" t="n">
+        <v>0</v>
+      </c>
       <c r="AH11" s="49">
         <f>IFERROR(AB11*INDEX(PARAMS_Trees,1,3)+AC11*INDEX(PARAMS_Trees,2,3)+AD11*INDEX(PARAMS_Trees,3,3)+AE11*INDEX(PARAMS_Trees,4,3)+AF11*INDEX(PARAMS_Trees,5,3)+AG11*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -12522,11 +12938,44 @@
         <f>IFERROR(IF(AL11=0,AK11,MIN(AK11,AL11)),0)</f>
         <v/>
       </c>
+      <c r="AN11" s="4" t="n"/>
+      <c r="AO11" s="4" t="n"/>
+      <c r="AP11" s="4" t="n"/>
+      <c r="AQ11" s="4" t="n"/>
+      <c r="AR11" s="4" t="n"/>
+      <c r="AS11" s="47">
+        <f>IFERROR(IF(D11&lt;&gt;"Bioretention","",IF(OR(AO11="",U11=""),"",MIN(IF(AP11="",9E9,AP11),IF(AQ11="",9E9,AQ11),IF(AR11="",9E9,AR11))- (AO11 + U11))),"")</f>
+        <v/>
+      </c>
+      <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="n"/>
+      <c r="AV11" s="4" t="n"/>
+      <c r="AW11" s="4" t="n"/>
+      <c r="AX11" s="4" t="n"/>
+      <c r="AY11" s="4" t="n"/>
+      <c r="AZ11" s="4" t="n"/>
+      <c r="BA11" s="4" t="n"/>
+      <c r="BB11" s="34">
+        <f>IFERROR(IF(OR(D11&lt;&gt;"Dry Swale",AT11="",AV11="",AW11=""),"",(AV11-AW11)/AT11),"")</f>
+        <v/>
+      </c>
+      <c r="BC11" s="34">
+        <f>IFERROR(IF(OR(D11&lt;&gt;"Dry Swale",AT11="",BA11="",BA11=0),"",FLOOR(AT11/BA11,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD11" s="34">
+        <f>IFERROR(IF(OR(D11&lt;&gt;"Dry Swale",BB11="",BB11=0,AZ11="",BA11="",AU11=""),"",0.5*MIN(BA11,AZ11/BB11)*AZ11*AU11),"")</f>
+        <v/>
+      </c>
+      <c r="BE11" s="47">
+        <f>IFERROR(IF(OR(BC11="",BD11=""),"",BC11*BD11),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>BMP-06-T</t>
+          <t>BMP-06-A</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -12534,15 +12983,19 @@
           <t>SDA-6</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>CDA-6</t>
+        </is>
+      </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Planted Trees</t>
+          <t>Bioretention</t>
         </is>
       </c>
       <c r="E12" s="46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Enhanced</t>
         </is>
       </c>
       <c r="F12" s="18" t="n"/>
@@ -12568,23 +13021,33 @@
         <f>IFERROR(IF(L12="","",IF(L12&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
+      <c r="N12" s="18" t="n">
+        <v>225</v>
+      </c>
+      <c r="O12" s="18" t="n">
+        <v>225</v>
+      </c>
       <c r="P12" s="21">
         <f>IFERROR((N12+O12)/2,0)</f>
         <v/>
       </c>
-      <c r="Q12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="R12" s="19">
         <f>IFERROR(IF(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S12" s="5" t="n"/>
+      <c r="S12" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T12" s="19">
         <f>IFERROR(IF(AND(D12="Permeable Pavement",E12="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D12="Permeable Pavement",E12="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D12="Bioretention",E12="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D12="Bioretention",E12="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D12="Bioretention",E12="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D12="Dry Swale",E12="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D12="Wet Swale",E12="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U12" s="5" t="n"/>
+      <c r="U12" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V12" s="40">
         <f>IFERROR(IF(OR(E12="Enhanced",E12="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C12,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -12603,24 +13066,12 @@
         <f>IFERROR(Y12+Z12,0)</f>
         <v/>
       </c>
-      <c r="AB12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB12" s="50" t="n"/>
+      <c r="AC12" s="50" t="n"/>
+      <c r="AD12" s="50" t="n"/>
+      <c r="AE12" s="50" t="n"/>
+      <c r="AF12" s="50" t="n"/>
+      <c r="AG12" s="50" t="n"/>
       <c r="AH12" s="49">
         <f>IFERROR(AB12*INDEX(PARAMS_Trees,1,3)+AC12*INDEX(PARAMS_Trees,2,3)+AD12*INDEX(PARAMS_Trees,3,3)+AE12*INDEX(PARAMS_Trees,4,3)+AF12*INDEX(PARAMS_Trees,5,3)+AG12*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -12645,31 +13096,70 @@
         <f>IFERROR(IF(AL12=0,AK12,MIN(AK12,AL12)),0)</f>
         <v/>
       </c>
+      <c r="AN12" s="4" t="n">
+        <v>315</v>
+      </c>
+      <c r="AO12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP12" s="4" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AQ12" s="4" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="AR12" s="4" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AS12" s="47">
+        <f>IFERROR(IF(D12&lt;&gt;"Bioretention","",IF(OR(AO12="",U12=""),"",MIN(IF(AP12="",9E9,AP12),IF(AQ12="",9E9,AQ12),IF(AR12="",9E9,AR12))- (AO12 + U12))),"")</f>
+        <v/>
+      </c>
+      <c r="AT12" s="4" t="n"/>
+      <c r="AU12" s="4" t="n"/>
+      <c r="AV12" s="4" t="n"/>
+      <c r="AW12" s="4" t="n"/>
+      <c r="AX12" s="4" t="n"/>
+      <c r="AY12" s="4" t="n"/>
+      <c r="AZ12" s="4" t="n"/>
+      <c r="BA12" s="4" t="n"/>
+      <c r="BB12" s="34">
+        <f>IFERROR(IF(OR(D12&lt;&gt;"Dry Swale",AT12="",AV12="",AW12=""),"",(AV12-AW12)/AT12),"")</f>
+        <v/>
+      </c>
+      <c r="BC12" s="34">
+        <f>IFERROR(IF(OR(D12&lt;&gt;"Dry Swale",AT12="",BA12="",BA12=0),"",FLOOR(AT12/BA12,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD12" s="34">
+        <f>IFERROR(IF(OR(D12&lt;&gt;"Dry Swale",BB12="",BB12=0,AZ12="",BA12="",AU12=""),"",0.5*MIN(BA12,AZ12/BB12)*AZ12*AU12),"")</f>
+        <v/>
+      </c>
+      <c r="BE12" s="47">
+        <f>IFERROR(IF(OR(BC12="",BD12=""),"",BC12*BD12),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>BMP-07-A</t>
+          <t>BMP-06-T</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SDA-7</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CDA-7</t>
-        </is>
-      </c>
+          <t>SDA-6</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Bioretention</t>
+          <t>Planted Trees</t>
         </is>
       </c>
       <c r="E13" s="46" t="inlineStr">
         <is>
-          <t>Enhanced</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="18" t="n"/>
@@ -12695,33 +13185,23 @@
         <f>IFERROR(IF(L13="","",IF(L13&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N13" s="18" t="n">
-        <v>220</v>
-      </c>
-      <c r="O13" s="18" t="n">
-        <v>220</v>
-      </c>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="18" t="n"/>
       <c r="P13" s="21">
         <f>IFERROR((N13+O13)/2,0)</f>
         <v/>
       </c>
-      <c r="Q13" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q13" s="5" t="n"/>
       <c r="R13" s="19">
         <f>IFERROR(IF(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S13" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="S13" s="5" t="n"/>
       <c r="T13" s="19">
         <f>IFERROR(IF(AND(D13="Permeable Pavement",E13="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D13="Permeable Pavement",E13="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D13="Bioretention",E13="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D13="Bioretention",E13="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D13="Bioretention",E13="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D13="Dry Swale",E13="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D13="Wet Swale",E13="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U13" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="U13" s="5" t="n"/>
       <c r="V13" s="40">
         <f>IFERROR(IF(OR(E13="Enhanced",E13="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C13,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -12740,12 +13220,24 @@
         <f>IFERROR(Y13+Z13,0)</f>
         <v/>
       </c>
-      <c r="AB13" s="50" t="n"/>
-      <c r="AC13" s="50" t="n"/>
-      <c r="AD13" s="50" t="n"/>
-      <c r="AE13" s="50" t="n"/>
-      <c r="AF13" s="50" t="n"/>
-      <c r="AG13" s="50" t="n"/>
+      <c r="AB13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="50" t="n">
+        <v>0</v>
+      </c>
       <c r="AH13" s="49">
         <f>IFERROR(AB13*INDEX(PARAMS_Trees,1,3)+AC13*INDEX(PARAMS_Trees,2,3)+AD13*INDEX(PARAMS_Trees,3,3)+AE13*INDEX(PARAMS_Trees,4,3)+AF13*INDEX(PARAMS_Trees,5,3)+AG13*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -12770,11 +13262,44 @@
         <f>IFERROR(IF(AL13=0,AK13,MIN(AK13,AL13)),0)</f>
         <v/>
       </c>
+      <c r="AN13" s="4" t="n"/>
+      <c r="AO13" s="4" t="n"/>
+      <c r="AP13" s="4" t="n"/>
+      <c r="AQ13" s="4" t="n"/>
+      <c r="AR13" s="4" t="n"/>
+      <c r="AS13" s="47">
+        <f>IFERROR(IF(D13&lt;&gt;"Bioretention","",IF(OR(AO13="",U13=""),"",MIN(IF(AP13="",9E9,AP13),IF(AQ13="",9E9,AQ13),IF(AR13="",9E9,AR13))- (AO13 + U13))),"")</f>
+        <v/>
+      </c>
+      <c r="AT13" s="4" t="n"/>
+      <c r="AU13" s="4" t="n"/>
+      <c r="AV13" s="4" t="n"/>
+      <c r="AW13" s="4" t="n"/>
+      <c r="AX13" s="4" t="n"/>
+      <c r="AY13" s="4" t="n"/>
+      <c r="AZ13" s="4" t="n"/>
+      <c r="BA13" s="4" t="n"/>
+      <c r="BB13" s="34">
+        <f>IFERROR(IF(OR(D13&lt;&gt;"Dry Swale",AT13="",AV13="",AW13=""),"",(AV13-AW13)/AT13),"")</f>
+        <v/>
+      </c>
+      <c r="BC13" s="34">
+        <f>IFERROR(IF(OR(D13&lt;&gt;"Dry Swale",AT13="",BA13="",BA13=0),"",FLOOR(AT13/BA13,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD13" s="34">
+        <f>IFERROR(IF(OR(D13&lt;&gt;"Dry Swale",BB13="",BB13=0,AZ13="",BA13="",AU13=""),"",0.5*MIN(BA13,AZ13/BB13)*AZ13*AU13),"")</f>
+        <v/>
+      </c>
+      <c r="BE13" s="47">
+        <f>IFERROR(IF(OR(BC13="",BD13=""),"",BC13*BD13),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>BMP-07-T</t>
+          <t>BMP-07-A</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -12782,15 +13307,19 @@
           <t>SDA-7</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CDA-7</t>
+        </is>
+      </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Planted Trees</t>
+          <t>Bioretention</t>
         </is>
       </c>
       <c r="E14" s="46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Enhanced</t>
         </is>
       </c>
       <c r="F14" s="18" t="n"/>
@@ -12816,23 +13345,33 @@
         <f>IFERROR(IF(L14="","",IF(L14&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N14" s="18" t="n"/>
-      <c r="O14" s="18" t="n"/>
+      <c r="N14" s="18" t="n">
+        <v>220</v>
+      </c>
+      <c r="O14" s="18" t="n">
+        <v>220</v>
+      </c>
       <c r="P14" s="21">
         <f>IFERROR((N14+O14)/2,0)</f>
         <v/>
       </c>
-      <c r="Q14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="R14" s="19">
         <f>IFERROR(IF(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S14" s="5" t="n"/>
+      <c r="S14" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T14" s="19">
         <f>IFERROR(IF(AND(D14="Permeable Pavement",E14="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D14="Permeable Pavement",E14="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D14="Bioretention",E14="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D14="Bioretention",E14="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D14="Bioretention",E14="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D14="Dry Swale",E14="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D14="Wet Swale",E14="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U14" s="5" t="n"/>
+      <c r="U14" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V14" s="40">
         <f>IFERROR(IF(OR(E14="Enhanced",E14="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C14,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -12851,24 +13390,12 @@
         <f>IFERROR(Y14+Z14,0)</f>
         <v/>
       </c>
-      <c r="AB14" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB14" s="50" t="n"/>
+      <c r="AC14" s="50" t="n"/>
+      <c r="AD14" s="50" t="n"/>
+      <c r="AE14" s="50" t="n"/>
+      <c r="AF14" s="50" t="n"/>
+      <c r="AG14" s="50" t="n"/>
       <c r="AH14" s="49">
         <f>IFERROR(AB14*INDEX(PARAMS_Trees,1,3)+AC14*INDEX(PARAMS_Trees,2,3)+AD14*INDEX(PARAMS_Trees,3,3)+AE14*INDEX(PARAMS_Trees,4,3)+AF14*INDEX(PARAMS_Trees,5,3)+AG14*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -12893,31 +13420,70 @@
         <f>IFERROR(IF(AL14=0,AK14,MIN(AK14,AL14)),0)</f>
         <v/>
       </c>
+      <c r="AN14" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="AO14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" s="4" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AQ14" s="4" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="AR14" s="4" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AS14" s="47">
+        <f>IFERROR(IF(D14&lt;&gt;"Bioretention","",IF(OR(AO14="",U14=""),"",MIN(IF(AP14="",9E9,AP14),IF(AQ14="",9E9,AQ14),IF(AR14="",9E9,AR14))- (AO14 + U14))),"")</f>
+        <v/>
+      </c>
+      <c r="AT14" s="4" t="n"/>
+      <c r="AU14" s="4" t="n"/>
+      <c r="AV14" s="4" t="n"/>
+      <c r="AW14" s="4" t="n"/>
+      <c r="AX14" s="4" t="n"/>
+      <c r="AY14" s="4" t="n"/>
+      <c r="AZ14" s="4" t="n"/>
+      <c r="BA14" s="4" t="n"/>
+      <c r="BB14" s="34">
+        <f>IFERROR(IF(OR(D14&lt;&gt;"Dry Swale",AT14="",AV14="",AW14=""),"",(AV14-AW14)/AT14),"")</f>
+        <v/>
+      </c>
+      <c r="BC14" s="34">
+        <f>IFERROR(IF(OR(D14&lt;&gt;"Dry Swale",AT14="",BA14="",BA14=0),"",FLOOR(AT14/BA14,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD14" s="34">
+        <f>IFERROR(IF(OR(D14&lt;&gt;"Dry Swale",BB14="",BB14=0,AZ14="",BA14="",AU14=""),"",0.5*MIN(BA14,AZ14/BB14)*AZ14*AU14),"")</f>
+        <v/>
+      </c>
+      <c r="BE14" s="47">
+        <f>IFERROR(IF(OR(BC14="",BD14=""),"",BC14*BD14),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>BMP-08-A</t>
+          <t>BMP-07-T</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SDA-8</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CDA-8</t>
-        </is>
-      </c>
+          <t>SDA-7</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Bioretention</t>
+          <t>Planted Trees</t>
         </is>
       </c>
       <c r="E15" s="46" t="inlineStr">
         <is>
-          <t>Enhanced</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="18" t="n"/>
@@ -12943,33 +13509,23 @@
         <f>IFERROR(IF(L15="","",IF(L15&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N15" s="18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O15" s="18" t="n">
-        <v>1000</v>
-      </c>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="18" t="n"/>
       <c r="P15" s="21">
         <f>IFERROR((N15+O15)/2,0)</f>
         <v/>
       </c>
-      <c r="Q15" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q15" s="5" t="n"/>
       <c r="R15" s="19">
         <f>IFERROR(IF(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S15" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="S15" s="5" t="n"/>
       <c r="T15" s="19">
         <f>IFERROR(IF(AND(D15="Permeable Pavement",E15="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D15="Permeable Pavement",E15="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D15="Bioretention",E15="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D15="Bioretention",E15="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D15="Bioretention",E15="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D15="Dry Swale",E15="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D15="Wet Swale",E15="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U15" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="U15" s="5" t="n"/>
       <c r="V15" s="40">
         <f>IFERROR(IF(OR(E15="Enhanced",E15="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C15,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -12988,12 +13544,24 @@
         <f>IFERROR(Y15+Z15,0)</f>
         <v/>
       </c>
-      <c r="AB15" s="50" t="n"/>
-      <c r="AC15" s="50" t="n"/>
-      <c r="AD15" s="50" t="n"/>
-      <c r="AE15" s="50" t="n"/>
-      <c r="AF15" s="50" t="n"/>
-      <c r="AG15" s="50" t="n"/>
+      <c r="AB15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="50" t="n">
+        <v>0</v>
+      </c>
       <c r="AH15" s="49">
         <f>IFERROR(AB15*INDEX(PARAMS_Trees,1,3)+AC15*INDEX(PARAMS_Trees,2,3)+AD15*INDEX(PARAMS_Trees,3,3)+AE15*INDEX(PARAMS_Trees,4,3)+AF15*INDEX(PARAMS_Trees,5,3)+AG15*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -13018,11 +13586,44 @@
         <f>IFERROR(IF(AL15=0,AK15,MIN(AK15,AL15)),0)</f>
         <v/>
       </c>
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="n"/>
+      <c r="AP15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="n"/>
+      <c r="AS15" s="47">
+        <f>IFERROR(IF(D15&lt;&gt;"Bioretention","",IF(OR(AO15="",U15=""),"",MIN(IF(AP15="",9E9,AP15),IF(AQ15="",9E9,AQ15),IF(AR15="",9E9,AR15))- (AO15 + U15))),"")</f>
+        <v/>
+      </c>
+      <c r="AT15" s="4" t="n"/>
+      <c r="AU15" s="4" t="n"/>
+      <c r="AV15" s="4" t="n"/>
+      <c r="AW15" s="4" t="n"/>
+      <c r="AX15" s="4" t="n"/>
+      <c r="AY15" s="4" t="n"/>
+      <c r="AZ15" s="4" t="n"/>
+      <c r="BA15" s="4" t="n"/>
+      <c r="BB15" s="34">
+        <f>IFERROR(IF(OR(D15&lt;&gt;"Dry Swale",AT15="",AV15="",AW15=""),"",(AV15-AW15)/AT15),"")</f>
+        <v/>
+      </c>
+      <c r="BC15" s="34">
+        <f>IFERROR(IF(OR(D15&lt;&gt;"Dry Swale",AT15="",BA15="",BA15=0),"",FLOOR(AT15/BA15,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD15" s="34">
+        <f>IFERROR(IF(OR(D15&lt;&gt;"Dry Swale",BB15="",BB15=0,AZ15="",BA15="",AU15=""),"",0.5*MIN(BA15,AZ15/BB15)*AZ15*AU15),"")</f>
+        <v/>
+      </c>
+      <c r="BE15" s="47">
+        <f>IFERROR(IF(OR(BC15="",BD15=""),"",BC15*BD15),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>BMP-08-T</t>
+          <t>BMP-08-A</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -13030,15 +13631,19 @@
           <t>SDA-8</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CDA-8</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Planted Trees</t>
+          <t>Bioretention</t>
         </is>
       </c>
       <c r="E16" s="46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Enhanced</t>
         </is>
       </c>
       <c r="F16" s="18" t="n"/>
@@ -13064,23 +13669,33 @@
         <f>IFERROR(IF(L16="","",IF(L16&lt;=2,"✓","✗")),"")</f>
         <v/>
       </c>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
+      <c r="N16" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O16" s="18" t="n">
+        <v>1000</v>
+      </c>
       <c r="P16" s="21">
         <f>IFERROR((N16+O16)/2,0)</f>
         <v/>
       </c>
-      <c r="Q16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="R16" s="19">
         <f>IFERROR(IF(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,3),IF(AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,3),IF(AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,3),IF(AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,3),IF(AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,3),IF(AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,3),IF(AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,3),""))))))),"")</f>
         <v/>
       </c>
-      <c r="S16" s="5" t="n"/>
+      <c r="S16" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T16" s="19">
         <f>IFERROR(IF(AND(D16="Permeable Pavement",E16="Enhanced"),INDEX(PARAMS_BMP,1,4),IF(AND(D16="Permeable Pavement",E16="Underdrained Enhanced"),INDEX(PARAMS_BMP,2,4),IF(AND(D16="Bioretention",E16="Standard"),INDEX(PARAMS_BMP,3,4),IF(AND(D16="Bioretention",E16="Enhanced"),INDEX(PARAMS_BMP,4,4),IF(AND(D16="Bioretention",E16="Enhanced w/ Underdrain"),INDEX(PARAMS_BMP,5,4),IF(AND(D16="Dry Swale",E16="—"),INDEX(PARAMS_BMP,6,4),IF(AND(D16="Wet Swale",E16="—"),INDEX(PARAMS_BMP,7,4),""))))))),"")</f>
         <v/>
       </c>
-      <c r="U16" s="5" t="n"/>
+      <c r="U16" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V16" s="40">
         <f>IFERROR(IF(OR(E16="Enhanced",E16="Enhanced w/ Underdrain"),VLOOKUP(IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"D")&gt;0,"D",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"C")&gt;0,"C",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"B")&gt;0,"B",IF(SUMIFS('CDA'!$G$4:$G$53,'CDA'!$A$4:$A$53,C16,'CDA'!$D$4:$D$53,"A")&gt;0,"A","")))),PARAMS_Ksat,2,FALSE),0),0)</f>
         <v/>
@@ -13099,24 +13714,12 @@
         <f>IFERROR(Y16+Z16,0)</f>
         <v/>
       </c>
-      <c r="AB16" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD16" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB16" s="50" t="n"/>
+      <c r="AC16" s="50" t="n"/>
+      <c r="AD16" s="50" t="n"/>
+      <c r="AE16" s="50" t="n"/>
+      <c r="AF16" s="50" t="n"/>
+      <c r="AG16" s="50" t="n"/>
       <c r="AH16" s="49">
         <f>IFERROR(AB16*INDEX(PARAMS_Trees,1,3)+AC16*INDEX(PARAMS_Trees,2,3)+AD16*INDEX(PARAMS_Trees,3,3)+AE16*INDEX(PARAMS_Trees,4,3)+AF16*INDEX(PARAMS_Trees,5,3)+AG16*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -13141,16 +13744,59 @@
         <f>IFERROR(IF(AL16=0,AK16,MIN(AK16,AL16)),0)</f>
         <v/>
       </c>
+      <c r="AN16" s="4" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AO16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP16" s="4" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AQ16" s="4" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="AR16" s="4" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AS16" s="47">
+        <f>IFERROR(IF(D16&lt;&gt;"Bioretention","",IF(OR(AO16="",U16=""),"",MIN(IF(AP16="",9E9,AP16),IF(AQ16="",9E9,AQ16),IF(AR16="",9E9,AR16))- (AO16 + U16))),"")</f>
+        <v/>
+      </c>
+      <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="n"/>
+      <c r="AV16" s="4" t="n"/>
+      <c r="AW16" s="4" t="n"/>
+      <c r="AX16" s="4" t="n"/>
+      <c r="AY16" s="4" t="n"/>
+      <c r="AZ16" s="4" t="n"/>
+      <c r="BA16" s="4" t="n"/>
+      <c r="BB16" s="34">
+        <f>IFERROR(IF(OR(D16&lt;&gt;"Dry Swale",AT16="",AV16="",AW16=""),"",(AV16-AW16)/AT16),"")</f>
+        <v/>
+      </c>
+      <c r="BC16" s="34">
+        <f>IFERROR(IF(OR(D16&lt;&gt;"Dry Swale",AT16="",BA16="",BA16=0),"",FLOOR(AT16/BA16,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD16" s="34">
+        <f>IFERROR(IF(OR(D16&lt;&gt;"Dry Swale",BB16="",BB16=0,AZ16="",BA16="",AU16=""),"",0.5*MIN(BA16,AZ16/BB16)*AZ16*AU16),"")</f>
+        <v/>
+      </c>
+      <c r="BE16" s="47">
+        <f>IFERROR(IF(OR(BC16="",BD16=""),"",BC16*BD16),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>BMP-09-T</t>
+          <t>BMP-08-T</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SDA-9</t>
+          <t>SDA-8</t>
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -13264,16 +13910,49 @@
         <f>IFERROR(IF(AL17=0,AK17,MIN(AK17,AL17)),0)</f>
         <v/>
       </c>
+      <c r="AN17" s="4" t="n"/>
+      <c r="AO17" s="4" t="n"/>
+      <c r="AP17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="47">
+        <f>IFERROR(IF(D17&lt;&gt;"Bioretention","",IF(OR(AO17="",U17=""),"",MIN(IF(AP17="",9E9,AP17),IF(AQ17="",9E9,AQ17),IF(AR17="",9E9,AR17))- (AO17 + U17))),"")</f>
+        <v/>
+      </c>
+      <c r="AT17" s="4" t="n"/>
+      <c r="AU17" s="4" t="n"/>
+      <c r="AV17" s="4" t="n"/>
+      <c r="AW17" s="4" t="n"/>
+      <c r="AX17" s="4" t="n"/>
+      <c r="AY17" s="4" t="n"/>
+      <c r="AZ17" s="4" t="n"/>
+      <c r="BA17" s="4" t="n"/>
+      <c r="BB17" s="34">
+        <f>IFERROR(IF(OR(D17&lt;&gt;"Dry Swale",AT17="",AV17="",AW17=""),"",(AV17-AW17)/AT17),"")</f>
+        <v/>
+      </c>
+      <c r="BC17" s="34">
+        <f>IFERROR(IF(OR(D17&lt;&gt;"Dry Swale",AT17="",BA17="",BA17=0),"",FLOOR(AT17/BA17,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD17" s="34">
+        <f>IFERROR(IF(OR(D17&lt;&gt;"Dry Swale",BB17="",BB17=0,AZ17="",BA17="",AU17=""),"",0.5*MIN(BA17,AZ17/BB17)*AZ17*AU17),"")</f>
+        <v/>
+      </c>
+      <c r="BE17" s="47">
+        <f>IFERROR(IF(OR(BC17="",BD17=""),"",BC17*BD17),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>BMP-10-T</t>
+          <t>BMP-09-T</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SDA-10</t>
+          <t>SDA-9</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -13349,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="AC18" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD18" s="50" t="n">
         <v>0</v>
@@ -13387,13 +14066,62 @@
         <f>IFERROR(IF(AL18=0,AK18,MIN(AK18,AL18)),0)</f>
         <v/>
       </c>
+      <c r="AN18" s="4" t="n"/>
+      <c r="AO18" s="4" t="n"/>
+      <c r="AP18" s="4" t="n"/>
+      <c r="AQ18" s="4" t="n"/>
+      <c r="AR18" s="4" t="n"/>
+      <c r="AS18" s="47">
+        <f>IFERROR(IF(D18&lt;&gt;"Bioretention","",IF(OR(AO18="",U18=""),"",MIN(IF(AP18="",9E9,AP18),IF(AQ18="",9E9,AQ18),IF(AR18="",9E9,AR18))- (AO18 + U18))),"")</f>
+        <v/>
+      </c>
+      <c r="AT18" s="4" t="n"/>
+      <c r="AU18" s="4" t="n"/>
+      <c r="AV18" s="4" t="n"/>
+      <c r="AW18" s="4" t="n"/>
+      <c r="AX18" s="4" t="n"/>
+      <c r="AY18" s="4" t="n"/>
+      <c r="AZ18" s="4" t="n"/>
+      <c r="BA18" s="4" t="n"/>
+      <c r="BB18" s="34">
+        <f>IFERROR(IF(OR(D18&lt;&gt;"Dry Swale",AT18="",AV18="",AW18=""),"",(AV18-AW18)/AT18),"")</f>
+        <v/>
+      </c>
+      <c r="BC18" s="34">
+        <f>IFERROR(IF(OR(D18&lt;&gt;"Dry Swale",AT18="",BA18="",BA18=0),"",FLOOR(AT18/BA18,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD18" s="34">
+        <f>IFERROR(IF(OR(D18&lt;&gt;"Dry Swale",BB18="",BB18=0,AZ18="",BA18="",AU18=""),"",0.5*MIN(BA18,AZ18/BB18)*AZ18*AU18),"")</f>
+        <v/>
+      </c>
+      <c r="BE18" s="47">
+        <f>IFERROR(IF(OR(BC18="",BD18=""),"",BC18*BD18),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BMP-10-T</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SDA-10</t>
+        </is>
+      </c>
       <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="46" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Planted Trees</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F19" s="18" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
@@ -13452,12 +14180,24 @@
         <f>IFERROR(Y19+Z19,0)</f>
         <v/>
       </c>
-      <c r="AB19" s="50" t="n"/>
-      <c r="AC19" s="50" t="n"/>
-      <c r="AD19" s="50" t="n"/>
-      <c r="AE19" s="50" t="n"/>
-      <c r="AF19" s="50" t="n"/>
-      <c r="AG19" s="50" t="n"/>
+      <c r="AB19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="50" t="n">
+        <v>0</v>
+      </c>
       <c r="AH19" s="49">
         <f>IFERROR(AB19*INDEX(PARAMS_Trees,1,3)+AC19*INDEX(PARAMS_Trees,2,3)+AD19*INDEX(PARAMS_Trees,3,3)+AE19*INDEX(PARAMS_Trees,4,3)+AF19*INDEX(PARAMS_Trees,5,3)+AG19*INDEX(PARAMS_Trees,6,3),0)</f>
         <v/>
@@ -13480,6 +14220,39 @@
       </c>
       <c r="AM19" s="49">
         <f>IFERROR(IF(AL19=0,AK19,MIN(AK19,AL19)),0)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="4" t="n"/>
+      <c r="AO19" s="4" t="n"/>
+      <c r="AP19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n"/>
+      <c r="AS19" s="47">
+        <f>IFERROR(IF(D19&lt;&gt;"Bioretention","",IF(OR(AO19="",U19=""),"",MIN(IF(AP19="",9E9,AP19),IF(AQ19="",9E9,AQ19),IF(AR19="",9E9,AR19))- (AO19 + U19))),"")</f>
+        <v/>
+      </c>
+      <c r="AT19" s="4" t="n"/>
+      <c r="AU19" s="4" t="n"/>
+      <c r="AV19" s="4" t="n"/>
+      <c r="AW19" s="4" t="n"/>
+      <c r="AX19" s="4" t="n"/>
+      <c r="AY19" s="4" t="n"/>
+      <c r="AZ19" s="4" t="n"/>
+      <c r="BA19" s="4" t="n"/>
+      <c r="BB19" s="34">
+        <f>IFERROR(IF(OR(D19&lt;&gt;"Dry Swale",AT19="",AV19="",AW19=""),"",(AV19-AW19)/AT19),"")</f>
+        <v/>
+      </c>
+      <c r="BC19" s="34">
+        <f>IFERROR(IF(OR(D19&lt;&gt;"Dry Swale",AT19="",BA19="",BA19=0),"",FLOOR(AT19/BA19,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD19" s="34">
+        <f>IFERROR(IF(OR(D19&lt;&gt;"Dry Swale",BB19="",BB19=0,AZ19="",BA19="",AU19=""),"",0.5*MIN(BA19,AZ19/BB19)*AZ19*AU19),"")</f>
+        <v/>
+      </c>
+      <c r="BE19" s="47">
+        <f>IFERROR(IF(OR(BC19="",BD19=""),"",BC19*BD19),"")</f>
         <v/>
       </c>
     </row>
@@ -13577,6 +14350,39 @@
         <f>IFERROR(IF(AL20=0,AK20,MIN(AK20,AL20)),0)</f>
         <v/>
       </c>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="n"/>
+      <c r="AP20" s="4" t="n"/>
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="47">
+        <f>IFERROR(IF(D20&lt;&gt;"Bioretention","",IF(OR(AO20="",U20=""),"",MIN(IF(AP20="",9E9,AP20),IF(AQ20="",9E9,AQ20),IF(AR20="",9E9,AR20))- (AO20 + U20))),"")</f>
+        <v/>
+      </c>
+      <c r="AT20" s="4" t="n"/>
+      <c r="AU20" s="4" t="n"/>
+      <c r="AV20" s="4" t="n"/>
+      <c r="AW20" s="4" t="n"/>
+      <c r="AX20" s="4" t="n"/>
+      <c r="AY20" s="4" t="n"/>
+      <c r="AZ20" s="4" t="n"/>
+      <c r="BA20" s="4" t="n"/>
+      <c r="BB20" s="34">
+        <f>IFERROR(IF(OR(D20&lt;&gt;"Dry Swale",AT20="",AV20="",AW20=""),"",(AV20-AW20)/AT20),"")</f>
+        <v/>
+      </c>
+      <c r="BC20" s="34">
+        <f>IFERROR(IF(OR(D20&lt;&gt;"Dry Swale",AT20="",BA20="",BA20=0),"",FLOOR(AT20/BA20,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD20" s="34">
+        <f>IFERROR(IF(OR(D20&lt;&gt;"Dry Swale",BB20="",BB20=0,AZ20="",BA20="",AU20=""),"",0.5*MIN(BA20,AZ20/BB20)*AZ20*AU20),"")</f>
+        <v/>
+      </c>
+      <c r="BE20" s="47">
+        <f>IFERROR(IF(OR(BC20="",BD20=""),"",BC20*BD20),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -13672,6 +14478,39 @@
         <f>IFERROR(IF(AL21=0,AK21,MIN(AK21,AL21)),0)</f>
         <v/>
       </c>
+      <c r="AN21" s="4" t="n"/>
+      <c r="AO21" s="4" t="n"/>
+      <c r="AP21" s="4" t="n"/>
+      <c r="AQ21" s="4" t="n"/>
+      <c r="AR21" s="4" t="n"/>
+      <c r="AS21" s="47">
+        <f>IFERROR(IF(D21&lt;&gt;"Bioretention","",IF(OR(AO21="",U21=""),"",MIN(IF(AP21="",9E9,AP21),IF(AQ21="",9E9,AQ21),IF(AR21="",9E9,AR21))- (AO21 + U21))),"")</f>
+        <v/>
+      </c>
+      <c r="AT21" s="4" t="n"/>
+      <c r="AU21" s="4" t="n"/>
+      <c r="AV21" s="4" t="n"/>
+      <c r="AW21" s="4" t="n"/>
+      <c r="AX21" s="4" t="n"/>
+      <c r="AY21" s="4" t="n"/>
+      <c r="AZ21" s="4" t="n"/>
+      <c r="BA21" s="4" t="n"/>
+      <c r="BB21" s="34">
+        <f>IFERROR(IF(OR(D21&lt;&gt;"Dry Swale",AT21="",AV21="",AW21=""),"",(AV21-AW21)/AT21),"")</f>
+        <v/>
+      </c>
+      <c r="BC21" s="34">
+        <f>IFERROR(IF(OR(D21&lt;&gt;"Dry Swale",AT21="",BA21="",BA21=0),"",FLOOR(AT21/BA21,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD21" s="34">
+        <f>IFERROR(IF(OR(D21&lt;&gt;"Dry Swale",BB21="",BB21=0,AZ21="",BA21="",AU21=""),"",0.5*MIN(BA21,AZ21/BB21)*AZ21*AU21),"")</f>
+        <v/>
+      </c>
+      <c r="BE21" s="47">
+        <f>IFERROR(IF(OR(BC21="",BD21=""),"",BC21*BD21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -13767,6 +14606,39 @@
         <f>IFERROR(IF(AL22=0,AK22,MIN(AK22,AL22)),0)</f>
         <v/>
       </c>
+      <c r="AN22" s="4" t="n"/>
+      <c r="AO22" s="4" t="n"/>
+      <c r="AP22" s="4" t="n"/>
+      <c r="AQ22" s="4" t="n"/>
+      <c r="AR22" s="4" t="n"/>
+      <c r="AS22" s="47">
+        <f>IFERROR(IF(D22&lt;&gt;"Bioretention","",IF(OR(AO22="",U22=""),"",MIN(IF(AP22="",9E9,AP22),IF(AQ22="",9E9,AQ22),IF(AR22="",9E9,AR22))- (AO22 + U22))),"")</f>
+        <v/>
+      </c>
+      <c r="AT22" s="4" t="n"/>
+      <c r="AU22" s="4" t="n"/>
+      <c r="AV22" s="4" t="n"/>
+      <c r="AW22" s="4" t="n"/>
+      <c r="AX22" s="4" t="n"/>
+      <c r="AY22" s="4" t="n"/>
+      <c r="AZ22" s="4" t="n"/>
+      <c r="BA22" s="4" t="n"/>
+      <c r="BB22" s="34">
+        <f>IFERROR(IF(OR(D22&lt;&gt;"Dry Swale",AT22="",AV22="",AW22=""),"",(AV22-AW22)/AT22),"")</f>
+        <v/>
+      </c>
+      <c r="BC22" s="34">
+        <f>IFERROR(IF(OR(D22&lt;&gt;"Dry Swale",AT22="",BA22="",BA22=0),"",FLOOR(AT22/BA22,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD22" s="34">
+        <f>IFERROR(IF(OR(D22&lt;&gt;"Dry Swale",BB22="",BB22=0,AZ22="",BA22="",AU22=""),"",0.5*MIN(BA22,AZ22/BB22)*AZ22*AU22),"")</f>
+        <v/>
+      </c>
+      <c r="BE22" s="47">
+        <f>IFERROR(IF(OR(BC22="",BD22=""),"",BC22*BD22),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -13862,6 +14734,39 @@
         <f>IFERROR(IF(AL23=0,AK23,MIN(AK23,AL23)),0)</f>
         <v/>
       </c>
+      <c r="AN23" s="4" t="n"/>
+      <c r="AO23" s="4" t="n"/>
+      <c r="AP23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="n"/>
+      <c r="AR23" s="4" t="n"/>
+      <c r="AS23" s="47">
+        <f>IFERROR(IF(D23&lt;&gt;"Bioretention","",IF(OR(AO23="",U23=""),"",MIN(IF(AP23="",9E9,AP23),IF(AQ23="",9E9,AQ23),IF(AR23="",9E9,AR23))- (AO23 + U23))),"")</f>
+        <v/>
+      </c>
+      <c r="AT23" s="4" t="n"/>
+      <c r="AU23" s="4" t="n"/>
+      <c r="AV23" s="4" t="n"/>
+      <c r="AW23" s="4" t="n"/>
+      <c r="AX23" s="4" t="n"/>
+      <c r="AY23" s="4" t="n"/>
+      <c r="AZ23" s="4" t="n"/>
+      <c r="BA23" s="4" t="n"/>
+      <c r="BB23" s="34">
+        <f>IFERROR(IF(OR(D23&lt;&gt;"Dry Swale",AT23="",AV23="",AW23=""),"",(AV23-AW23)/AT23),"")</f>
+        <v/>
+      </c>
+      <c r="BC23" s="34">
+        <f>IFERROR(IF(OR(D23&lt;&gt;"Dry Swale",AT23="",BA23="",BA23=0),"",FLOOR(AT23/BA23,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD23" s="34">
+        <f>IFERROR(IF(OR(D23&lt;&gt;"Dry Swale",BB23="",BB23=0,AZ23="",BA23="",AU23=""),"",0.5*MIN(BA23,AZ23/BB23)*AZ23*AU23),"")</f>
+        <v/>
+      </c>
+      <c r="BE23" s="47">
+        <f>IFERROR(IF(OR(BC23="",BD23=""),"",BC23*BD23),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -13957,6 +14862,39 @@
         <f>IFERROR(IF(AL24=0,AK24,MIN(AK24,AL24)),0)</f>
         <v/>
       </c>
+      <c r="AN24" s="4" t="n"/>
+      <c r="AO24" s="4" t="n"/>
+      <c r="AP24" s="4" t="n"/>
+      <c r="AQ24" s="4" t="n"/>
+      <c r="AR24" s="4" t="n"/>
+      <c r="AS24" s="47">
+        <f>IFERROR(IF(D24&lt;&gt;"Bioretention","",IF(OR(AO24="",U24=""),"",MIN(IF(AP24="",9E9,AP24),IF(AQ24="",9E9,AQ24),IF(AR24="",9E9,AR24))- (AO24 + U24))),"")</f>
+        <v/>
+      </c>
+      <c r="AT24" s="4" t="n"/>
+      <c r="AU24" s="4" t="n"/>
+      <c r="AV24" s="4" t="n"/>
+      <c r="AW24" s="4" t="n"/>
+      <c r="AX24" s="4" t="n"/>
+      <c r="AY24" s="4" t="n"/>
+      <c r="AZ24" s="4" t="n"/>
+      <c r="BA24" s="4" t="n"/>
+      <c r="BB24" s="34">
+        <f>IFERROR(IF(OR(D24&lt;&gt;"Dry Swale",AT24="",AV24="",AW24=""),"",(AV24-AW24)/AT24),"")</f>
+        <v/>
+      </c>
+      <c r="BC24" s="34">
+        <f>IFERROR(IF(OR(D24&lt;&gt;"Dry Swale",AT24="",BA24="",BA24=0),"",FLOOR(AT24/BA24,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD24" s="34">
+        <f>IFERROR(IF(OR(D24&lt;&gt;"Dry Swale",BB24="",BB24=0,AZ24="",BA24="",AU24=""),"",0.5*MIN(BA24,AZ24/BB24)*AZ24*AU24),"")</f>
+        <v/>
+      </c>
+      <c r="BE24" s="47">
+        <f>IFERROR(IF(OR(BC24="",BD24=""),"",BC24*BD24),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -14052,6 +14990,39 @@
         <f>IFERROR(IF(AL25=0,AK25,MIN(AK25,AL25)),0)</f>
         <v/>
       </c>
+      <c r="AN25" s="4" t="n"/>
+      <c r="AO25" s="4" t="n"/>
+      <c r="AP25" s="4" t="n"/>
+      <c r="AQ25" s="4" t="n"/>
+      <c r="AR25" s="4" t="n"/>
+      <c r="AS25" s="47">
+        <f>IFERROR(IF(D25&lt;&gt;"Bioretention","",IF(OR(AO25="",U25=""),"",MIN(IF(AP25="",9E9,AP25),IF(AQ25="",9E9,AQ25),IF(AR25="",9E9,AR25))- (AO25 + U25))),"")</f>
+        <v/>
+      </c>
+      <c r="AT25" s="4" t="n"/>
+      <c r="AU25" s="4" t="n"/>
+      <c r="AV25" s="4" t="n"/>
+      <c r="AW25" s="4" t="n"/>
+      <c r="AX25" s="4" t="n"/>
+      <c r="AY25" s="4" t="n"/>
+      <c r="AZ25" s="4" t="n"/>
+      <c r="BA25" s="4" t="n"/>
+      <c r="BB25" s="34">
+        <f>IFERROR(IF(OR(D25&lt;&gt;"Dry Swale",AT25="",AV25="",AW25=""),"",(AV25-AW25)/AT25),"")</f>
+        <v/>
+      </c>
+      <c r="BC25" s="34">
+        <f>IFERROR(IF(OR(D25&lt;&gt;"Dry Swale",AT25="",BA25="",BA25=0),"",FLOOR(AT25/BA25,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD25" s="34">
+        <f>IFERROR(IF(OR(D25&lt;&gt;"Dry Swale",BB25="",BB25=0,AZ25="",BA25="",AU25=""),"",0.5*MIN(BA25,AZ25/BB25)*AZ25*AU25),"")</f>
+        <v/>
+      </c>
+      <c r="BE25" s="47">
+        <f>IFERROR(IF(OR(BC25="",BD25=""),"",BC25*BD25),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -14147,6 +15118,39 @@
         <f>IFERROR(IF(AL26=0,AK26,MIN(AK26,AL26)),0)</f>
         <v/>
       </c>
+      <c r="AN26" s="4" t="n"/>
+      <c r="AO26" s="4" t="n"/>
+      <c r="AP26" s="4" t="n"/>
+      <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="47">
+        <f>IFERROR(IF(D26&lt;&gt;"Bioretention","",IF(OR(AO26="",U26=""),"",MIN(IF(AP26="",9E9,AP26),IF(AQ26="",9E9,AQ26),IF(AR26="",9E9,AR26))- (AO26 + U26))),"")</f>
+        <v/>
+      </c>
+      <c r="AT26" s="4" t="n"/>
+      <c r="AU26" s="4" t="n"/>
+      <c r="AV26" s="4" t="n"/>
+      <c r="AW26" s="4" t="n"/>
+      <c r="AX26" s="4" t="n"/>
+      <c r="AY26" s="4" t="n"/>
+      <c r="AZ26" s="4" t="n"/>
+      <c r="BA26" s="4" t="n"/>
+      <c r="BB26" s="34">
+        <f>IFERROR(IF(OR(D26&lt;&gt;"Dry Swale",AT26="",AV26="",AW26=""),"",(AV26-AW26)/AT26),"")</f>
+        <v/>
+      </c>
+      <c r="BC26" s="34">
+        <f>IFERROR(IF(OR(D26&lt;&gt;"Dry Swale",AT26="",BA26="",BA26=0),"",FLOOR(AT26/BA26,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD26" s="34">
+        <f>IFERROR(IF(OR(D26&lt;&gt;"Dry Swale",BB26="",BB26=0,AZ26="",BA26="",AU26=""),"",0.5*MIN(BA26,AZ26/BB26)*AZ26*AU26),"")</f>
+        <v/>
+      </c>
+      <c r="BE26" s="47">
+        <f>IFERROR(IF(OR(BC26="",BD26=""),"",BC26*BD26),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -14242,6 +15246,39 @@
         <f>IFERROR(IF(AL27=0,AK27,MIN(AK27,AL27)),0)</f>
         <v/>
       </c>
+      <c r="AN27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n"/>
+      <c r="AP27" s="4" t="n"/>
+      <c r="AQ27" s="4" t="n"/>
+      <c r="AR27" s="4" t="n"/>
+      <c r="AS27" s="47">
+        <f>IFERROR(IF(D27&lt;&gt;"Bioretention","",IF(OR(AO27="",U27=""),"",MIN(IF(AP27="",9E9,AP27),IF(AQ27="",9E9,AQ27),IF(AR27="",9E9,AR27))- (AO27 + U27))),"")</f>
+        <v/>
+      </c>
+      <c r="AT27" s="4" t="n"/>
+      <c r="AU27" s="4" t="n"/>
+      <c r="AV27" s="4" t="n"/>
+      <c r="AW27" s="4" t="n"/>
+      <c r="AX27" s="4" t="n"/>
+      <c r="AY27" s="4" t="n"/>
+      <c r="AZ27" s="4" t="n"/>
+      <c r="BA27" s="4" t="n"/>
+      <c r="BB27" s="34">
+        <f>IFERROR(IF(OR(D27&lt;&gt;"Dry Swale",AT27="",AV27="",AW27=""),"",(AV27-AW27)/AT27),"")</f>
+        <v/>
+      </c>
+      <c r="BC27" s="34">
+        <f>IFERROR(IF(OR(D27&lt;&gt;"Dry Swale",AT27="",BA27="",BA27=0),"",FLOOR(AT27/BA27,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD27" s="34">
+        <f>IFERROR(IF(OR(D27&lt;&gt;"Dry Swale",BB27="",BB27=0,AZ27="",BA27="",AU27=""),"",0.5*MIN(BA27,AZ27/BB27)*AZ27*AU27),"")</f>
+        <v/>
+      </c>
+      <c r="BE27" s="47">
+        <f>IFERROR(IF(OR(BC27="",BD27=""),"",BC27*BD27),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -14337,6 +15374,39 @@
         <f>IFERROR(IF(AL28=0,AK28,MIN(AK28,AL28)),0)</f>
         <v/>
       </c>
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n"/>
+      <c r="AP28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="47">
+        <f>IFERROR(IF(D28&lt;&gt;"Bioretention","",IF(OR(AO28="",U28=""),"",MIN(IF(AP28="",9E9,AP28),IF(AQ28="",9E9,AQ28),IF(AR28="",9E9,AR28))- (AO28 + U28))),"")</f>
+        <v/>
+      </c>
+      <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="n"/>
+      <c r="AV28" s="4" t="n"/>
+      <c r="AW28" s="4" t="n"/>
+      <c r="AX28" s="4" t="n"/>
+      <c r="AY28" s="4" t="n"/>
+      <c r="AZ28" s="4" t="n"/>
+      <c r="BA28" s="4" t="n"/>
+      <c r="BB28" s="34">
+        <f>IFERROR(IF(OR(D28&lt;&gt;"Dry Swale",AT28="",AV28="",AW28=""),"",(AV28-AW28)/AT28),"")</f>
+        <v/>
+      </c>
+      <c r="BC28" s="34">
+        <f>IFERROR(IF(OR(D28&lt;&gt;"Dry Swale",AT28="",BA28="",BA28=0),"",FLOOR(AT28/BA28,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD28" s="34">
+        <f>IFERROR(IF(OR(D28&lt;&gt;"Dry Swale",BB28="",BB28=0,AZ28="",BA28="",AU28=""),"",0.5*MIN(BA28,AZ28/BB28)*AZ28*AU28),"")</f>
+        <v/>
+      </c>
+      <c r="BE28" s="47">
+        <f>IFERROR(IF(OR(BC28="",BD28=""),"",BC28*BD28),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -14432,6 +15502,39 @@
         <f>IFERROR(IF(AL29=0,AK29,MIN(AK29,AL29)),0)</f>
         <v/>
       </c>
+      <c r="AN29" s="4" t="n"/>
+      <c r="AO29" s="4" t="n"/>
+      <c r="AP29" s="4" t="n"/>
+      <c r="AQ29" s="4" t="n"/>
+      <c r="AR29" s="4" t="n"/>
+      <c r="AS29" s="47">
+        <f>IFERROR(IF(D29&lt;&gt;"Bioretention","",IF(OR(AO29="",U29=""),"",MIN(IF(AP29="",9E9,AP29),IF(AQ29="",9E9,AQ29),IF(AR29="",9E9,AR29))- (AO29 + U29))),"")</f>
+        <v/>
+      </c>
+      <c r="AT29" s="4" t="n"/>
+      <c r="AU29" s="4" t="n"/>
+      <c r="AV29" s="4" t="n"/>
+      <c r="AW29" s="4" t="n"/>
+      <c r="AX29" s="4" t="n"/>
+      <c r="AY29" s="4" t="n"/>
+      <c r="AZ29" s="4" t="n"/>
+      <c r="BA29" s="4" t="n"/>
+      <c r="BB29" s="34">
+        <f>IFERROR(IF(OR(D29&lt;&gt;"Dry Swale",AT29="",AV29="",AW29=""),"",(AV29-AW29)/AT29),"")</f>
+        <v/>
+      </c>
+      <c r="BC29" s="34">
+        <f>IFERROR(IF(OR(D29&lt;&gt;"Dry Swale",AT29="",BA29="",BA29=0),"",FLOOR(AT29/BA29,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD29" s="34">
+        <f>IFERROR(IF(OR(D29&lt;&gt;"Dry Swale",BB29="",BB29=0,AZ29="",BA29="",AU29=""),"",0.5*MIN(BA29,AZ29/BB29)*AZ29*AU29),"")</f>
+        <v/>
+      </c>
+      <c r="BE29" s="47">
+        <f>IFERROR(IF(OR(BC29="",BD29=""),"",BC29*BD29),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -14527,6 +15630,39 @@
         <f>IFERROR(IF(AL30=0,AK30,MIN(AK30,AL30)),0)</f>
         <v/>
       </c>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="n"/>
+      <c r="AP30" s="4" t="n"/>
+      <c r="AQ30" s="4" t="n"/>
+      <c r="AR30" s="4" t="n"/>
+      <c r="AS30" s="47">
+        <f>IFERROR(IF(D30&lt;&gt;"Bioretention","",IF(OR(AO30="",U30=""),"",MIN(IF(AP30="",9E9,AP30),IF(AQ30="",9E9,AQ30),IF(AR30="",9E9,AR30))- (AO30 + U30))),"")</f>
+        <v/>
+      </c>
+      <c r="AT30" s="4" t="n"/>
+      <c r="AU30" s="4" t="n"/>
+      <c r="AV30" s="4" t="n"/>
+      <c r="AW30" s="4" t="n"/>
+      <c r="AX30" s="4" t="n"/>
+      <c r="AY30" s="4" t="n"/>
+      <c r="AZ30" s="4" t="n"/>
+      <c r="BA30" s="4" t="n"/>
+      <c r="BB30" s="34">
+        <f>IFERROR(IF(OR(D30&lt;&gt;"Dry Swale",AT30="",AV30="",AW30=""),"",(AV30-AW30)/AT30),"")</f>
+        <v/>
+      </c>
+      <c r="BC30" s="34">
+        <f>IFERROR(IF(OR(D30&lt;&gt;"Dry Swale",AT30="",BA30="",BA30=0),"",FLOOR(AT30/BA30,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD30" s="34">
+        <f>IFERROR(IF(OR(D30&lt;&gt;"Dry Swale",BB30="",BB30=0,AZ30="",BA30="",AU30=""),"",0.5*MIN(BA30,AZ30/BB30)*AZ30*AU30),"")</f>
+        <v/>
+      </c>
+      <c r="BE30" s="47">
+        <f>IFERROR(IF(OR(BC30="",BD30=""),"",BC30*BD30),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -14622,6 +15758,39 @@
         <f>IFERROR(IF(AL31=0,AK31,MIN(AK31,AL31)),0)</f>
         <v/>
       </c>
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n"/>
+      <c r="AP31" s="4" t="n"/>
+      <c r="AQ31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="47">
+        <f>IFERROR(IF(D31&lt;&gt;"Bioretention","",IF(OR(AO31="",U31=""),"",MIN(IF(AP31="",9E9,AP31),IF(AQ31="",9E9,AQ31),IF(AR31="",9E9,AR31))- (AO31 + U31))),"")</f>
+        <v/>
+      </c>
+      <c r="AT31" s="4" t="n"/>
+      <c r="AU31" s="4" t="n"/>
+      <c r="AV31" s="4" t="n"/>
+      <c r="AW31" s="4" t="n"/>
+      <c r="AX31" s="4" t="n"/>
+      <c r="AY31" s="4" t="n"/>
+      <c r="AZ31" s="4" t="n"/>
+      <c r="BA31" s="4" t="n"/>
+      <c r="BB31" s="34">
+        <f>IFERROR(IF(OR(D31&lt;&gt;"Dry Swale",AT31="",AV31="",AW31=""),"",(AV31-AW31)/AT31),"")</f>
+        <v/>
+      </c>
+      <c r="BC31" s="34">
+        <f>IFERROR(IF(OR(D31&lt;&gt;"Dry Swale",AT31="",BA31="",BA31=0),"",FLOOR(AT31/BA31,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD31" s="34">
+        <f>IFERROR(IF(OR(D31&lt;&gt;"Dry Swale",BB31="",BB31=0,AZ31="",BA31="",AU31=""),"",0.5*MIN(BA31,AZ31/BB31)*AZ31*AU31),"")</f>
+        <v/>
+      </c>
+      <c r="BE31" s="47">
+        <f>IFERROR(IF(OR(BC31="",BD31=""),"",BC31*BD31),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -14717,6 +15886,39 @@
         <f>IFERROR(IF(AL32=0,AK32,MIN(AK32,AL32)),0)</f>
         <v/>
       </c>
+      <c r="AN32" s="4" t="n"/>
+      <c r="AO32" s="4" t="n"/>
+      <c r="AP32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n"/>
+      <c r="AS32" s="47">
+        <f>IFERROR(IF(D32&lt;&gt;"Bioretention","",IF(OR(AO32="",U32=""),"",MIN(IF(AP32="",9E9,AP32),IF(AQ32="",9E9,AQ32),IF(AR32="",9E9,AR32))- (AO32 + U32))),"")</f>
+        <v/>
+      </c>
+      <c r="AT32" s="4" t="n"/>
+      <c r="AU32" s="4" t="n"/>
+      <c r="AV32" s="4" t="n"/>
+      <c r="AW32" s="4" t="n"/>
+      <c r="AX32" s="4" t="n"/>
+      <c r="AY32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="n"/>
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="34">
+        <f>IFERROR(IF(OR(D32&lt;&gt;"Dry Swale",AT32="",AV32="",AW32=""),"",(AV32-AW32)/AT32),"")</f>
+        <v/>
+      </c>
+      <c r="BC32" s="34">
+        <f>IFERROR(IF(OR(D32&lt;&gt;"Dry Swale",AT32="",BA32="",BA32=0),"",FLOOR(AT32/BA32,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD32" s="34">
+        <f>IFERROR(IF(OR(D32&lt;&gt;"Dry Swale",BB32="",BB32=0,AZ32="",BA32="",AU32=""),"",0.5*MIN(BA32,AZ32/BB32)*AZ32*AU32),"")</f>
+        <v/>
+      </c>
+      <c r="BE32" s="47">
+        <f>IFERROR(IF(OR(BC32="",BD32=""),"",BC32*BD32),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -14812,6 +16014,39 @@
         <f>IFERROR(IF(AL33=0,AK33,MIN(AK33,AL33)),0)</f>
         <v/>
       </c>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="n"/>
+      <c r="AP33" s="4" t="n"/>
+      <c r="AQ33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="47">
+        <f>IFERROR(IF(D33&lt;&gt;"Bioretention","",IF(OR(AO33="",U33=""),"",MIN(IF(AP33="",9E9,AP33),IF(AQ33="",9E9,AQ33),IF(AR33="",9E9,AR33))- (AO33 + U33))),"")</f>
+        <v/>
+      </c>
+      <c r="AT33" s="4" t="n"/>
+      <c r="AU33" s="4" t="n"/>
+      <c r="AV33" s="4" t="n"/>
+      <c r="AW33" s="4" t="n"/>
+      <c r="AX33" s="4" t="n"/>
+      <c r="AY33" s="4" t="n"/>
+      <c r="AZ33" s="4" t="n"/>
+      <c r="BA33" s="4" t="n"/>
+      <c r="BB33" s="34">
+        <f>IFERROR(IF(OR(D33&lt;&gt;"Dry Swale",AT33="",AV33="",AW33=""),"",(AV33-AW33)/AT33),"")</f>
+        <v/>
+      </c>
+      <c r="BC33" s="34">
+        <f>IFERROR(IF(OR(D33&lt;&gt;"Dry Swale",AT33="",BA33="",BA33=0),"",FLOOR(AT33/BA33,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD33" s="34">
+        <f>IFERROR(IF(OR(D33&lt;&gt;"Dry Swale",BB33="",BB33=0,AZ33="",BA33="",AU33=""),"",0.5*MIN(BA33,AZ33/BB33)*AZ33*AU33),"")</f>
+        <v/>
+      </c>
+      <c r="BE33" s="47">
+        <f>IFERROR(IF(OR(BC33="",BD33=""),"",BC33*BD33),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -14907,6 +16142,39 @@
         <f>IFERROR(IF(AL34=0,AK34,MIN(AK34,AL34)),0)</f>
         <v/>
       </c>
+      <c r="AN34" s="4" t="n"/>
+      <c r="AO34" s="4" t="n"/>
+      <c r="AP34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="n"/>
+      <c r="AR34" s="4" t="n"/>
+      <c r="AS34" s="47">
+        <f>IFERROR(IF(D34&lt;&gt;"Bioretention","",IF(OR(AO34="",U34=""),"",MIN(IF(AP34="",9E9,AP34),IF(AQ34="",9E9,AQ34),IF(AR34="",9E9,AR34))- (AO34 + U34))),"")</f>
+        <v/>
+      </c>
+      <c r="AT34" s="4" t="n"/>
+      <c r="AU34" s="4" t="n"/>
+      <c r="AV34" s="4" t="n"/>
+      <c r="AW34" s="4" t="n"/>
+      <c r="AX34" s="4" t="n"/>
+      <c r="AY34" s="4" t="n"/>
+      <c r="AZ34" s="4" t="n"/>
+      <c r="BA34" s="4" t="n"/>
+      <c r="BB34" s="34">
+        <f>IFERROR(IF(OR(D34&lt;&gt;"Dry Swale",AT34="",AV34="",AW34=""),"",(AV34-AW34)/AT34),"")</f>
+        <v/>
+      </c>
+      <c r="BC34" s="34">
+        <f>IFERROR(IF(OR(D34&lt;&gt;"Dry Swale",AT34="",BA34="",BA34=0),"",FLOOR(AT34/BA34,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD34" s="34">
+        <f>IFERROR(IF(OR(D34&lt;&gt;"Dry Swale",BB34="",BB34=0,AZ34="",BA34="",AU34=""),"",0.5*MIN(BA34,AZ34/BB34)*AZ34*AU34),"")</f>
+        <v/>
+      </c>
+      <c r="BE34" s="47">
+        <f>IFERROR(IF(OR(BC34="",BD34=""),"",BC34*BD34),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -15002,6 +16270,39 @@
         <f>IFERROR(IF(AL35=0,AK35,MIN(AK35,AL35)),0)</f>
         <v/>
       </c>
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="n"/>
+      <c r="AP35" s="4" t="n"/>
+      <c r="AQ35" s="4" t="n"/>
+      <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="47">
+        <f>IFERROR(IF(D35&lt;&gt;"Bioretention","",IF(OR(AO35="",U35=""),"",MIN(IF(AP35="",9E9,AP35),IF(AQ35="",9E9,AQ35),IF(AR35="",9E9,AR35))- (AO35 + U35))),"")</f>
+        <v/>
+      </c>
+      <c r="AT35" s="4" t="n"/>
+      <c r="AU35" s="4" t="n"/>
+      <c r="AV35" s="4" t="n"/>
+      <c r="AW35" s="4" t="n"/>
+      <c r="AX35" s="4" t="n"/>
+      <c r="AY35" s="4" t="n"/>
+      <c r="AZ35" s="4" t="n"/>
+      <c r="BA35" s="4" t="n"/>
+      <c r="BB35" s="34">
+        <f>IFERROR(IF(OR(D35&lt;&gt;"Dry Swale",AT35="",AV35="",AW35=""),"",(AV35-AW35)/AT35),"")</f>
+        <v/>
+      </c>
+      <c r="BC35" s="34">
+        <f>IFERROR(IF(OR(D35&lt;&gt;"Dry Swale",AT35="",BA35="",BA35=0),"",FLOOR(AT35/BA35,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD35" s="34">
+        <f>IFERROR(IF(OR(D35&lt;&gt;"Dry Swale",BB35="",BB35=0,AZ35="",BA35="",AU35=""),"",0.5*MIN(BA35,AZ35/BB35)*AZ35*AU35),"")</f>
+        <v/>
+      </c>
+      <c r="BE35" s="47">
+        <f>IFERROR(IF(OR(BC35="",BD35=""),"",BC35*BD35),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -15097,6 +16398,39 @@
         <f>IFERROR(IF(AL36=0,AK36,MIN(AK36,AL36)),0)</f>
         <v/>
       </c>
+      <c r="AN36" s="4" t="n"/>
+      <c r="AO36" s="4" t="n"/>
+      <c r="AP36" s="4" t="n"/>
+      <c r="AQ36" s="4" t="n"/>
+      <c r="AR36" s="4" t="n"/>
+      <c r="AS36" s="47">
+        <f>IFERROR(IF(D36&lt;&gt;"Bioretention","",IF(OR(AO36="",U36=""),"",MIN(IF(AP36="",9E9,AP36),IF(AQ36="",9E9,AQ36),IF(AR36="",9E9,AR36))- (AO36 + U36))),"")</f>
+        <v/>
+      </c>
+      <c r="AT36" s="4" t="n"/>
+      <c r="AU36" s="4" t="n"/>
+      <c r="AV36" s="4" t="n"/>
+      <c r="AW36" s="4" t="n"/>
+      <c r="AX36" s="4" t="n"/>
+      <c r="AY36" s="4" t="n"/>
+      <c r="AZ36" s="4" t="n"/>
+      <c r="BA36" s="4" t="n"/>
+      <c r="BB36" s="34">
+        <f>IFERROR(IF(OR(D36&lt;&gt;"Dry Swale",AT36="",AV36="",AW36=""),"",(AV36-AW36)/AT36),"")</f>
+        <v/>
+      </c>
+      <c r="BC36" s="34">
+        <f>IFERROR(IF(OR(D36&lt;&gt;"Dry Swale",AT36="",BA36="",BA36=0),"",FLOOR(AT36/BA36,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD36" s="34">
+        <f>IFERROR(IF(OR(D36&lt;&gt;"Dry Swale",BB36="",BB36=0,AZ36="",BA36="",AU36=""),"",0.5*MIN(BA36,AZ36/BB36)*AZ36*AU36),"")</f>
+        <v/>
+      </c>
+      <c r="BE36" s="47">
+        <f>IFERROR(IF(OR(BC36="",BD36=""),"",BC36*BD36),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -15192,6 +16526,39 @@
         <f>IFERROR(IF(AL37=0,AK37,MIN(AK37,AL37)),0)</f>
         <v/>
       </c>
+      <c r="AN37" s="4" t="n"/>
+      <c r="AO37" s="4" t="n"/>
+      <c r="AP37" s="4" t="n"/>
+      <c r="AQ37" s="4" t="n"/>
+      <c r="AR37" s="4" t="n"/>
+      <c r="AS37" s="47">
+        <f>IFERROR(IF(D37&lt;&gt;"Bioretention","",IF(OR(AO37="",U37=""),"",MIN(IF(AP37="",9E9,AP37),IF(AQ37="",9E9,AQ37),IF(AR37="",9E9,AR37))- (AO37 + U37))),"")</f>
+        <v/>
+      </c>
+      <c r="AT37" s="4" t="n"/>
+      <c r="AU37" s="4" t="n"/>
+      <c r="AV37" s="4" t="n"/>
+      <c r="AW37" s="4" t="n"/>
+      <c r="AX37" s="4" t="n"/>
+      <c r="AY37" s="4" t="n"/>
+      <c r="AZ37" s="4" t="n"/>
+      <c r="BA37" s="4" t="n"/>
+      <c r="BB37" s="34">
+        <f>IFERROR(IF(OR(D37&lt;&gt;"Dry Swale",AT37="",AV37="",AW37=""),"",(AV37-AW37)/AT37),"")</f>
+        <v/>
+      </c>
+      <c r="BC37" s="34">
+        <f>IFERROR(IF(OR(D37&lt;&gt;"Dry Swale",AT37="",BA37="",BA37=0),"",FLOOR(AT37/BA37,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD37" s="34">
+        <f>IFERROR(IF(OR(D37&lt;&gt;"Dry Swale",BB37="",BB37=0,AZ37="",BA37="",AU37=""),"",0.5*MIN(BA37,AZ37/BB37)*AZ37*AU37),"")</f>
+        <v/>
+      </c>
+      <c r="BE37" s="47">
+        <f>IFERROR(IF(OR(BC37="",BD37=""),"",BC37*BD37),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -15287,6 +16654,39 @@
         <f>IFERROR(IF(AL38=0,AK38,MIN(AK38,AL38)),0)</f>
         <v/>
       </c>
+      <c r="AN38" s="4" t="n"/>
+      <c r="AO38" s="4" t="n"/>
+      <c r="AP38" s="4" t="n"/>
+      <c r="AQ38" s="4" t="n"/>
+      <c r="AR38" s="4" t="n"/>
+      <c r="AS38" s="47">
+        <f>IFERROR(IF(D38&lt;&gt;"Bioretention","",IF(OR(AO38="",U38=""),"",MIN(IF(AP38="",9E9,AP38),IF(AQ38="",9E9,AQ38),IF(AR38="",9E9,AR38))- (AO38 + U38))),"")</f>
+        <v/>
+      </c>
+      <c r="AT38" s="4" t="n"/>
+      <c r="AU38" s="4" t="n"/>
+      <c r="AV38" s="4" t="n"/>
+      <c r="AW38" s="4" t="n"/>
+      <c r="AX38" s="4" t="n"/>
+      <c r="AY38" s="4" t="n"/>
+      <c r="AZ38" s="4" t="n"/>
+      <c r="BA38" s="4" t="n"/>
+      <c r="BB38" s="34">
+        <f>IFERROR(IF(OR(D38&lt;&gt;"Dry Swale",AT38="",AV38="",AW38=""),"",(AV38-AW38)/AT38),"")</f>
+        <v/>
+      </c>
+      <c r="BC38" s="34">
+        <f>IFERROR(IF(OR(D38&lt;&gt;"Dry Swale",AT38="",BA38="",BA38=0),"",FLOOR(AT38/BA38,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD38" s="34">
+        <f>IFERROR(IF(OR(D38&lt;&gt;"Dry Swale",BB38="",BB38=0,AZ38="",BA38="",AU38=""),"",0.5*MIN(BA38,AZ38/BB38)*AZ38*AU38),"")</f>
+        <v/>
+      </c>
+      <c r="BE38" s="47">
+        <f>IFERROR(IF(OR(BC38="",BD38=""),"",BC38*BD38),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -15382,6 +16782,39 @@
         <f>IFERROR(IF(AL39=0,AK39,MIN(AK39,AL39)),0)</f>
         <v/>
       </c>
+      <c r="AN39" s="4" t="n"/>
+      <c r="AO39" s="4" t="n"/>
+      <c r="AP39" s="4" t="n"/>
+      <c r="AQ39" s="4" t="n"/>
+      <c r="AR39" s="4" t="n"/>
+      <c r="AS39" s="47">
+        <f>IFERROR(IF(D39&lt;&gt;"Bioretention","",IF(OR(AO39="",U39=""),"",MIN(IF(AP39="",9E9,AP39),IF(AQ39="",9E9,AQ39),IF(AR39="",9E9,AR39))- (AO39 + U39))),"")</f>
+        <v/>
+      </c>
+      <c r="AT39" s="4" t="n"/>
+      <c r="AU39" s="4" t="n"/>
+      <c r="AV39" s="4" t="n"/>
+      <c r="AW39" s="4" t="n"/>
+      <c r="AX39" s="4" t="n"/>
+      <c r="AY39" s="4" t="n"/>
+      <c r="AZ39" s="4" t="n"/>
+      <c r="BA39" s="4" t="n"/>
+      <c r="BB39" s="34">
+        <f>IFERROR(IF(OR(D39&lt;&gt;"Dry Swale",AT39="",AV39="",AW39=""),"",(AV39-AW39)/AT39),"")</f>
+        <v/>
+      </c>
+      <c r="BC39" s="34">
+        <f>IFERROR(IF(OR(D39&lt;&gt;"Dry Swale",AT39="",BA39="",BA39=0),"",FLOOR(AT39/BA39,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD39" s="34">
+        <f>IFERROR(IF(OR(D39&lt;&gt;"Dry Swale",BB39="",BB39=0,AZ39="",BA39="",AU39=""),"",0.5*MIN(BA39,AZ39/BB39)*AZ39*AU39),"")</f>
+        <v/>
+      </c>
+      <c r="BE39" s="47">
+        <f>IFERROR(IF(OR(BC39="",BD39=""),"",BC39*BD39),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -15477,6 +16910,39 @@
         <f>IFERROR(IF(AL40=0,AK40,MIN(AK40,AL40)),0)</f>
         <v/>
       </c>
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="n"/>
+      <c r="AP40" s="4" t="n"/>
+      <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="47">
+        <f>IFERROR(IF(D40&lt;&gt;"Bioretention","",IF(OR(AO40="",U40=""),"",MIN(IF(AP40="",9E9,AP40),IF(AQ40="",9E9,AQ40),IF(AR40="",9E9,AR40))- (AO40 + U40))),"")</f>
+        <v/>
+      </c>
+      <c r="AT40" s="4" t="n"/>
+      <c r="AU40" s="4" t="n"/>
+      <c r="AV40" s="4" t="n"/>
+      <c r="AW40" s="4" t="n"/>
+      <c r="AX40" s="4" t="n"/>
+      <c r="AY40" s="4" t="n"/>
+      <c r="AZ40" s="4" t="n"/>
+      <c r="BA40" s="4" t="n"/>
+      <c r="BB40" s="34">
+        <f>IFERROR(IF(OR(D40&lt;&gt;"Dry Swale",AT40="",AV40="",AW40=""),"",(AV40-AW40)/AT40),"")</f>
+        <v/>
+      </c>
+      <c r="BC40" s="34">
+        <f>IFERROR(IF(OR(D40&lt;&gt;"Dry Swale",AT40="",BA40="",BA40=0),"",FLOOR(AT40/BA40,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD40" s="34">
+        <f>IFERROR(IF(OR(D40&lt;&gt;"Dry Swale",BB40="",BB40=0,AZ40="",BA40="",AU40=""),"",0.5*MIN(BA40,AZ40/BB40)*AZ40*AU40),"")</f>
+        <v/>
+      </c>
+      <c r="BE40" s="47">
+        <f>IFERROR(IF(OR(BC40="",BD40=""),"",BC40*BD40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -15572,6 +17038,39 @@
         <f>IFERROR(IF(AL41=0,AK41,MIN(AK41,AL41)),0)</f>
         <v/>
       </c>
+      <c r="AN41" s="4" t="n"/>
+      <c r="AO41" s="4" t="n"/>
+      <c r="AP41" s="4" t="n"/>
+      <c r="AQ41" s="4" t="n"/>
+      <c r="AR41" s="4" t="n"/>
+      <c r="AS41" s="47">
+        <f>IFERROR(IF(D41&lt;&gt;"Bioretention","",IF(OR(AO41="",U41=""),"",MIN(IF(AP41="",9E9,AP41),IF(AQ41="",9E9,AQ41),IF(AR41="",9E9,AR41))- (AO41 + U41))),"")</f>
+        <v/>
+      </c>
+      <c r="AT41" s="4" t="n"/>
+      <c r="AU41" s="4" t="n"/>
+      <c r="AV41" s="4" t="n"/>
+      <c r="AW41" s="4" t="n"/>
+      <c r="AX41" s="4" t="n"/>
+      <c r="AY41" s="4" t="n"/>
+      <c r="AZ41" s="4" t="n"/>
+      <c r="BA41" s="4" t="n"/>
+      <c r="BB41" s="34">
+        <f>IFERROR(IF(OR(D41&lt;&gt;"Dry Swale",AT41="",AV41="",AW41=""),"",(AV41-AW41)/AT41),"")</f>
+        <v/>
+      </c>
+      <c r="BC41" s="34">
+        <f>IFERROR(IF(OR(D41&lt;&gt;"Dry Swale",AT41="",BA41="",BA41=0),"",FLOOR(AT41/BA41,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD41" s="34">
+        <f>IFERROR(IF(OR(D41&lt;&gt;"Dry Swale",BB41="",BB41=0,AZ41="",BA41="",AU41=""),"",0.5*MIN(BA41,AZ41/BB41)*AZ41*AU41),"")</f>
+        <v/>
+      </c>
+      <c r="BE41" s="47">
+        <f>IFERROR(IF(OR(BC41="",BD41=""),"",BC41*BD41),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -15667,6 +17166,39 @@
         <f>IFERROR(IF(AL42=0,AK42,MIN(AK42,AL42)),0)</f>
         <v/>
       </c>
+      <c r="AN42" s="4" t="n"/>
+      <c r="AO42" s="4" t="n"/>
+      <c r="AP42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="n"/>
+      <c r="AS42" s="47">
+        <f>IFERROR(IF(D42&lt;&gt;"Bioretention","",IF(OR(AO42="",U42=""),"",MIN(IF(AP42="",9E9,AP42),IF(AQ42="",9E9,AQ42),IF(AR42="",9E9,AR42))- (AO42 + U42))),"")</f>
+        <v/>
+      </c>
+      <c r="AT42" s="4" t="n"/>
+      <c r="AU42" s="4" t="n"/>
+      <c r="AV42" s="4" t="n"/>
+      <c r="AW42" s="4" t="n"/>
+      <c r="AX42" s="4" t="n"/>
+      <c r="AY42" s="4" t="n"/>
+      <c r="AZ42" s="4" t="n"/>
+      <c r="BA42" s="4" t="n"/>
+      <c r="BB42" s="34">
+        <f>IFERROR(IF(OR(D42&lt;&gt;"Dry Swale",AT42="",AV42="",AW42=""),"",(AV42-AW42)/AT42),"")</f>
+        <v/>
+      </c>
+      <c r="BC42" s="34">
+        <f>IFERROR(IF(OR(D42&lt;&gt;"Dry Swale",AT42="",BA42="",BA42=0),"",FLOOR(AT42/BA42,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD42" s="34">
+        <f>IFERROR(IF(OR(D42&lt;&gt;"Dry Swale",BB42="",BB42=0,AZ42="",BA42="",AU42=""),"",0.5*MIN(BA42,AZ42/BB42)*AZ42*AU42),"")</f>
+        <v/>
+      </c>
+      <c r="BE42" s="47">
+        <f>IFERROR(IF(OR(BC42="",BD42=""),"",BC42*BD42),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -15762,6 +17294,39 @@
         <f>IFERROR(IF(AL43=0,AK43,MIN(AK43,AL43)),0)</f>
         <v/>
       </c>
+      <c r="AN43" s="4" t="n"/>
+      <c r="AO43" s="4" t="n"/>
+      <c r="AP43" s="4" t="n"/>
+      <c r="AQ43" s="4" t="n"/>
+      <c r="AR43" s="4" t="n"/>
+      <c r="AS43" s="47">
+        <f>IFERROR(IF(D43&lt;&gt;"Bioretention","",IF(OR(AO43="",U43=""),"",MIN(IF(AP43="",9E9,AP43),IF(AQ43="",9E9,AQ43),IF(AR43="",9E9,AR43))- (AO43 + U43))),"")</f>
+        <v/>
+      </c>
+      <c r="AT43" s="4" t="n"/>
+      <c r="AU43" s="4" t="n"/>
+      <c r="AV43" s="4" t="n"/>
+      <c r="AW43" s="4" t="n"/>
+      <c r="AX43" s="4" t="n"/>
+      <c r="AY43" s="4" t="n"/>
+      <c r="AZ43" s="4" t="n"/>
+      <c r="BA43" s="4" t="n"/>
+      <c r="BB43" s="34">
+        <f>IFERROR(IF(OR(D43&lt;&gt;"Dry Swale",AT43="",AV43="",AW43=""),"",(AV43-AW43)/AT43),"")</f>
+        <v/>
+      </c>
+      <c r="BC43" s="34">
+        <f>IFERROR(IF(OR(D43&lt;&gt;"Dry Swale",AT43="",BA43="",BA43=0),"",FLOOR(AT43/BA43,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD43" s="34">
+        <f>IFERROR(IF(OR(D43&lt;&gt;"Dry Swale",BB43="",BB43=0,AZ43="",BA43="",AU43=""),"",0.5*MIN(BA43,AZ43/BB43)*AZ43*AU43),"")</f>
+        <v/>
+      </c>
+      <c r="BE43" s="47">
+        <f>IFERROR(IF(OR(BC43="",BD43=""),"",BC43*BD43),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -15857,6 +17422,39 @@
         <f>IFERROR(IF(AL44=0,AK44,MIN(AK44,AL44)),0)</f>
         <v/>
       </c>
+      <c r="AN44" s="4" t="n"/>
+      <c r="AO44" s="4" t="n"/>
+      <c r="AP44" s="4" t="n"/>
+      <c r="AQ44" s="4" t="n"/>
+      <c r="AR44" s="4" t="n"/>
+      <c r="AS44" s="47">
+        <f>IFERROR(IF(D44&lt;&gt;"Bioretention","",IF(OR(AO44="",U44=""),"",MIN(IF(AP44="",9E9,AP44),IF(AQ44="",9E9,AQ44),IF(AR44="",9E9,AR44))- (AO44 + U44))),"")</f>
+        <v/>
+      </c>
+      <c r="AT44" s="4" t="n"/>
+      <c r="AU44" s="4" t="n"/>
+      <c r="AV44" s="4" t="n"/>
+      <c r="AW44" s="4" t="n"/>
+      <c r="AX44" s="4" t="n"/>
+      <c r="AY44" s="4" t="n"/>
+      <c r="AZ44" s="4" t="n"/>
+      <c r="BA44" s="4" t="n"/>
+      <c r="BB44" s="34">
+        <f>IFERROR(IF(OR(D44&lt;&gt;"Dry Swale",AT44="",AV44="",AW44=""),"",(AV44-AW44)/AT44),"")</f>
+        <v/>
+      </c>
+      <c r="BC44" s="34">
+        <f>IFERROR(IF(OR(D44&lt;&gt;"Dry Swale",AT44="",BA44="",BA44=0),"",FLOOR(AT44/BA44,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD44" s="34">
+        <f>IFERROR(IF(OR(D44&lt;&gt;"Dry Swale",BB44="",BB44=0,AZ44="",BA44="",AU44=""),"",0.5*MIN(BA44,AZ44/BB44)*AZ44*AU44),"")</f>
+        <v/>
+      </c>
+      <c r="BE44" s="47">
+        <f>IFERROR(IF(OR(BC44="",BD44=""),"",BC44*BD44),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -15952,6 +17550,39 @@
         <f>IFERROR(IF(AL45=0,AK45,MIN(AK45,AL45)),0)</f>
         <v/>
       </c>
+      <c r="AN45" s="4" t="n"/>
+      <c r="AO45" s="4" t="n"/>
+      <c r="AP45" s="4" t="n"/>
+      <c r="AQ45" s="4" t="n"/>
+      <c r="AR45" s="4" t="n"/>
+      <c r="AS45" s="47">
+        <f>IFERROR(IF(D45&lt;&gt;"Bioretention","",IF(OR(AO45="",U45=""),"",MIN(IF(AP45="",9E9,AP45),IF(AQ45="",9E9,AQ45),IF(AR45="",9E9,AR45))- (AO45 + U45))),"")</f>
+        <v/>
+      </c>
+      <c r="AT45" s="4" t="n"/>
+      <c r="AU45" s="4" t="n"/>
+      <c r="AV45" s="4" t="n"/>
+      <c r="AW45" s="4" t="n"/>
+      <c r="AX45" s="4" t="n"/>
+      <c r="AY45" s="4" t="n"/>
+      <c r="AZ45" s="4" t="n"/>
+      <c r="BA45" s="4" t="n"/>
+      <c r="BB45" s="34">
+        <f>IFERROR(IF(OR(D45&lt;&gt;"Dry Swale",AT45="",AV45="",AW45=""),"",(AV45-AW45)/AT45),"")</f>
+        <v/>
+      </c>
+      <c r="BC45" s="34">
+        <f>IFERROR(IF(OR(D45&lt;&gt;"Dry Swale",AT45="",BA45="",BA45=0),"",FLOOR(AT45/BA45,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD45" s="34">
+        <f>IFERROR(IF(OR(D45&lt;&gt;"Dry Swale",BB45="",BB45=0,AZ45="",BA45="",AU45=""),"",0.5*MIN(BA45,AZ45/BB45)*AZ45*AU45),"")</f>
+        <v/>
+      </c>
+      <c r="BE45" s="47">
+        <f>IFERROR(IF(OR(BC45="",BD45=""),"",BC45*BD45),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -16047,6 +17678,39 @@
         <f>IFERROR(IF(AL46=0,AK46,MIN(AK46,AL46)),0)</f>
         <v/>
       </c>
+      <c r="AN46" s="4" t="n"/>
+      <c r="AO46" s="4" t="n"/>
+      <c r="AP46" s="4" t="n"/>
+      <c r="AQ46" s="4" t="n"/>
+      <c r="AR46" s="4" t="n"/>
+      <c r="AS46" s="47">
+        <f>IFERROR(IF(D46&lt;&gt;"Bioretention","",IF(OR(AO46="",U46=""),"",MIN(IF(AP46="",9E9,AP46),IF(AQ46="",9E9,AQ46),IF(AR46="",9E9,AR46))- (AO46 + U46))),"")</f>
+        <v/>
+      </c>
+      <c r="AT46" s="4" t="n"/>
+      <c r="AU46" s="4" t="n"/>
+      <c r="AV46" s="4" t="n"/>
+      <c r="AW46" s="4" t="n"/>
+      <c r="AX46" s="4" t="n"/>
+      <c r="AY46" s="4" t="n"/>
+      <c r="AZ46" s="4" t="n"/>
+      <c r="BA46" s="4" t="n"/>
+      <c r="BB46" s="34">
+        <f>IFERROR(IF(OR(D46&lt;&gt;"Dry Swale",AT46="",AV46="",AW46=""),"",(AV46-AW46)/AT46),"")</f>
+        <v/>
+      </c>
+      <c r="BC46" s="34">
+        <f>IFERROR(IF(OR(D46&lt;&gt;"Dry Swale",AT46="",BA46="",BA46=0),"",FLOOR(AT46/BA46,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD46" s="34">
+        <f>IFERROR(IF(OR(D46&lt;&gt;"Dry Swale",BB46="",BB46=0,AZ46="",BA46="",AU46=""),"",0.5*MIN(BA46,AZ46/BB46)*AZ46*AU46),"")</f>
+        <v/>
+      </c>
+      <c r="BE46" s="47">
+        <f>IFERROR(IF(OR(BC46="",BD46=""),"",BC46*BD46),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -16142,6 +17806,39 @@
         <f>IFERROR(IF(AL47=0,AK47,MIN(AK47,AL47)),0)</f>
         <v/>
       </c>
+      <c r="AN47" s="4" t="n"/>
+      <c r="AO47" s="4" t="n"/>
+      <c r="AP47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="n"/>
+      <c r="AR47" s="4" t="n"/>
+      <c r="AS47" s="47">
+        <f>IFERROR(IF(D47&lt;&gt;"Bioretention","",IF(OR(AO47="",U47=""),"",MIN(IF(AP47="",9E9,AP47),IF(AQ47="",9E9,AQ47),IF(AR47="",9E9,AR47))- (AO47 + U47))),"")</f>
+        <v/>
+      </c>
+      <c r="AT47" s="4" t="n"/>
+      <c r="AU47" s="4" t="n"/>
+      <c r="AV47" s="4" t="n"/>
+      <c r="AW47" s="4" t="n"/>
+      <c r="AX47" s="4" t="n"/>
+      <c r="AY47" s="4" t="n"/>
+      <c r="AZ47" s="4" t="n"/>
+      <c r="BA47" s="4" t="n"/>
+      <c r="BB47" s="34">
+        <f>IFERROR(IF(OR(D47&lt;&gt;"Dry Swale",AT47="",AV47="",AW47=""),"",(AV47-AW47)/AT47),"")</f>
+        <v/>
+      </c>
+      <c r="BC47" s="34">
+        <f>IFERROR(IF(OR(D47&lt;&gt;"Dry Swale",AT47="",BA47="",BA47=0),"",FLOOR(AT47/BA47,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD47" s="34">
+        <f>IFERROR(IF(OR(D47&lt;&gt;"Dry Swale",BB47="",BB47=0,AZ47="",BA47="",AU47=""),"",0.5*MIN(BA47,AZ47/BB47)*AZ47*AU47),"")</f>
+        <v/>
+      </c>
+      <c r="BE47" s="47">
+        <f>IFERROR(IF(OR(BC47="",BD47=""),"",BC47*BD47),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -16237,6 +17934,39 @@
         <f>IFERROR(IF(AL48=0,AK48,MIN(AK48,AL48)),0)</f>
         <v/>
       </c>
+      <c r="AN48" s="4" t="n"/>
+      <c r="AO48" s="4" t="n"/>
+      <c r="AP48" s="4" t="n"/>
+      <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="n"/>
+      <c r="AS48" s="47">
+        <f>IFERROR(IF(D48&lt;&gt;"Bioretention","",IF(OR(AO48="",U48=""),"",MIN(IF(AP48="",9E9,AP48),IF(AQ48="",9E9,AQ48),IF(AR48="",9E9,AR48))- (AO48 + U48))),"")</f>
+        <v/>
+      </c>
+      <c r="AT48" s="4" t="n"/>
+      <c r="AU48" s="4" t="n"/>
+      <c r="AV48" s="4" t="n"/>
+      <c r="AW48" s="4" t="n"/>
+      <c r="AX48" s="4" t="n"/>
+      <c r="AY48" s="4" t="n"/>
+      <c r="AZ48" s="4" t="n"/>
+      <c r="BA48" s="4" t="n"/>
+      <c r="BB48" s="34">
+        <f>IFERROR(IF(OR(D48&lt;&gt;"Dry Swale",AT48="",AV48="",AW48=""),"",(AV48-AW48)/AT48),"")</f>
+        <v/>
+      </c>
+      <c r="BC48" s="34">
+        <f>IFERROR(IF(OR(D48&lt;&gt;"Dry Swale",AT48="",BA48="",BA48=0),"",FLOOR(AT48/BA48,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD48" s="34">
+        <f>IFERROR(IF(OR(D48&lt;&gt;"Dry Swale",BB48="",BB48=0,AZ48="",BA48="",AU48=""),"",0.5*MIN(BA48,AZ48/BB48)*AZ48*AU48),"")</f>
+        <v/>
+      </c>
+      <c r="BE48" s="47">
+        <f>IFERROR(IF(OR(BC48="",BD48=""),"",BC48*BD48),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -16332,6 +18062,39 @@
         <f>IFERROR(IF(AL49=0,AK49,MIN(AK49,AL49)),0)</f>
         <v/>
       </c>
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="n"/>
+      <c r="AP49" s="4" t="n"/>
+      <c r="AQ49" s="4" t="n"/>
+      <c r="AR49" s="4" t="n"/>
+      <c r="AS49" s="47">
+        <f>IFERROR(IF(D49&lt;&gt;"Bioretention","",IF(OR(AO49="",U49=""),"",MIN(IF(AP49="",9E9,AP49),IF(AQ49="",9E9,AQ49),IF(AR49="",9E9,AR49))- (AO49 + U49))),"")</f>
+        <v/>
+      </c>
+      <c r="AT49" s="4" t="n"/>
+      <c r="AU49" s="4" t="n"/>
+      <c r="AV49" s="4" t="n"/>
+      <c r="AW49" s="4" t="n"/>
+      <c r="AX49" s="4" t="n"/>
+      <c r="AY49" s="4" t="n"/>
+      <c r="AZ49" s="4" t="n"/>
+      <c r="BA49" s="4" t="n"/>
+      <c r="BB49" s="34">
+        <f>IFERROR(IF(OR(D49&lt;&gt;"Dry Swale",AT49="",AV49="",AW49=""),"",(AV49-AW49)/AT49),"")</f>
+        <v/>
+      </c>
+      <c r="BC49" s="34">
+        <f>IFERROR(IF(OR(D49&lt;&gt;"Dry Swale",AT49="",BA49="",BA49=0),"",FLOOR(AT49/BA49,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD49" s="34">
+        <f>IFERROR(IF(OR(D49&lt;&gt;"Dry Swale",BB49="",BB49=0,AZ49="",BA49="",AU49=""),"",0.5*MIN(BA49,AZ49/BB49)*AZ49*AU49),"")</f>
+        <v/>
+      </c>
+      <c r="BE49" s="47">
+        <f>IFERROR(IF(OR(BC49="",BD49=""),"",BC49*BD49),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -16427,6 +18190,39 @@
         <f>IFERROR(IF(AL50=0,AK50,MIN(AK50,AL50)),0)</f>
         <v/>
       </c>
+      <c r="AN50" s="4" t="n"/>
+      <c r="AO50" s="4" t="n"/>
+      <c r="AP50" s="4" t="n"/>
+      <c r="AQ50" s="4" t="n"/>
+      <c r="AR50" s="4" t="n"/>
+      <c r="AS50" s="47">
+        <f>IFERROR(IF(D50&lt;&gt;"Bioretention","",IF(OR(AO50="",U50=""),"",MIN(IF(AP50="",9E9,AP50),IF(AQ50="",9E9,AQ50),IF(AR50="",9E9,AR50))- (AO50 + U50))),"")</f>
+        <v/>
+      </c>
+      <c r="AT50" s="4" t="n"/>
+      <c r="AU50" s="4" t="n"/>
+      <c r="AV50" s="4" t="n"/>
+      <c r="AW50" s="4" t="n"/>
+      <c r="AX50" s="4" t="n"/>
+      <c r="AY50" s="4" t="n"/>
+      <c r="AZ50" s="4" t="n"/>
+      <c r="BA50" s="4" t="n"/>
+      <c r="BB50" s="34">
+        <f>IFERROR(IF(OR(D50&lt;&gt;"Dry Swale",AT50="",AV50="",AW50=""),"",(AV50-AW50)/AT50),"")</f>
+        <v/>
+      </c>
+      <c r="BC50" s="34">
+        <f>IFERROR(IF(OR(D50&lt;&gt;"Dry Swale",AT50="",BA50="",BA50=0),"",FLOOR(AT50/BA50,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD50" s="34">
+        <f>IFERROR(IF(OR(D50&lt;&gt;"Dry Swale",BB50="",BB50=0,AZ50="",BA50="",AU50=""),"",0.5*MIN(BA50,AZ50/BB50)*AZ50*AU50),"")</f>
+        <v/>
+      </c>
+      <c r="BE50" s="47">
+        <f>IFERROR(IF(OR(BC50="",BD50=""),"",BC50*BD50),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -16522,6 +18318,39 @@
         <f>IFERROR(IF(AL51=0,AK51,MIN(AK51,AL51)),0)</f>
         <v/>
       </c>
+      <c r="AN51" s="4" t="n"/>
+      <c r="AO51" s="4" t="n"/>
+      <c r="AP51" s="4" t="n"/>
+      <c r="AQ51" s="4" t="n"/>
+      <c r="AR51" s="4" t="n"/>
+      <c r="AS51" s="47">
+        <f>IFERROR(IF(D51&lt;&gt;"Bioretention","",IF(OR(AO51="",U51=""),"",MIN(IF(AP51="",9E9,AP51),IF(AQ51="",9E9,AQ51),IF(AR51="",9E9,AR51))- (AO51 + U51))),"")</f>
+        <v/>
+      </c>
+      <c r="AT51" s="4" t="n"/>
+      <c r="AU51" s="4" t="n"/>
+      <c r="AV51" s="4" t="n"/>
+      <c r="AW51" s="4" t="n"/>
+      <c r="AX51" s="4" t="n"/>
+      <c r="AY51" s="4" t="n"/>
+      <c r="AZ51" s="4" t="n"/>
+      <c r="BA51" s="4" t="n"/>
+      <c r="BB51" s="34">
+        <f>IFERROR(IF(OR(D51&lt;&gt;"Dry Swale",AT51="",AV51="",AW51=""),"",(AV51-AW51)/AT51),"")</f>
+        <v/>
+      </c>
+      <c r="BC51" s="34">
+        <f>IFERROR(IF(OR(D51&lt;&gt;"Dry Swale",AT51="",BA51="",BA51=0),"",FLOOR(AT51/BA51,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD51" s="34">
+        <f>IFERROR(IF(OR(D51&lt;&gt;"Dry Swale",BB51="",BB51=0,AZ51="",BA51="",AU51=""),"",0.5*MIN(BA51,AZ51/BB51)*AZ51*AU51),"")</f>
+        <v/>
+      </c>
+      <c r="BE51" s="47">
+        <f>IFERROR(IF(OR(BC51="",BD51=""),"",BC51*BD51),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -16617,6 +18446,39 @@
         <f>IFERROR(IF(AL52=0,AK52,MIN(AK52,AL52)),0)</f>
         <v/>
       </c>
+      <c r="AN52" s="4" t="n"/>
+      <c r="AO52" s="4" t="n"/>
+      <c r="AP52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="n"/>
+      <c r="AS52" s="47">
+        <f>IFERROR(IF(D52&lt;&gt;"Bioretention","",IF(OR(AO52="",U52=""),"",MIN(IF(AP52="",9E9,AP52),IF(AQ52="",9E9,AQ52),IF(AR52="",9E9,AR52))- (AO52 + U52))),"")</f>
+        <v/>
+      </c>
+      <c r="AT52" s="4" t="n"/>
+      <c r="AU52" s="4" t="n"/>
+      <c r="AV52" s="4" t="n"/>
+      <c r="AW52" s="4" t="n"/>
+      <c r="AX52" s="4" t="n"/>
+      <c r="AY52" s="4" t="n"/>
+      <c r="AZ52" s="4" t="n"/>
+      <c r="BA52" s="4" t="n"/>
+      <c r="BB52" s="34">
+        <f>IFERROR(IF(OR(D52&lt;&gt;"Dry Swale",AT52="",AV52="",AW52=""),"",(AV52-AW52)/AT52),"")</f>
+        <v/>
+      </c>
+      <c r="BC52" s="34">
+        <f>IFERROR(IF(OR(D52&lt;&gt;"Dry Swale",AT52="",BA52="",BA52=0),"",FLOOR(AT52/BA52,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD52" s="34">
+        <f>IFERROR(IF(OR(D52&lt;&gt;"Dry Swale",BB52="",BB52=0,AZ52="",BA52="",AU52=""),"",0.5*MIN(BA52,AZ52/BB52)*AZ52*AU52),"")</f>
+        <v/>
+      </c>
+      <c r="BE52" s="47">
+        <f>IFERROR(IF(OR(BC52="",BD52=""),"",BC52*BD52),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -16710,6 +18572,39 @@
       </c>
       <c r="AM53" s="49">
         <f>IFERROR(IF(AL53=0,AK53,MIN(AK53,AL53)),0)</f>
+        <v/>
+      </c>
+      <c r="AN53" s="4" t="n"/>
+      <c r="AO53" s="4" t="n"/>
+      <c r="AP53" s="4" t="n"/>
+      <c r="AQ53" s="4" t="n"/>
+      <c r="AR53" s="4" t="n"/>
+      <c r="AS53" s="47">
+        <f>IFERROR(IF(D53&lt;&gt;"Bioretention","",IF(OR(AO53="",U53=""),"",MIN(IF(AP53="",9E9,AP53),IF(AQ53="",9E9,AQ53),IF(AR53="",9E9,AR53))- (AO53 + U53))),"")</f>
+        <v/>
+      </c>
+      <c r="AT53" s="4" t="n"/>
+      <c r="AU53" s="4" t="n"/>
+      <c r="AV53" s="4" t="n"/>
+      <c r="AW53" s="4" t="n"/>
+      <c r="AX53" s="4" t="n"/>
+      <c r="AY53" s="4" t="n"/>
+      <c r="AZ53" s="4" t="n"/>
+      <c r="BA53" s="4" t="n"/>
+      <c r="BB53" s="34">
+        <f>IFERROR(IF(OR(D53&lt;&gt;"Dry Swale",AT53="",AV53="",AW53=""),"",(AV53-AW53)/AT53),"")</f>
+        <v/>
+      </c>
+      <c r="BC53" s="34">
+        <f>IFERROR(IF(OR(D53&lt;&gt;"Dry Swale",AT53="",BA53="",BA53=0),"",FLOOR(AT53/BA53,1)),"")</f>
+        <v/>
+      </c>
+      <c r="BD53" s="34">
+        <f>IFERROR(IF(OR(D53&lt;&gt;"Dry Swale",BB53="",BB53=0,AZ53="",BA53="",AU53=""),"",0.5*MIN(BA53,AZ53/BB53)*AZ53*AU53),"")</f>
+        <v/>
+      </c>
+      <c r="BE53" s="47">
+        <f>IFERROR(IF(OR(BC53="",BD53=""),"",BC53*BD53),"")</f>
         <v/>
       </c>
     </row>
@@ -16827,6 +18722,24 @@
       <c r="AK56" s="53" t="n"/>
       <c r="AL56" s="53" t="n"/>
       <c r="AM56" s="58" t="n"/>
+      <c r="AN56" s="60" t="n"/>
+      <c r="AO56" s="60" t="n"/>
+      <c r="AP56" s="60" t="n"/>
+      <c r="AQ56" s="60" t="n"/>
+      <c r="AR56" s="60" t="n"/>
+      <c r="AS56" s="56" t="n"/>
+      <c r="AT56" s="60" t="n"/>
+      <c r="AU56" s="60" t="n"/>
+      <c r="AV56" s="60" t="n"/>
+      <c r="AW56" s="60" t="n"/>
+      <c r="AX56" s="60" t="n"/>
+      <c r="AY56" s="60" t="n"/>
+      <c r="AZ56" s="60" t="n"/>
+      <c r="BA56" s="60" t="n"/>
+      <c r="BB56" s="60" t="n"/>
+      <c r="BC56" s="60" t="n"/>
+      <c r="BD56" s="60" t="n"/>
+      <c r="BE56" s="56" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -16861,7 +18774,7 @@
       <c r="J57" s="23" t="n"/>
       <c r="K57" s="22" t="n"/>
       <c r="L57" s="24" t="n"/>
-      <c r="M57" s="60" t="n"/>
+      <c r="M57" s="61" t="n"/>
       <c r="N57" s="22" t="n"/>
       <c r="O57" s="22" t="n"/>
       <c r="P57" s="22" t="n"/>
@@ -16872,22 +18785,24 @@
       <c r="U57" s="24" t="n"/>
       <c r="V57" s="23" t="n"/>
       <c r="W57" s="22" t="n"/>
-      <c r="X57" s="61" t="n"/>
+      <c r="X57" s="62" t="n"/>
       <c r="Y57" s="22" t="n"/>
       <c r="Z57" s="22" t="n"/>
-      <c r="AA57" s="62" t="n"/>
+      <c r="AA57" s="63" t="n"/>
       <c r="AB57" s="51" t="n"/>
       <c r="AC57" s="51" t="n"/>
       <c r="AD57" s="51" t="n"/>
       <c r="AE57" s="51" t="n"/>
       <c r="AF57" s="51" t="n"/>
       <c r="AG57" s="51" t="n"/>
-      <c r="AH57" s="62" t="n"/>
+      <c r="AH57" s="63" t="n"/>
       <c r="AI57" s="22" t="n"/>
       <c r="AJ57" s="23" t="n"/>
       <c r="AK57" s="22" t="n"/>
       <c r="AL57" s="22" t="n"/>
-      <c r="AM57" s="62" t="n"/>
+      <c r="AM57" s="63" t="n"/>
+      <c r="AS57" s="61" t="n"/>
+      <c r="BE57" s="61" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="34">
@@ -16917,7 +18832,7 @@
       <c r="J58" s="23" t="n"/>
       <c r="K58" s="22" t="n"/>
       <c r="L58" s="24" t="n"/>
-      <c r="M58" s="60" t="n"/>
+      <c r="M58" s="61" t="n"/>
       <c r="N58" s="22" t="n"/>
       <c r="O58" s="22" t="n"/>
       <c r="P58" s="22" t="n"/>
@@ -16928,22 +18843,24 @@
       <c r="U58" s="24" t="n"/>
       <c r="V58" s="23" t="n"/>
       <c r="W58" s="22" t="n"/>
-      <c r="X58" s="61" t="n"/>
+      <c r="X58" s="62" t="n"/>
       <c r="Y58" s="22" t="n"/>
       <c r="Z58" s="22" t="n"/>
-      <c r="AA58" s="62" t="n"/>
+      <c r="AA58" s="63" t="n"/>
       <c r="AB58" s="51" t="n"/>
       <c r="AC58" s="51" t="n"/>
       <c r="AD58" s="51" t="n"/>
       <c r="AE58" s="51" t="n"/>
       <c r="AF58" s="51" t="n"/>
       <c r="AG58" s="51" t="n"/>
-      <c r="AH58" s="62" t="n"/>
+      <c r="AH58" s="63" t="n"/>
       <c r="AI58" s="22" t="n"/>
       <c r="AJ58" s="23" t="n"/>
       <c r="AK58" s="22" t="n"/>
       <c r="AL58" s="22" t="n"/>
-      <c r="AM58" s="62" t="n"/>
+      <c r="AM58" s="63" t="n"/>
+      <c r="AS58" s="61" t="n"/>
+      <c r="BE58" s="61" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="34">
@@ -16973,7 +18890,7 @@
       <c r="J59" s="23" t="n"/>
       <c r="K59" s="22" t="n"/>
       <c r="L59" s="24" t="n"/>
-      <c r="M59" s="60" t="n"/>
+      <c r="M59" s="61" t="n"/>
       <c r="N59" s="22" t="n"/>
       <c r="O59" s="22" t="n"/>
       <c r="P59" s="22" t="n"/>
@@ -16984,22 +18901,24 @@
       <c r="U59" s="24" t="n"/>
       <c r="V59" s="23" t="n"/>
       <c r="W59" s="22" t="n"/>
-      <c r="X59" s="61" t="n"/>
+      <c r="X59" s="62" t="n"/>
       <c r="Y59" s="22" t="n"/>
       <c r="Z59" s="22" t="n"/>
-      <c r="AA59" s="62" t="n"/>
+      <c r="AA59" s="63" t="n"/>
       <c r="AB59" s="51" t="n"/>
       <c r="AC59" s="51" t="n"/>
       <c r="AD59" s="51" t="n"/>
       <c r="AE59" s="51" t="n"/>
       <c r="AF59" s="51" t="n"/>
       <c r="AG59" s="51" t="n"/>
-      <c r="AH59" s="62" t="n"/>
+      <c r="AH59" s="63" t="n"/>
       <c r="AI59" s="22" t="n"/>
       <c r="AJ59" s="23" t="n"/>
       <c r="AK59" s="22" t="n"/>
       <c r="AL59" s="22" t="n"/>
-      <c r="AM59" s="62" t="n"/>
+      <c r="AM59" s="63" t="n"/>
+      <c r="AS59" s="61" t="n"/>
+      <c r="BE59" s="61" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="34">
@@ -17029,7 +18948,7 @@
       <c r="J60" s="23" t="n"/>
       <c r="K60" s="22" t="n"/>
       <c r="L60" s="24" t="n"/>
-      <c r="M60" s="60" t="n"/>
+      <c r="M60" s="61" t="n"/>
       <c r="N60" s="22" t="n"/>
       <c r="O60" s="22" t="n"/>
       <c r="P60" s="22" t="n"/>
@@ -17040,22 +18959,24 @@
       <c r="U60" s="24" t="n"/>
       <c r="V60" s="23" t="n"/>
       <c r="W60" s="22" t="n"/>
-      <c r="X60" s="61" t="n"/>
+      <c r="X60" s="62" t="n"/>
       <c r="Y60" s="22" t="n"/>
       <c r="Z60" s="22" t="n"/>
-      <c r="AA60" s="62" t="n"/>
+      <c r="AA60" s="63" t="n"/>
       <c r="AB60" s="51" t="n"/>
       <c r="AC60" s="51" t="n"/>
       <c r="AD60" s="51" t="n"/>
       <c r="AE60" s="51" t="n"/>
       <c r="AF60" s="51" t="n"/>
       <c r="AG60" s="51" t="n"/>
-      <c r="AH60" s="62" t="n"/>
+      <c r="AH60" s="63" t="n"/>
       <c r="AI60" s="22" t="n"/>
       <c r="AJ60" s="23" t="n"/>
       <c r="AK60" s="22" t="n"/>
       <c r="AL60" s="22" t="n"/>
-      <c r="AM60" s="62" t="n"/>
+      <c r="AM60" s="63" t="n"/>
+      <c r="AS60" s="61" t="n"/>
+      <c r="BE60" s="61" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="34">
@@ -17085,7 +19006,7 @@
       <c r="J61" s="23" t="n"/>
       <c r="K61" s="22" t="n"/>
       <c r="L61" s="24" t="n"/>
-      <c r="M61" s="60" t="n"/>
+      <c r="M61" s="61" t="n"/>
       <c r="N61" s="22" t="n"/>
       <c r="O61" s="22" t="n"/>
       <c r="P61" s="22" t="n"/>
@@ -17096,22 +19017,24 @@
       <c r="U61" s="24" t="n"/>
       <c r="V61" s="23" t="n"/>
       <c r="W61" s="22" t="n"/>
-      <c r="X61" s="61" t="n"/>
+      <c r="X61" s="62" t="n"/>
       <c r="Y61" s="22" t="n"/>
       <c r="Z61" s="22" t="n"/>
-      <c r="AA61" s="62" t="n"/>
+      <c r="AA61" s="63" t="n"/>
       <c r="AB61" s="51" t="n"/>
       <c r="AC61" s="51" t="n"/>
       <c r="AD61" s="51" t="n"/>
       <c r="AE61" s="51" t="n"/>
       <c r="AF61" s="51" t="n"/>
       <c r="AG61" s="51" t="n"/>
-      <c r="AH61" s="62" t="n"/>
+      <c r="AH61" s="63" t="n"/>
       <c r="AI61" s="22" t="n"/>
       <c r="AJ61" s="23" t="n"/>
       <c r="AK61" s="22" t="n"/>
       <c r="AL61" s="22" t="n"/>
-      <c r="AM61" s="62" t="n"/>
+      <c r="AM61" s="63" t="n"/>
+      <c r="AS61" s="61" t="n"/>
+      <c r="BE61" s="61" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="34">
@@ -17141,7 +19064,7 @@
       <c r="J62" s="23" t="n"/>
       <c r="K62" s="22" t="n"/>
       <c r="L62" s="24" t="n"/>
-      <c r="M62" s="60" t="n"/>
+      <c r="M62" s="61" t="n"/>
       <c r="N62" s="22" t="n"/>
       <c r="O62" s="22" t="n"/>
       <c r="P62" s="22" t="n"/>
@@ -17152,22 +19075,24 @@
       <c r="U62" s="24" t="n"/>
       <c r="V62" s="23" t="n"/>
       <c r="W62" s="22" t="n"/>
-      <c r="X62" s="61" t="n"/>
+      <c r="X62" s="62" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="22" t="n"/>
-      <c r="AA62" s="62" t="n"/>
+      <c r="AA62" s="63" t="n"/>
       <c r="AB62" s="51" t="n"/>
       <c r="AC62" s="51" t="n"/>
       <c r="AD62" s="51" t="n"/>
       <c r="AE62" s="51" t="n"/>
       <c r="AF62" s="51" t="n"/>
       <c r="AG62" s="51" t="n"/>
-      <c r="AH62" s="62" t="n"/>
+      <c r="AH62" s="63" t="n"/>
       <c r="AI62" s="22" t="n"/>
       <c r="AJ62" s="23" t="n"/>
       <c r="AK62" s="22" t="n"/>
       <c r="AL62" s="22" t="n"/>
-      <c r="AM62" s="62" t="n"/>
+      <c r="AM62" s="63" t="n"/>
+      <c r="AS62" s="61" t="n"/>
+      <c r="BE62" s="61" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="34">
@@ -17197,7 +19122,7 @@
       <c r="J63" s="23" t="n"/>
       <c r="K63" s="22" t="n"/>
       <c r="L63" s="24" t="n"/>
-      <c r="M63" s="60" t="n"/>
+      <c r="M63" s="61" t="n"/>
       <c r="N63" s="22" t="n"/>
       <c r="O63" s="22" t="n"/>
       <c r="P63" s="22" t="n"/>
@@ -17208,22 +19133,24 @@
       <c r="U63" s="24" t="n"/>
       <c r="V63" s="23" t="n"/>
       <c r="W63" s="22" t="n"/>
-      <c r="X63" s="61" t="n"/>
+      <c r="X63" s="62" t="n"/>
       <c r="Y63" s="22" t="n"/>
       <c r="Z63" s="22" t="n"/>
-      <c r="AA63" s="62" t="n"/>
+      <c r="AA63" s="63" t="n"/>
       <c r="AB63" s="51" t="n"/>
       <c r="AC63" s="51" t="n"/>
       <c r="AD63" s="51" t="n"/>
       <c r="AE63" s="51" t="n"/>
       <c r="AF63" s="51" t="n"/>
       <c r="AG63" s="51" t="n"/>
-      <c r="AH63" s="62" t="n"/>
+      <c r="AH63" s="63" t="n"/>
       <c r="AI63" s="22" t="n"/>
       <c r="AJ63" s="23" t="n"/>
       <c r="AK63" s="22" t="n"/>
       <c r="AL63" s="22" t="n"/>
-      <c r="AM63" s="62" t="n"/>
+      <c r="AM63" s="63" t="n"/>
+      <c r="AS63" s="61" t="n"/>
+      <c r="BE63" s="61" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="34">
@@ -17253,7 +19180,7 @@
       <c r="J64" s="23" t="n"/>
       <c r="K64" s="22" t="n"/>
       <c r="L64" s="24" t="n"/>
-      <c r="M64" s="60" t="n"/>
+      <c r="M64" s="61" t="n"/>
       <c r="N64" s="22" t="n"/>
       <c r="O64" s="22" t="n"/>
       <c r="P64" s="22" t="n"/>
@@ -17264,22 +19191,24 @@
       <c r="U64" s="24" t="n"/>
       <c r="V64" s="23" t="n"/>
       <c r="W64" s="22" t="n"/>
-      <c r="X64" s="61" t="n"/>
+      <c r="X64" s="62" t="n"/>
       <c r="Y64" s="22" t="n"/>
       <c r="Z64" s="22" t="n"/>
-      <c r="AA64" s="62" t="n"/>
+      <c r="AA64" s="63" t="n"/>
       <c r="AB64" s="51" t="n"/>
       <c r="AC64" s="51" t="n"/>
       <c r="AD64" s="51" t="n"/>
       <c r="AE64" s="51" t="n"/>
       <c r="AF64" s="51" t="n"/>
       <c r="AG64" s="51" t="n"/>
-      <c r="AH64" s="62" t="n"/>
+      <c r="AH64" s="63" t="n"/>
       <c r="AI64" s="22" t="n"/>
       <c r="AJ64" s="23" t="n"/>
       <c r="AK64" s="22" t="n"/>
       <c r="AL64" s="22" t="n"/>
-      <c r="AM64" s="62" t="n"/>
+      <c r="AM64" s="63" t="n"/>
+      <c r="AS64" s="61" t="n"/>
+      <c r="BE64" s="61" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="34">
@@ -17309,7 +19238,7 @@
       <c r="J65" s="23" t="n"/>
       <c r="K65" s="22" t="n"/>
       <c r="L65" s="24" t="n"/>
-      <c r="M65" s="60" t="n"/>
+      <c r="M65" s="61" t="n"/>
       <c r="N65" s="22" t="n"/>
       <c r="O65" s="22" t="n"/>
       <c r="P65" s="22" t="n"/>
@@ -17320,22 +19249,24 @@
       <c r="U65" s="24" t="n"/>
       <c r="V65" s="23" t="n"/>
       <c r="W65" s="22" t="n"/>
-      <c r="X65" s="61" t="n"/>
+      <c r="X65" s="62" t="n"/>
       <c r="Y65" s="22" t="n"/>
       <c r="Z65" s="22" t="n"/>
-      <c r="AA65" s="62" t="n"/>
+      <c r="AA65" s="63" t="n"/>
       <c r="AB65" s="51" t="n"/>
       <c r="AC65" s="51" t="n"/>
       <c r="AD65" s="51" t="n"/>
       <c r="AE65" s="51" t="n"/>
       <c r="AF65" s="51" t="n"/>
       <c r="AG65" s="51" t="n"/>
-      <c r="AH65" s="62" t="n"/>
+      <c r="AH65" s="63" t="n"/>
       <c r="AI65" s="22" t="n"/>
       <c r="AJ65" s="23" t="n"/>
       <c r="AK65" s="22" t="n"/>
       <c r="AL65" s="22" t="n"/>
-      <c r="AM65" s="62" t="n"/>
+      <c r="AM65" s="63" t="n"/>
+      <c r="AS65" s="61" t="n"/>
+      <c r="BE65" s="61" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="34">
@@ -17365,7 +19296,7 @@
       <c r="J66" s="23" t="n"/>
       <c r="K66" s="22" t="n"/>
       <c r="L66" s="24" t="n"/>
-      <c r="M66" s="60" t="n"/>
+      <c r="M66" s="61" t="n"/>
       <c r="N66" s="22" t="n"/>
       <c r="O66" s="22" t="n"/>
       <c r="P66" s="22" t="n"/>
@@ -17376,22 +19307,24 @@
       <c r="U66" s="24" t="n"/>
       <c r="V66" s="23" t="n"/>
       <c r="W66" s="22" t="n"/>
-      <c r="X66" s="61" t="n"/>
+      <c r="X66" s="62" t="n"/>
       <c r="Y66" s="22" t="n"/>
       <c r="Z66" s="22" t="n"/>
-      <c r="AA66" s="62" t="n"/>
+      <c r="AA66" s="63" t="n"/>
       <c r="AB66" s="51" t="n"/>
       <c r="AC66" s="51" t="n"/>
       <c r="AD66" s="51" t="n"/>
       <c r="AE66" s="51" t="n"/>
       <c r="AF66" s="51" t="n"/>
       <c r="AG66" s="51" t="n"/>
-      <c r="AH66" s="62" t="n"/>
+      <c r="AH66" s="63" t="n"/>
       <c r="AI66" s="22" t="n"/>
       <c r="AJ66" s="23" t="n"/>
       <c r="AK66" s="22" t="n"/>
       <c r="AL66" s="22" t="n"/>
-      <c r="AM66" s="62" t="n"/>
+      <c r="AM66" s="63" t="n"/>
+      <c r="AS66" s="61" t="n"/>
+      <c r="BE66" s="61" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="36">
@@ -17410,7 +19343,7 @@
         <f>IFERROR(C67-B67,"")</f>
         <v/>
       </c>
-      <c r="E67" s="63">
+      <c r="E67" s="64">
         <f>IFERROR(IF(B67=0,"—",IF(D67&gt;=0,"✓","✗")),"")</f>
         <v/>
       </c>
@@ -17421,7 +19354,7 @@
       <c r="J67" s="23" t="n"/>
       <c r="K67" s="22" t="n"/>
       <c r="L67" s="24" t="n"/>
-      <c r="M67" s="60" t="n"/>
+      <c r="M67" s="61" t="n"/>
       <c r="N67" s="22" t="n"/>
       <c r="O67" s="22" t="n"/>
       <c r="P67" s="22" t="n"/>
@@ -17432,28 +19365,30 @@
       <c r="U67" s="24" t="n"/>
       <c r="V67" s="23" t="n"/>
       <c r="W67" s="22" t="n"/>
-      <c r="X67" s="61" t="n"/>
+      <c r="X67" s="62" t="n"/>
       <c r="Y67" s="22" t="n"/>
       <c r="Z67" s="22" t="n"/>
-      <c r="AA67" s="62" t="n"/>
+      <c r="AA67" s="63" t="n"/>
       <c r="AB67" s="51" t="n"/>
       <c r="AC67" s="51" t="n"/>
       <c r="AD67" s="51" t="n"/>
       <c r="AE67" s="51" t="n"/>
       <c r="AF67" s="51" t="n"/>
       <c r="AG67" s="51" t="n"/>
-      <c r="AH67" s="62" t="n"/>
+      <c r="AH67" s="63" t="n"/>
       <c r="AI67" s="22" t="n"/>
       <c r="AJ67" s="23" t="n"/>
       <c r="AK67" s="22" t="n"/>
       <c r="AL67" s="22" t="n"/>
-      <c r="AM67" s="62" t="n"/>
+      <c r="AM67" s="63" t="n"/>
+      <c r="AS67" s="61" t="n"/>
+      <c r="BE67" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="A1:AM1"/>
+    <mergeCell ref="A2:BE2"/>
     <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A1:BE1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B4:B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -17533,16 +19468,16 @@
         <f>PROJECT_Name</f>
         <v/>
       </c>
-      <c r="E1" s="64" t="n"/>
-      <c r="F1" s="64" t="n"/>
-      <c r="G1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="66" t="n"/>
       <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Project No:</t>
         </is>
       </c>
-      <c r="I1" s="66" t="n"/>
-      <c r="J1" s="66" t="n"/>
+      <c r="I1" s="67" t="n"/>
+      <c r="J1" s="67" t="n"/>
       <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Check One: MS4 / CSS</t>
@@ -17570,7 +19505,7 @@
         <f>PROJECT_DOEEReview</f>
         <v/>
       </c>
-      <c r="U1" s="65" t="n"/>
+      <c r="U1" s="66" t="n"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Project Name:</t>
@@ -17591,7 +19526,7 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="68" t="inlineStr">
         <is>
           <t>Summary Data: 90%/Final Design Phase</t>
         </is>
@@ -17601,18 +19536,18 @@
           <t>Notes:</t>
         </is>
       </c>
-      <c r="W2" s="68">
+      <c r="W2" s="69">
         <f>B2</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="I3" s="69" t="inlineStr">
+      <c r="I3" s="70" t="inlineStr">
         <is>
           <t>Regulated Retention Volume (1.2"):</t>
         </is>
       </c>
-      <c r="J3" s="70">
+      <c r="J3" s="71">
         <f>J45</f>
         <v/>
       </c>
@@ -17621,7 +19556,7 @@
           <t>CF</t>
         </is>
       </c>
-      <c r="L3" s="71" t="inlineStr">
+      <c r="L3" s="72" t="inlineStr">
         <is>
           <t>Blocks in the worksheet that are not shaded are data entry fields for the designer.</t>
         </is>
@@ -17640,21 +19575,21 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="B4" s="69" t="inlineStr">
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>Disturbance Area (ac.):</t>
         </is>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="73">
         <f>E45/43560</f>
         <v/>
       </c>
-      <c r="I4" s="69" t="inlineStr">
+      <c r="I4" s="70" t="inlineStr">
         <is>
           <t>Volume Retained:</t>
         </is>
       </c>
-      <c r="J4" s="70">
+      <c r="J4" s="71">
         <f>AL45</f>
         <v/>
       </c>
@@ -17663,7 +19598,7 @@
           <t>CF</t>
         </is>
       </c>
-      <c r="L4" s="71" t="inlineStr">
+      <c r="L4" s="72" t="inlineStr">
         <is>
           <t>All shaded blocks are computations internal to the worksheet and should not be edited.</t>
         </is>
@@ -17690,21 +19625,21 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="69" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>No. of Drainage Areas:</t>
         </is>
       </c>
-      <c r="E5" s="73">
+      <c r="E5" s="74">
         <f>COUNTA(A12:A44)</f>
         <v/>
       </c>
-      <c r="I5" s="69" t="inlineStr">
+      <c r="I5" s="70" t="inlineStr">
         <is>
           <t>Difference:</t>
         </is>
       </c>
-      <c r="J5" s="70">
+      <c r="J5" s="71">
         <f>J4-J3</f>
         <v/>
       </c>
@@ -17749,7 +19684,7 @@
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
-      <c r="K7" s="74" t="n"/>
+      <c r="K7" s="75" t="n"/>
       <c r="L7" s="1" t="inlineStr">
         <is>
           <t>Step 2:  Consider Infiltration</t>
@@ -17758,7 +19693,7 @@
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
       <c r="O7" s="6" t="n"/>
-      <c r="P7" s="74" t="n"/>
+      <c r="P7" s="75" t="n"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
           <t>Step 3:  Evaluate Existing Infrastructure Constraints</t>
@@ -17768,7 +19703,7 @@
       <c r="S7" s="6" t="n"/>
       <c r="T7" s="6" t="n"/>
       <c r="U7" s="6" t="n"/>
-      <c r="V7" s="74" t="n"/>
+      <c r="V7" s="75" t="n"/>
       <c r="W7" s="1" t="inlineStr">
         <is>
           <t>Step 4:  Identify Land Conversion and BMP Placement Opportunities</t>
@@ -17778,7 +19713,7 @@
       <c r="Y7" s="6" t="n"/>
       <c r="Z7" s="6" t="n"/>
       <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="74" t="n"/>
+      <c r="AB7" s="75" t="n"/>
       <c r="AC7" s="1" t="inlineStr">
         <is>
           <t>Step 5: Size BMPs and Compute Achieved Retention Volumes</t>
@@ -17793,476 +19728,476 @@
       <c r="AJ7" s="6" t="n"/>
       <c r="AK7" s="6" t="n"/>
       <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="74" t="n"/>
+      <c r="AM7" s="75" t="n"/>
     </row>
     <row r="8" ht="102.75" customHeight="1">
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>Update from 65% based on refined or revised design: 
 Number and list each drainage area within the project limits of disturbance (LOD). Provide the drainage area square footage that contributes runoff in the LOD and outside the LOD. The SWRv is calculated for each drainage area. Provide corresponding drainage area identifications on the SWMP.</t>
         </is>
       </c>
-      <c r="K8" s="60" t="n"/>
-      <c r="L8" s="75" t="inlineStr">
+      <c r="K8" s="61" t="n"/>
+      <c r="L8" s="76" t="inlineStr">
         <is>
           <t>Record the water table, bedrock concerns, infiltration rate, and hotspot concerns within the LOD for each drainage area.</t>
         </is>
       </c>
-      <c r="P8" s="60" t="n"/>
-      <c r="Q8" s="75" t="inlineStr">
+      <c r="P8" s="61" t="n"/>
+      <c r="Q8" s="76" t="inlineStr">
         <is>
           <t>On the SWMP, depict utility locations and conveyance infrastructure to confirm/adjust opportunities for land conversions and BMPs. Delineate areas of potential conflict, and areas without conflict, including areas where minimum depths for BMPs can not be met.  Delineate trees (size, species, condition) and tree protection.</t>
         </is>
       </c>
-      <c r="V8" s="60" t="n"/>
-      <c r="W8" s="75" t="inlineStr">
+      <c r="V8" s="61" t="n"/>
+      <c r="W8" s="76" t="inlineStr">
         <is>
           <t>For land conversion and BMP opportunities already defined at 30%, and for new opportunities added, provide the areas below.  Land Conversion and BMP surface areas within the LOD must be reflected in the SWRv computation; update those columns as necessary. Additional allowable BMPs such as impervious surface disconnection, swales, and infiltration should also be considered and described in the narrative. Describe the reason for eliminated Land Conversion/BMP locations.</t>
         </is>
       </c>
-      <c r="AB8" s="60" t="n"/>
-      <c r="AC8" s="75" t="inlineStr">
+      <c r="AB8" s="61" t="n"/>
+      <c r="AC8" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide the contributing drainage area to the BMP locations. The ceiling stormwater runoff volume reaching the BMPs is calculated. </t>
         </is>
       </c>
-      <c r="AG8" s="75" t="inlineStr">
+      <c r="AG8" s="76" t="inlineStr">
         <is>
           <t>Calculate and sum the total maximum possible BMP storage volumes. Total the number of proposed trees meeting the required soil volume to be considered for stormwater retention volume.  Total the maximum retention volume capacity of all facilities and compare to the required regulated volume. If a deficit exists, review BMP placements/sizes to determine if additional volume can be captured.</t>
         </is>
       </c>
-      <c r="AM8" s="60" t="n"/>
+      <c r="AM8" s="61" t="n"/>
     </row>
     <row r="9" ht="42.6" customHeight="1">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>Drainage Area
 ID</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Drainage Area </t>
         </is>
       </c>
-      <c r="J9" s="76" t="inlineStr">
+      <c r="J9" s="77" t="inlineStr">
         <is>
           <t>SWRv</t>
         </is>
       </c>
-      <c r="K9" s="60" t="n"/>
-      <c r="L9" s="76" t="inlineStr">
+      <c r="K9" s="61" t="n"/>
+      <c r="L9" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve"> Hydrologic Soil Group</t>
         </is>
       </c>
-      <c r="M9" s="76" t="inlineStr">
+      <c r="M9" s="77" t="inlineStr">
         <is>
           <t>Water Table OK?</t>
         </is>
       </c>
-      <c r="N9" s="76" t="inlineStr">
+      <c r="N9" s="77" t="inlineStr">
         <is>
           <t>Bedrock Elevation OK?</t>
         </is>
       </c>
-      <c r="O9" s="76" t="inlineStr">
+      <c r="O9" s="77" t="inlineStr">
         <is>
           <t>Infiltration Rate</t>
         </is>
       </c>
-      <c r="P9" s="77" t="inlineStr">
+      <c r="P9" s="78" t="inlineStr">
         <is>
           <t>Hotspot Concern Found?</t>
         </is>
       </c>
-      <c r="Q9" s="76" t="inlineStr">
+      <c r="Q9" s="77" t="inlineStr">
         <is>
           <t>Preservation of Small, Large, and/or Special/Heritage Trees which are in fair or better condition</t>
         </is>
       </c>
-      <c r="V9" s="60" t="n"/>
-      <c r="W9" s="76" t="inlineStr">
+      <c r="V9" s="61" t="n"/>
+      <c r="W9" s="77" t="inlineStr">
         <is>
           <t>Land Conversion Area</t>
         </is>
       </c>
-      <c r="Y9" s="76" t="inlineStr">
+      <c r="Y9" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Bioretention Opportunity Areas </t>
         </is>
       </c>
-      <c r="AA9" s="76" t="inlineStr">
+      <c r="AA9" s="77" t="inlineStr">
         <is>
           <t>Permeable Pavement Opportunity Areas</t>
         </is>
       </c>
-      <c r="AB9" s="60" t="n"/>
-      <c r="AC9" s="76" t="inlineStr">
+      <c r="AB9" s="61" t="n"/>
+      <c r="AC9" s="77" t="inlineStr">
         <is>
           <t>Total BMP Contributing Drainage Area</t>
         </is>
       </c>
-      <c r="AE9" s="76" t="inlineStr">
+      <c r="AE9" s="77" t="inlineStr">
         <is>
           <t>1.7 inch (ceiling) stormwater runoff reaching BMPs</t>
         </is>
       </c>
-      <c r="AG9" s="76" t="inlineStr">
+      <c r="AG9" s="77" t="inlineStr">
         <is>
           <t>Max. Storage Volume of Bioretention Based on Size (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AH9" s="76" t="inlineStr">
+      <c r="AH9" s="77" t="inlineStr">
         <is>
           <t>Max. Storage Volume of Permeable Pavement. Based on Size (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AI9" s="76" t="inlineStr">
+      <c r="AI9" s="77" t="inlineStr">
         <is>
           <t>Max. "Other" Storage Volume - (Total in DA - See separate sizing computations)</t>
         </is>
       </c>
-      <c r="AJ9" s="76" t="inlineStr">
+      <c r="AJ9" s="77" t="inlineStr">
         <is>
           <t>No. of proposed small trees meeting soil volume requirement</t>
         </is>
       </c>
-      <c r="AK9" s="76" t="inlineStr">
+      <c r="AK9" s="77" t="inlineStr">
         <is>
           <t>No. of proposed large trees meeting soil volume requirement</t>
         </is>
       </c>
-      <c r="AL9" s="76" t="inlineStr">
+      <c r="AL9" s="77" t="inlineStr">
         <is>
           <t>Total Sv Practice -Maximum Retention Volume Achievable (BMPs and Trees)</t>
         </is>
       </c>
-      <c r="AM9" s="77" t="inlineStr">
+      <c r="AM9" s="78" t="inlineStr">
         <is>
           <t>Overage / (Deficit) Volume (as compared to SWRv)</t>
         </is>
       </c>
-      <c r="AP9" s="76" t="inlineStr">
+      <c r="AP9" s="77" t="inlineStr">
         <is>
           <t>Runoff Coefficient</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48.75" customHeight="1">
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Impervious 
 within LOD</t>
         </is>
       </c>
-      <c r="C10" s="76" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>Compacted    within LOD</t>
         </is>
       </c>
-      <c r="D10" s="76" t="inlineStr">
+      <c r="D10" s="77" t="inlineStr">
         <is>
           <t>Natural 
 within LOD</t>
         </is>
       </c>
-      <c r="E10" s="76" t="inlineStr">
+      <c r="E10" s="77" t="inlineStr">
         <is>
           <t>Total within LOD</t>
         </is>
       </c>
-      <c r="F10" s="76" t="inlineStr">
+      <c r="F10" s="77" t="inlineStr">
         <is>
           <t>Impervious outside LOD</t>
         </is>
       </c>
-      <c r="G10" s="76" t="inlineStr">
+      <c r="G10" s="77" t="inlineStr">
         <is>
           <t>Compacted outside LOD</t>
         </is>
       </c>
-      <c r="H10" s="76" t="inlineStr">
+      <c r="H10" s="77" t="inlineStr">
         <is>
           <t>Natural outside LOD</t>
         </is>
       </c>
-      <c r="I10" s="76" t="inlineStr">
+      <c r="I10" s="77" t="inlineStr">
         <is>
           <t>Total outside LOD</t>
         </is>
       </c>
-      <c r="J10" s="76" t="inlineStr">
+      <c r="J10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="K10" s="77" t="inlineStr">
+      <c r="K10" s="78" t="inlineStr">
         <is>
           <t>Outside LOD</t>
         </is>
       </c>
-      <c r="P10" s="60" t="n"/>
-      <c r="V10" s="60" t="n"/>
-      <c r="W10" s="76" t="inlineStr">
+      <c r="P10" s="61" t="n"/>
+      <c r="V10" s="61" t="n"/>
+      <c r="W10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="X10" s="76" t="inlineStr">
+      <c r="X10" s="77" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="Y10" s="76" t="inlineStr">
+      <c r="Y10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="Z10" s="76" t="inlineStr">
+      <c r="Z10" s="77" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AA10" s="76" t="inlineStr">
+      <c r="AA10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AB10" s="77" t="inlineStr">
+      <c r="AB10" s="78" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AC10" s="76" t="inlineStr">
+      <c r="AC10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AD10" s="76" t="inlineStr">
+      <c r="AD10" s="77" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AE10" s="76" t="inlineStr">
+      <c r="AE10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AF10" s="76" t="inlineStr">
+      <c r="AF10" s="77" t="inlineStr">
         <is>
           <t>Adjacent to LOD</t>
         </is>
       </c>
-      <c r="AM10" s="60" t="n"/>
-      <c r="AP10" s="76" t="inlineStr">
+      <c r="AM10" s="61" t="n"/>
+      <c r="AP10" s="77" t="inlineStr">
         <is>
           <t>Within LOD</t>
         </is>
       </c>
-      <c r="AQ10" s="76" t="inlineStr">
+      <c r="AQ10" s="77" t="inlineStr">
         <is>
           <t>Outside LOD</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32.45" customHeight="1">
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="C11" s="76" t="inlineStr">
+      <c r="C11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D11" s="76" t="inlineStr">
+      <c r="D11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E11" s="76" t="inlineStr">
+      <c r="E11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="F11" s="76" t="inlineStr">
+      <c r="F11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="G11" s="76" t="inlineStr">
+      <c r="G11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H11" s="76" t="inlineStr">
+      <c r="H11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="I11" s="76" t="inlineStr">
+      <c r="I11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="J11" s="76" t="inlineStr">
+      <c r="J11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="K11" s="77" t="inlineStr">
+      <c r="K11" s="78" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="L11" s="76" t="inlineStr">
+      <c r="L11" s="77" t="inlineStr">
         <is>
           <t>A, B, C, D, or Urban Land</t>
         </is>
       </c>
-      <c r="M11" s="76" t="inlineStr">
+      <c r="M11" s="77" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="N11" s="76" t="inlineStr">
+      <c r="N11" s="77" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="O11" s="76" t="inlineStr">
+      <c r="O11" s="77" t="inlineStr">
         <is>
           <t>in-hr</t>
         </is>
       </c>
-      <c r="P11" s="77" t="inlineStr">
+      <c r="P11" s="78" t="inlineStr">
         <is>
           <t>Y/N</t>
         </is>
       </c>
-      <c r="Q11" s="76" t="inlineStr">
+      <c r="Q11" s="77" t="inlineStr">
         <is>
           <t># of Small Trees</t>
         </is>
       </c>
-      <c r="R11" s="76" t="inlineStr">
+      <c r="R11" s="77" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="S11" s="76" t="inlineStr">
+      <c r="S11" s="77" t="inlineStr">
         <is>
           <t># of Large Trees</t>
         </is>
       </c>
-      <c r="T11" s="76" t="inlineStr">
+      <c r="T11" s="77" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="U11" s="76" t="inlineStr">
+      <c r="U11" s="77" t="inlineStr">
         <is>
           <t># of Special/ Heritage Trees</t>
         </is>
       </c>
-      <c r="V11" s="77" t="inlineStr">
+      <c r="V11" s="78" t="inlineStr">
         <is>
           <t>Tree Volume Credit (CF)</t>
         </is>
       </c>
-      <c r="W11" s="76" t="inlineStr">
+      <c r="W11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="X11" s="76" t="inlineStr">
+      <c r="X11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="Y11" s="76" t="inlineStr">
+      <c r="Y11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="Z11" s="76" t="inlineStr">
+      <c r="Z11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AA11" s="76" t="inlineStr">
+      <c r="AA11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AB11" s="77" t="inlineStr">
+      <c r="AB11" s="78" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AC11" s="76" t="inlineStr">
+      <c r="AC11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AD11" s="76" t="inlineStr">
+      <c r="AD11" s="77" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="AE11" s="76" t="inlineStr">
+      <c r="AE11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AF11" s="76" t="inlineStr">
+      <c r="AF11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AG11" s="76" t="inlineStr">
+      <c r="AG11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AH11" s="76" t="inlineStr">
+      <c r="AH11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AI11" s="76" t="inlineStr">
+      <c r="AI11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AJ11" s="76" t="inlineStr">
+      <c r="AJ11" s="77" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="AK11" s="76" t="inlineStr">
+      <c r="AK11" s="77" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="AL11" s="76" t="inlineStr">
+      <c r="AL11" s="77" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AM11" s="77" t="inlineStr">
+      <c r="AM11" s="78" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="AP11" s="76" t="inlineStr">
+      <c r="AP11" s="77" t="inlineStr">
         <is>
           <t>(unitless)</t>
         </is>
       </c>
-      <c r="AQ11" s="76" t="inlineStr">
+      <c r="AQ11" s="77" t="inlineStr">
         <is>
           <t>(unitless)</t>
         </is>
@@ -18336,7 +20271,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q12" s="78">
+      <c r="Q12" s="79">
         <f>IF(A12="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
@@ -18344,7 +20279,7 @@
         <f>IF(A12="","",Q12*10)</f>
         <v/>
       </c>
-      <c r="S12" s="78">
+      <c r="S12" s="79">
         <f>IF(A12="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
@@ -18352,7 +20287,7 @@
         <f>IF(A12="","",S12*20)</f>
         <v/>
       </c>
-      <c r="U12" s="78">
+      <c r="U12" s="79">
         <f>IF(A12="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A12)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
@@ -18371,7 +20306,7 @@
         <f>IF(A12="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB12" s="79" t="n"/>
+      <c r="AB12" s="80" t="n"/>
       <c r="AC12" s="21">
         <f>IF(A12="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A12))</f>
         <v/>
@@ -18400,11 +20335,11 @@
         <f>IF(A12="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A12,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ12" s="78">
+      <c r="AJ12" s="79">
         <f>IF(A12="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
-      <c r="AK12" s="78">
+      <c r="AK12" s="79">
         <f>IF(A12="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A12))</f>
         <v/>
       </c>
@@ -18493,7 +20428,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q13" s="78">
+      <c r="Q13" s="79">
         <f>IF(A13="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
@@ -18501,7 +20436,7 @@
         <f>IF(A13="","",Q13*10)</f>
         <v/>
       </c>
-      <c r="S13" s="78">
+      <c r="S13" s="79">
         <f>IF(A13="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
@@ -18509,7 +20444,7 @@
         <f>IF(A13="","",S13*20)</f>
         <v/>
       </c>
-      <c r="U13" s="78">
+      <c r="U13" s="79">
         <f>IF(A13="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A13)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
@@ -18528,7 +20463,7 @@
         <f>IF(A13="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB13" s="79" t="n"/>
+      <c r="AB13" s="80" t="n"/>
       <c r="AC13" s="21">
         <f>IF(A13="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A13))</f>
         <v/>
@@ -18557,11 +20492,11 @@
         <f>IF(A13="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A13,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ13" s="78">
+      <c r="AJ13" s="79">
         <f>IF(A13="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
-      <c r="AK13" s="78">
+      <c r="AK13" s="79">
         <f>IF(A13="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A13))</f>
         <v/>
       </c>
@@ -18650,7 +20585,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q14" s="78">
+      <c r="Q14" s="79">
         <f>IF(A14="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
@@ -18658,7 +20593,7 @@
         <f>IF(A14="","",Q14*10)</f>
         <v/>
       </c>
-      <c r="S14" s="78">
+      <c r="S14" s="79">
         <f>IF(A14="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
@@ -18666,7 +20601,7 @@
         <f>IF(A14="","",S14*20)</f>
         <v/>
       </c>
-      <c r="U14" s="78">
+      <c r="U14" s="79">
         <f>IF(A14="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A14)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
@@ -18685,7 +20620,7 @@
         <f>IF(A14="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB14" s="79" t="n"/>
+      <c r="AB14" s="80" t="n"/>
       <c r="AC14" s="21">
         <f>IF(A14="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A14))</f>
         <v/>
@@ -18714,11 +20649,11 @@
         <f>IF(A14="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A14,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ14" s="78">
+      <c r="AJ14" s="79">
         <f>IF(A14="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
-      <c r="AK14" s="78">
+      <c r="AK14" s="79">
         <f>IF(A14="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A14))</f>
         <v/>
       </c>
@@ -18807,7 +20742,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q15" s="78">
+      <c r="Q15" s="79">
         <f>IF(A15="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
@@ -18815,7 +20750,7 @@
         <f>IF(A15="","",Q15*10)</f>
         <v/>
       </c>
-      <c r="S15" s="78">
+      <c r="S15" s="79">
         <f>IF(A15="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
@@ -18823,7 +20758,7 @@
         <f>IF(A15="","",S15*20)</f>
         <v/>
       </c>
-      <c r="U15" s="78">
+      <c r="U15" s="79">
         <f>IF(A15="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A15)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
@@ -18842,7 +20777,7 @@
         <f>IF(A15="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB15" s="79" t="n"/>
+      <c r="AB15" s="80" t="n"/>
       <c r="AC15" s="21">
         <f>IF(A15="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A15))</f>
         <v/>
@@ -18871,11 +20806,11 @@
         <f>IF(A15="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A15,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ15" s="78">
+      <c r="AJ15" s="79">
         <f>IF(A15="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
-      <c r="AK15" s="78">
+      <c r="AK15" s="79">
         <f>IF(A15="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A15))</f>
         <v/>
       </c>
@@ -18964,7 +20899,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q16" s="78">
+      <c r="Q16" s="79">
         <f>IF(A16="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
@@ -18972,7 +20907,7 @@
         <f>IF(A16="","",Q16*10)</f>
         <v/>
       </c>
-      <c r="S16" s="78">
+      <c r="S16" s="79">
         <f>IF(A16="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
@@ -18980,7 +20915,7 @@
         <f>IF(A16="","",S16*20)</f>
         <v/>
       </c>
-      <c r="U16" s="78">
+      <c r="U16" s="79">
         <f>IF(A16="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A16)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
@@ -18999,7 +20934,7 @@
         <f>IF(A16="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB16" s="79" t="n"/>
+      <c r="AB16" s="80" t="n"/>
       <c r="AC16" s="21">
         <f>IF(A16="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A16))</f>
         <v/>
@@ -19028,11 +20963,11 @@
         <f>IF(A16="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A16,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ16" s="78">
+      <c r="AJ16" s="79">
         <f>IF(A16="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
-      <c r="AK16" s="78">
+      <c r="AK16" s="79">
         <f>IF(A16="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A16))</f>
         <v/>
       </c>
@@ -19121,7 +21056,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q17" s="78">
+      <c r="Q17" s="79">
         <f>IF(A17="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
@@ -19129,7 +21064,7 @@
         <f>IF(A17="","",Q17*10)</f>
         <v/>
       </c>
-      <c r="S17" s="78">
+      <c r="S17" s="79">
         <f>IF(A17="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
@@ -19137,7 +21072,7 @@
         <f>IF(A17="","",S17*20)</f>
         <v/>
       </c>
-      <c r="U17" s="78">
+      <c r="U17" s="79">
         <f>IF(A17="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A17)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
@@ -19156,7 +21091,7 @@
         <f>IF(A17="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB17" s="79" t="n"/>
+      <c r="AB17" s="80" t="n"/>
       <c r="AC17" s="21">
         <f>IF(A17="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A17))</f>
         <v/>
@@ -19185,11 +21120,11 @@
         <f>IF(A17="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A17,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ17" s="78">
+      <c r="AJ17" s="79">
         <f>IF(A17="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
-      <c r="AK17" s="78">
+      <c r="AK17" s="79">
         <f>IF(A17="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A17))</f>
         <v/>
       </c>
@@ -19278,7 +21213,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q18" s="78">
+      <c r="Q18" s="79">
         <f>IF(A18="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
@@ -19286,7 +21221,7 @@
         <f>IF(A18="","",Q18*10)</f>
         <v/>
       </c>
-      <c r="S18" s="78">
+      <c r="S18" s="79">
         <f>IF(A18="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
@@ -19294,7 +21229,7 @@
         <f>IF(A18="","",S18*20)</f>
         <v/>
       </c>
-      <c r="U18" s="78">
+      <c r="U18" s="79">
         <f>IF(A18="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A18)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
@@ -19313,7 +21248,7 @@
         <f>IF(A18="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB18" s="79" t="n"/>
+      <c r="AB18" s="80" t="n"/>
       <c r="AC18" s="21">
         <f>IF(A18="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A18))</f>
         <v/>
@@ -19342,11 +21277,11 @@
         <f>IF(A18="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A18,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ18" s="78">
+      <c r="AJ18" s="79">
         <f>IF(A18="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
-      <c r="AK18" s="78">
+      <c r="AK18" s="79">
         <f>IF(A18="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A18))</f>
         <v/>
       </c>
@@ -19435,7 +21370,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q19" s="78">
+      <c r="Q19" s="79">
         <f>IF(A19="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
@@ -19443,7 +21378,7 @@
         <f>IF(A19="","",Q19*10)</f>
         <v/>
       </c>
-      <c r="S19" s="78">
+      <c r="S19" s="79">
         <f>IF(A19="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
@@ -19451,7 +21386,7 @@
         <f>IF(A19="","",S19*20)</f>
         <v/>
       </c>
-      <c r="U19" s="78">
+      <c r="U19" s="79">
         <f>IF(A19="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A19)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
@@ -19470,7 +21405,7 @@
         <f>IF(A19="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB19" s="79" t="n"/>
+      <c r="AB19" s="80" t="n"/>
       <c r="AC19" s="21">
         <f>IF(A19="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A19))</f>
         <v/>
@@ -19499,11 +21434,11 @@
         <f>IF(A19="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A19,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ19" s="78">
+      <c r="AJ19" s="79">
         <f>IF(A19="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
-      <c r="AK19" s="78">
+      <c r="AK19" s="79">
         <f>IF(A19="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A19))</f>
         <v/>
       </c>
@@ -19592,7 +21527,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q20" s="78">
+      <c r="Q20" s="79">
         <f>IF(A20="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
@@ -19600,7 +21535,7 @@
         <f>IF(A20="","",Q20*10)</f>
         <v/>
       </c>
-      <c r="S20" s="78">
+      <c r="S20" s="79">
         <f>IF(A20="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
@@ -19608,7 +21543,7 @@
         <f>IF(A20="","",S20*20)</f>
         <v/>
       </c>
-      <c r="U20" s="78">
+      <c r="U20" s="79">
         <f>IF(A20="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A20)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
@@ -19627,7 +21562,7 @@
         <f>IF(A20="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB20" s="79" t="n"/>
+      <c r="AB20" s="80" t="n"/>
       <c r="AC20" s="21">
         <f>IF(A20="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A20))</f>
         <v/>
@@ -19656,11 +21591,11 @@
         <f>IF(A20="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A20,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ20" s="78">
+      <c r="AJ20" s="79">
         <f>IF(A20="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
-      <c r="AK20" s="78">
+      <c r="AK20" s="79">
         <f>IF(A20="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A20))</f>
         <v/>
       </c>
@@ -19749,7 +21684,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Q21" s="78">
+      <c r="Q21" s="79">
         <f>IF(A21="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
@@ -19757,7 +21692,7 @@
         <f>IF(A21="","",Q21*10)</f>
         <v/>
       </c>
-      <c r="S21" s="78">
+      <c r="S21" s="79">
         <f>IF(A21="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
@@ -19765,7 +21700,7 @@
         <f>IF(A21="","",S21*20)</f>
         <v/>
       </c>
-      <c r="U21" s="78">
+      <c r="U21" s="79">
         <f>IF(A21="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A21)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
@@ -19784,7 +21719,7 @@
         <f>IF(A21="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB21" s="79" t="n"/>
+      <c r="AB21" s="80" t="n"/>
       <c r="AC21" s="21">
         <f>IF(A21="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A21))</f>
         <v/>
@@ -19813,11 +21748,11 @@
         <f>IF(A21="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A21,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ21" s="78">
+      <c r="AJ21" s="79">
         <f>IF(A21="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
-      <c r="AK21" s="78">
+      <c r="AK21" s="79">
         <f>IF(A21="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A21))</f>
         <v/>
       </c>
@@ -19894,7 +21829,7 @@
         <v/>
       </c>
       <c r="P22" s="46" t="n"/>
-      <c r="Q22" s="78">
+      <c r="Q22" s="79">
         <f>IF(A22="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
@@ -19902,7 +21837,7 @@
         <f>IF(A22="","",Q22*10)</f>
         <v/>
       </c>
-      <c r="S22" s="78">
+      <c r="S22" s="79">
         <f>IF(A22="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
@@ -19910,7 +21845,7 @@
         <f>IF(A22="","",S22*20)</f>
         <v/>
       </c>
-      <c r="U22" s="78">
+      <c r="U22" s="79">
         <f>IF(A22="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A22)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
@@ -19929,7 +21864,7 @@
         <f>IF(A22="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB22" s="79" t="n"/>
+      <c r="AB22" s="80" t="n"/>
       <c r="AC22" s="21">
         <f>IF(A22="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A22))</f>
         <v/>
@@ -19958,11 +21893,11 @@
         <f>IF(A22="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A22,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ22" s="78">
+      <c r="AJ22" s="79">
         <f>IF(A22="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
-      <c r="AK22" s="78">
+      <c r="AK22" s="79">
         <f>IF(A22="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A22))</f>
         <v/>
       </c>
@@ -20039,7 +21974,7 @@
         <v/>
       </c>
       <c r="P23" s="46" t="n"/>
-      <c r="Q23" s="78">
+      <c r="Q23" s="79">
         <f>IF(A23="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
@@ -20047,7 +21982,7 @@
         <f>IF(A23="","",Q23*10)</f>
         <v/>
       </c>
-      <c r="S23" s="78">
+      <c r="S23" s="79">
         <f>IF(A23="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
@@ -20055,7 +21990,7 @@
         <f>IF(A23="","",S23*20)</f>
         <v/>
       </c>
-      <c r="U23" s="78">
+      <c r="U23" s="79">
         <f>IF(A23="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A23)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
@@ -20074,7 +22009,7 @@
         <f>IF(A23="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB23" s="79" t="n"/>
+      <c r="AB23" s="80" t="n"/>
       <c r="AC23" s="21">
         <f>IF(A23="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A23))</f>
         <v/>
@@ -20103,11 +22038,11 @@
         <f>IF(A23="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A23,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ23" s="78">
+      <c r="AJ23" s="79">
         <f>IF(A23="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
-      <c r="AK23" s="78">
+      <c r="AK23" s="79">
         <f>IF(A23="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A23))</f>
         <v/>
       </c>
@@ -20184,7 +22119,7 @@
         <v/>
       </c>
       <c r="P24" s="46" t="n"/>
-      <c r="Q24" s="78">
+      <c r="Q24" s="79">
         <f>IF(A24="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
@@ -20192,7 +22127,7 @@
         <f>IF(A24="","",Q24*10)</f>
         <v/>
       </c>
-      <c r="S24" s="78">
+      <c r="S24" s="79">
         <f>IF(A24="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
@@ -20200,7 +22135,7 @@
         <f>IF(A24="","",S24*20)</f>
         <v/>
       </c>
-      <c r="U24" s="78">
+      <c r="U24" s="79">
         <f>IF(A24="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A24)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
@@ -20219,7 +22154,7 @@
         <f>IF(A24="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB24" s="79" t="n"/>
+      <c r="AB24" s="80" t="n"/>
       <c r="AC24" s="21">
         <f>IF(A24="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A24))</f>
         <v/>
@@ -20248,11 +22183,11 @@
         <f>IF(A24="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A24,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ24" s="78">
+      <c r="AJ24" s="79">
         <f>IF(A24="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
-      <c r="AK24" s="78">
+      <c r="AK24" s="79">
         <f>IF(A24="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A24))</f>
         <v/>
       </c>
@@ -20329,7 +22264,7 @@
         <v/>
       </c>
       <c r="P25" s="46" t="n"/>
-      <c r="Q25" s="78">
+      <c r="Q25" s="79">
         <f>IF(A25="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
@@ -20337,7 +22272,7 @@
         <f>IF(A25="","",Q25*10)</f>
         <v/>
       </c>
-      <c r="S25" s="78">
+      <c r="S25" s="79">
         <f>IF(A25="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
@@ -20345,7 +22280,7 @@
         <f>IF(A25="","",S25*20)</f>
         <v/>
       </c>
-      <c r="U25" s="78">
+      <c r="U25" s="79">
         <f>IF(A25="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A25)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
@@ -20364,7 +22299,7 @@
         <f>IF(A25="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB25" s="79" t="n"/>
+      <c r="AB25" s="80" t="n"/>
       <c r="AC25" s="21">
         <f>IF(A25="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A25))</f>
         <v/>
@@ -20393,11 +22328,11 @@
         <f>IF(A25="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A25,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ25" s="78">
+      <c r="AJ25" s="79">
         <f>IF(A25="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
-      <c r="AK25" s="78">
+      <c r="AK25" s="79">
         <f>IF(A25="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A25))</f>
         <v/>
       </c>
@@ -20474,7 +22409,7 @@
         <v/>
       </c>
       <c r="P26" s="46" t="n"/>
-      <c r="Q26" s="78">
+      <c r="Q26" s="79">
         <f>IF(A26="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
@@ -20482,7 +22417,7 @@
         <f>IF(A26="","",Q26*10)</f>
         <v/>
       </c>
-      <c r="S26" s="78">
+      <c r="S26" s="79">
         <f>IF(A26="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
@@ -20490,7 +22425,7 @@
         <f>IF(A26="","",S26*20)</f>
         <v/>
       </c>
-      <c r="U26" s="78">
+      <c r="U26" s="79">
         <f>IF(A26="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A26)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
@@ -20509,7 +22444,7 @@
         <f>IF(A26="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB26" s="79" t="n"/>
+      <c r="AB26" s="80" t="n"/>
       <c r="AC26" s="21">
         <f>IF(A26="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A26))</f>
         <v/>
@@ -20538,11 +22473,11 @@
         <f>IF(A26="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A26,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ26" s="78">
+      <c r="AJ26" s="79">
         <f>IF(A26="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
-      <c r="AK26" s="78">
+      <c r="AK26" s="79">
         <f>IF(A26="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A26))</f>
         <v/>
       </c>
@@ -20619,7 +22554,7 @@
         <v/>
       </c>
       <c r="P27" s="46" t="n"/>
-      <c r="Q27" s="78">
+      <c r="Q27" s="79">
         <f>IF(A27="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
@@ -20627,7 +22562,7 @@
         <f>IF(A27="","",Q27*10)</f>
         <v/>
       </c>
-      <c r="S27" s="78">
+      <c r="S27" s="79">
         <f>IF(A27="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
@@ -20635,7 +22570,7 @@
         <f>IF(A27="","",S27*20)</f>
         <v/>
       </c>
-      <c r="U27" s="78">
+      <c r="U27" s="79">
         <f>IF(A27="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A27)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
@@ -20654,7 +22589,7 @@
         <f>IF(A27="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB27" s="79" t="n"/>
+      <c r="AB27" s="80" t="n"/>
       <c r="AC27" s="21">
         <f>IF(A27="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A27))</f>
         <v/>
@@ -20683,11 +22618,11 @@
         <f>IF(A27="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A27,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ27" s="78">
+      <c r="AJ27" s="79">
         <f>IF(A27="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
-      <c r="AK27" s="78">
+      <c r="AK27" s="79">
         <f>IF(A27="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A27))</f>
         <v/>
       </c>
@@ -20764,7 +22699,7 @@
         <v/>
       </c>
       <c r="P28" s="46" t="n"/>
-      <c r="Q28" s="78">
+      <c r="Q28" s="79">
         <f>IF(A28="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
@@ -20772,7 +22707,7 @@
         <f>IF(A28="","",Q28*10)</f>
         <v/>
       </c>
-      <c r="S28" s="78">
+      <c r="S28" s="79">
         <f>IF(A28="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
@@ -20780,7 +22715,7 @@
         <f>IF(A28="","",S28*20)</f>
         <v/>
       </c>
-      <c r="U28" s="78">
+      <c r="U28" s="79">
         <f>IF(A28="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A28)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
@@ -20799,7 +22734,7 @@
         <f>IF(A28="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB28" s="79" t="n"/>
+      <c r="AB28" s="80" t="n"/>
       <c r="AC28" s="21">
         <f>IF(A28="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A28))</f>
         <v/>
@@ -20828,11 +22763,11 @@
         <f>IF(A28="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A28,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ28" s="78">
+      <c r="AJ28" s="79">
         <f>IF(A28="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
-      <c r="AK28" s="78">
+      <c r="AK28" s="79">
         <f>IF(A28="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A28))</f>
         <v/>
       </c>
@@ -20909,7 +22844,7 @@
         <v/>
       </c>
       <c r="P29" s="46" t="n"/>
-      <c r="Q29" s="78">
+      <c r="Q29" s="79">
         <f>IF(A29="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
@@ -20917,7 +22852,7 @@
         <f>IF(A29="","",Q29*10)</f>
         <v/>
       </c>
-      <c r="S29" s="78">
+      <c r="S29" s="79">
         <f>IF(A29="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
@@ -20925,7 +22860,7 @@
         <f>IF(A29="","",S29*20)</f>
         <v/>
       </c>
-      <c r="U29" s="78">
+      <c r="U29" s="79">
         <f>IF(A29="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A29)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
@@ -20944,7 +22879,7 @@
         <f>IF(A29="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB29" s="79" t="n"/>
+      <c r="AB29" s="80" t="n"/>
       <c r="AC29" s="21">
         <f>IF(A29="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A29))</f>
         <v/>
@@ -20973,11 +22908,11 @@
         <f>IF(A29="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A29,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ29" s="78">
+      <c r="AJ29" s="79">
         <f>IF(A29="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
-      <c r="AK29" s="78">
+      <c r="AK29" s="79">
         <f>IF(A29="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A29))</f>
         <v/>
       </c>
@@ -21054,7 +22989,7 @@
         <v/>
       </c>
       <c r="P30" s="46" t="n"/>
-      <c r="Q30" s="78">
+      <c r="Q30" s="79">
         <f>IF(A30="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
@@ -21062,7 +22997,7 @@
         <f>IF(A30="","",Q30*10)</f>
         <v/>
       </c>
-      <c r="S30" s="78">
+      <c r="S30" s="79">
         <f>IF(A30="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
@@ -21070,7 +23005,7 @@
         <f>IF(A30="","",S30*20)</f>
         <v/>
       </c>
-      <c r="U30" s="78">
+      <c r="U30" s="79">
         <f>IF(A30="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A30)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
@@ -21089,7 +23024,7 @@
         <f>IF(A30="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB30" s="79" t="n"/>
+      <c r="AB30" s="80" t="n"/>
       <c r="AC30" s="21">
         <f>IF(A30="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A30))</f>
         <v/>
@@ -21118,11 +23053,11 @@
         <f>IF(A30="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A30,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ30" s="78">
+      <c r="AJ30" s="79">
         <f>IF(A30="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
-      <c r="AK30" s="78">
+      <c r="AK30" s="79">
         <f>IF(A30="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A30))</f>
         <v/>
       </c>
@@ -21199,7 +23134,7 @@
         <v/>
       </c>
       <c r="P31" s="46" t="n"/>
-      <c r="Q31" s="78">
+      <c r="Q31" s="79">
         <f>IF(A31="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
@@ -21207,7 +23142,7 @@
         <f>IF(A31="","",Q31*10)</f>
         <v/>
       </c>
-      <c r="S31" s="78">
+      <c r="S31" s="79">
         <f>IF(A31="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
@@ -21215,7 +23150,7 @@
         <f>IF(A31="","",S31*20)</f>
         <v/>
       </c>
-      <c r="U31" s="78">
+      <c r="U31" s="79">
         <f>IF(A31="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A31)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
@@ -21234,7 +23169,7 @@
         <f>IF(A31="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB31" s="79" t="n"/>
+      <c r="AB31" s="80" t="n"/>
       <c r="AC31" s="21">
         <f>IF(A31="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A31))</f>
         <v/>
@@ -21263,11 +23198,11 @@
         <f>IF(A31="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A31,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ31" s="78">
+      <c r="AJ31" s="79">
         <f>IF(A31="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
-      <c r="AK31" s="78">
+      <c r="AK31" s="79">
         <f>IF(A31="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A31))</f>
         <v/>
       </c>
@@ -21344,7 +23279,7 @@
         <v/>
       </c>
       <c r="P32" s="46" t="n"/>
-      <c r="Q32" s="78">
+      <c r="Q32" s="79">
         <f>IF(A32="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
@@ -21352,7 +23287,7 @@
         <f>IF(A32="","",Q32*10)</f>
         <v/>
       </c>
-      <c r="S32" s="78">
+      <c r="S32" s="79">
         <f>IF(A32="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
@@ -21360,7 +23295,7 @@
         <f>IF(A32="","",S32*20)</f>
         <v/>
       </c>
-      <c r="U32" s="78">
+      <c r="U32" s="79">
         <f>IF(A32="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A32)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
@@ -21379,7 +23314,7 @@
         <f>IF(A32="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB32" s="79" t="n"/>
+      <c r="AB32" s="80" t="n"/>
       <c r="AC32" s="21">
         <f>IF(A32="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A32))</f>
         <v/>
@@ -21408,11 +23343,11 @@
         <f>IF(A32="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A32,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ32" s="78">
+      <c r="AJ32" s="79">
         <f>IF(A32="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
-      <c r="AK32" s="78">
+      <c r="AK32" s="79">
         <f>IF(A32="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A32))</f>
         <v/>
       </c>
@@ -21489,7 +23424,7 @@
         <v/>
       </c>
       <c r="P33" s="46" t="n"/>
-      <c r="Q33" s="78">
+      <c r="Q33" s="79">
         <f>IF(A33="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
@@ -21497,7 +23432,7 @@
         <f>IF(A33="","",Q33*10)</f>
         <v/>
       </c>
-      <c r="S33" s="78">
+      <c r="S33" s="79">
         <f>IF(A33="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
@@ -21505,7 +23440,7 @@
         <f>IF(A33="","",S33*20)</f>
         <v/>
       </c>
-      <c r="U33" s="78">
+      <c r="U33" s="79">
         <f>IF(A33="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A33)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
@@ -21524,7 +23459,7 @@
         <f>IF(A33="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB33" s="79" t="n"/>
+      <c r="AB33" s="80" t="n"/>
       <c r="AC33" s="21">
         <f>IF(A33="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A33))</f>
         <v/>
@@ -21553,11 +23488,11 @@
         <f>IF(A33="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A33,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ33" s="78">
+      <c r="AJ33" s="79">
         <f>IF(A33="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
-      <c r="AK33" s="78">
+      <c r="AK33" s="79">
         <f>IF(A33="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A33))</f>
         <v/>
       </c>
@@ -21634,7 +23569,7 @@
         <v/>
       </c>
       <c r="P34" s="46" t="n"/>
-      <c r="Q34" s="78">
+      <c r="Q34" s="79">
         <f>IF(A34="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
@@ -21642,7 +23577,7 @@
         <f>IF(A34="","",Q34*10)</f>
         <v/>
       </c>
-      <c r="S34" s="78">
+      <c r="S34" s="79">
         <f>IF(A34="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
@@ -21650,7 +23585,7 @@
         <f>IF(A34="","",S34*20)</f>
         <v/>
       </c>
-      <c r="U34" s="78">
+      <c r="U34" s="79">
         <f>IF(A34="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A34)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
@@ -21669,7 +23604,7 @@
         <f>IF(A34="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB34" s="79" t="n"/>
+      <c r="AB34" s="80" t="n"/>
       <c r="AC34" s="21">
         <f>IF(A34="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A34))</f>
         <v/>
@@ -21698,11 +23633,11 @@
         <f>IF(A34="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A34,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ34" s="78">
+      <c r="AJ34" s="79">
         <f>IF(A34="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
-      <c r="AK34" s="78">
+      <c r="AK34" s="79">
         <f>IF(A34="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A34))</f>
         <v/>
       </c>
@@ -21779,7 +23714,7 @@
         <v/>
       </c>
       <c r="P35" s="46" t="n"/>
-      <c r="Q35" s="78">
+      <c r="Q35" s="79">
         <f>IF(A35="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
@@ -21787,7 +23722,7 @@
         <f>IF(A35="","",Q35*10)</f>
         <v/>
       </c>
-      <c r="S35" s="78">
+      <c r="S35" s="79">
         <f>IF(A35="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
@@ -21795,7 +23730,7 @@
         <f>IF(A35="","",S35*20)</f>
         <v/>
       </c>
-      <c r="U35" s="78">
+      <c r="U35" s="79">
         <f>IF(A35="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A35)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
@@ -21814,7 +23749,7 @@
         <f>IF(A35="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB35" s="79" t="n"/>
+      <c r="AB35" s="80" t="n"/>
       <c r="AC35" s="21">
         <f>IF(A35="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A35))</f>
         <v/>
@@ -21843,11 +23778,11 @@
         <f>IF(A35="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A35,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ35" s="78">
+      <c r="AJ35" s="79">
         <f>IF(A35="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
-      <c r="AK35" s="78">
+      <c r="AK35" s="79">
         <f>IF(A35="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A35))</f>
         <v/>
       </c>
@@ -21924,7 +23859,7 @@
         <v/>
       </c>
       <c r="P36" s="46" t="n"/>
-      <c r="Q36" s="78">
+      <c r="Q36" s="79">
         <f>IF(A36="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
@@ -21932,7 +23867,7 @@
         <f>IF(A36="","",Q36*10)</f>
         <v/>
       </c>
-      <c r="S36" s="78">
+      <c r="S36" s="79">
         <f>IF(A36="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
@@ -21940,7 +23875,7 @@
         <f>IF(A36="","",S36*20)</f>
         <v/>
       </c>
-      <c r="U36" s="78">
+      <c r="U36" s="79">
         <f>IF(A36="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A36)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
@@ -21959,7 +23894,7 @@
         <f>IF(A36="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB36" s="79" t="n"/>
+      <c r="AB36" s="80" t="n"/>
       <c r="AC36" s="21">
         <f>IF(A36="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A36))</f>
         <v/>
@@ -21988,11 +23923,11 @@
         <f>IF(A36="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A36,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ36" s="78">
+      <c r="AJ36" s="79">
         <f>IF(A36="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
-      <c r="AK36" s="78">
+      <c r="AK36" s="79">
         <f>IF(A36="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A36))</f>
         <v/>
       </c>
@@ -22069,7 +24004,7 @@
         <v/>
       </c>
       <c r="P37" s="46" t="n"/>
-      <c r="Q37" s="78">
+      <c r="Q37" s="79">
         <f>IF(A37="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
@@ -22077,7 +24012,7 @@
         <f>IF(A37="","",Q37*10)</f>
         <v/>
       </c>
-      <c r="S37" s="78">
+      <c r="S37" s="79">
         <f>IF(A37="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
@@ -22085,7 +24020,7 @@
         <f>IF(A37="","",S37*20)</f>
         <v/>
       </c>
-      <c r="U37" s="78">
+      <c r="U37" s="79">
         <f>IF(A37="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A37)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
@@ -22104,7 +24039,7 @@
         <f>IF(A37="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB37" s="79" t="n"/>
+      <c r="AB37" s="80" t="n"/>
       <c r="AC37" s="21">
         <f>IF(A37="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A37))</f>
         <v/>
@@ -22133,11 +24068,11 @@
         <f>IF(A37="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A37,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ37" s="78">
+      <c r="AJ37" s="79">
         <f>IF(A37="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
-      <c r="AK37" s="78">
+      <c r="AK37" s="79">
         <f>IF(A37="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A37))</f>
         <v/>
       </c>
@@ -22214,7 +24149,7 @@
         <v/>
       </c>
       <c r="P38" s="46" t="n"/>
-      <c r="Q38" s="78">
+      <c r="Q38" s="79">
         <f>IF(A38="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
@@ -22222,7 +24157,7 @@
         <f>IF(A38="","",Q38*10)</f>
         <v/>
       </c>
-      <c r="S38" s="78">
+      <c r="S38" s="79">
         <f>IF(A38="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
@@ -22230,7 +24165,7 @@
         <f>IF(A38="","",S38*20)</f>
         <v/>
       </c>
-      <c r="U38" s="78">
+      <c r="U38" s="79">
         <f>IF(A38="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A38)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
@@ -22249,7 +24184,7 @@
         <f>IF(A38="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB38" s="79" t="n"/>
+      <c r="AB38" s="80" t="n"/>
       <c r="AC38" s="21">
         <f>IF(A38="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A38))</f>
         <v/>
@@ -22278,11 +24213,11 @@
         <f>IF(A38="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A38,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ38" s="78">
+      <c r="AJ38" s="79">
         <f>IF(A38="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
-      <c r="AK38" s="78">
+      <c r="AK38" s="79">
         <f>IF(A38="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A38))</f>
         <v/>
       </c>
@@ -22359,7 +24294,7 @@
         <v/>
       </c>
       <c r="P39" s="46" t="n"/>
-      <c r="Q39" s="78">
+      <c r="Q39" s="79">
         <f>IF(A39="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
@@ -22367,7 +24302,7 @@
         <f>IF(A39="","",Q39*10)</f>
         <v/>
       </c>
-      <c r="S39" s="78">
+      <c r="S39" s="79">
         <f>IF(A39="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
@@ -22375,7 +24310,7 @@
         <f>IF(A39="","",S39*20)</f>
         <v/>
       </c>
-      <c r="U39" s="78">
+      <c r="U39" s="79">
         <f>IF(A39="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A39)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
@@ -22394,7 +24329,7 @@
         <f>IF(A39="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB39" s="79" t="n"/>
+      <c r="AB39" s="80" t="n"/>
       <c r="AC39" s="21">
         <f>IF(A39="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A39))</f>
         <v/>
@@ -22423,11 +24358,11 @@
         <f>IF(A39="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A39,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ39" s="78">
+      <c r="AJ39" s="79">
         <f>IF(A39="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
-      <c r="AK39" s="78">
+      <c r="AK39" s="79">
         <f>IF(A39="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A39))</f>
         <v/>
       </c>
@@ -22504,7 +24439,7 @@
         <v/>
       </c>
       <c r="P40" s="46" t="n"/>
-      <c r="Q40" s="78">
+      <c r="Q40" s="79">
         <f>IF(A40="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
@@ -22512,7 +24447,7 @@
         <f>IF(A40="","",Q40*10)</f>
         <v/>
       </c>
-      <c r="S40" s="78">
+      <c r="S40" s="79">
         <f>IF(A40="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
@@ -22520,7 +24455,7 @@
         <f>IF(A40="","",S40*20)</f>
         <v/>
       </c>
-      <c r="U40" s="78">
+      <c r="U40" s="79">
         <f>IF(A40="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A40)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
@@ -22539,7 +24474,7 @@
         <f>IF(A40="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB40" s="79" t="n"/>
+      <c r="AB40" s="80" t="n"/>
       <c r="AC40" s="21">
         <f>IF(A40="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A40))</f>
         <v/>
@@ -22568,11 +24503,11 @@
         <f>IF(A40="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A40,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ40" s="78">
+      <c r="AJ40" s="79">
         <f>IF(A40="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
-      <c r="AK40" s="78">
+      <c r="AK40" s="79">
         <f>IF(A40="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A40))</f>
         <v/>
       </c>
@@ -22649,7 +24584,7 @@
         <v/>
       </c>
       <c r="P41" s="46" t="n"/>
-      <c r="Q41" s="78">
+      <c r="Q41" s="79">
         <f>IF(A41="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
@@ -22657,7 +24592,7 @@
         <f>IF(A41="","",Q41*10)</f>
         <v/>
       </c>
-      <c r="S41" s="78">
+      <c r="S41" s="79">
         <f>IF(A41="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
@@ -22665,7 +24600,7 @@
         <f>IF(A41="","",S41*20)</f>
         <v/>
       </c>
-      <c r="U41" s="78">
+      <c r="U41" s="79">
         <f>IF(A41="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A41)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
@@ -22684,7 +24619,7 @@
         <f>IF(A41="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB41" s="79" t="n"/>
+      <c r="AB41" s="80" t="n"/>
       <c r="AC41" s="21">
         <f>IF(A41="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A41))</f>
         <v/>
@@ -22713,11 +24648,11 @@
         <f>IF(A41="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A41,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ41" s="78">
+      <c r="AJ41" s="79">
         <f>IF(A41="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
-      <c r="AK41" s="78">
+      <c r="AK41" s="79">
         <f>IF(A41="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A41))</f>
         <v/>
       </c>
@@ -22794,7 +24729,7 @@
         <v/>
       </c>
       <c r="P42" s="46" t="n"/>
-      <c r="Q42" s="78">
+      <c r="Q42" s="79">
         <f>IF(A42="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
@@ -22802,7 +24737,7 @@
         <f>IF(A42="","",Q42*10)</f>
         <v/>
       </c>
-      <c r="S42" s="78">
+      <c r="S42" s="79">
         <f>IF(A42="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
@@ -22810,7 +24745,7 @@
         <f>IF(A42="","",S42*20)</f>
         <v/>
       </c>
-      <c r="U42" s="78">
+      <c r="U42" s="79">
         <f>IF(A42="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A42)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
@@ -22829,7 +24764,7 @@
         <f>IF(A42="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB42" s="79" t="n"/>
+      <c r="AB42" s="80" t="n"/>
       <c r="AC42" s="21">
         <f>IF(A42="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A42))</f>
         <v/>
@@ -22858,11 +24793,11 @@
         <f>IF(A42="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A42,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ42" s="78">
+      <c r="AJ42" s="79">
         <f>IF(A42="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
-      <c r="AK42" s="78">
+      <c r="AK42" s="79">
         <f>IF(A42="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A42))</f>
         <v/>
       </c>
@@ -22939,7 +24874,7 @@
         <v/>
       </c>
       <c r="P43" s="46" t="n"/>
-      <c r="Q43" s="78">
+      <c r="Q43" s="79">
         <f>IF(A43="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
@@ -22947,7 +24882,7 @@
         <f>IF(A43="","",Q43*10)</f>
         <v/>
       </c>
-      <c r="S43" s="78">
+      <c r="S43" s="79">
         <f>IF(A43="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
@@ -22955,7 +24890,7 @@
         <f>IF(A43="","",S43*20)</f>
         <v/>
       </c>
-      <c r="U43" s="78">
+      <c r="U43" s="79">
         <f>IF(A43="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A43)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
@@ -22974,7 +24909,7 @@
         <f>IF(A43="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB43" s="79" t="n"/>
+      <c r="AB43" s="80" t="n"/>
       <c r="AC43" s="21">
         <f>IF(A43="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A43))</f>
         <v/>
@@ -23003,11 +24938,11 @@
         <f>IF(A43="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A43,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ43" s="78">
+      <c r="AJ43" s="79">
         <f>IF(A43="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
-      <c r="AK43" s="78">
+      <c r="AK43" s="79">
         <f>IF(A43="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A43))</f>
         <v/>
       </c>
@@ -23084,7 +25019,7 @@
         <v/>
       </c>
       <c r="P44" s="46" t="n"/>
-      <c r="Q44" s="78">
+      <c r="Q44" s="79">
         <f>IF(A44="","",SUMIFS('BMP'!$AD$4:$AD$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
@@ -23092,7 +25027,7 @@
         <f>IF(A44="","",Q44*10)</f>
         <v/>
       </c>
-      <c r="S44" s="78">
+      <c r="S44" s="79">
         <f>IF(A44="","",SUMIFS('BMP'!$AE$4:$AE$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
@@ -23100,7 +25035,7 @@
         <f>IF(A44="","",S44*20)</f>
         <v/>
       </c>
-      <c r="U44" s="78">
+      <c r="U44" s="79">
         <f>IF(A44="","",SUMIFS('BMP'!$AF$4:$AF$53,'BMP'!$B$4:$B$53,A44)+SUMIFS('BMP'!$AG$4:$AG$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
@@ -23119,7 +25054,7 @@
         <f>IF(A44="","",SUMIFS('BMP'!$F$4:$F$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Permeable Pavement"))</f>
         <v/>
       </c>
-      <c r="AB44" s="79" t="n"/>
+      <c r="AB44" s="80" t="n"/>
       <c r="AC44" s="21">
         <f>IF(A44="","",SUMIFS('CDA'!$G$4:$G$53,'CDA'!$B$4:$B$53,A44))</f>
         <v/>
@@ -23148,11 +25083,11 @@
         <f>IF(A44="","",SUMIFS('BMP'!$AA$4:$AA$53,'BMP'!$B$4:$B$53,A44,'BMP'!$D$4:$D$53,"Wet Swale"))</f>
         <v/>
       </c>
-      <c r="AJ44" s="78">
+      <c r="AJ44" s="79">
         <f>IF(A44="","",SUMIFS('BMP'!$AB$4:$AB$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
-      <c r="AK44" s="78">
+      <c r="AK44" s="79">
         <f>IF(A44="","",SUMIFS('BMP'!$AC$4:$AC$53,'BMP'!$B$4:$B$53,A44))</f>
         <v/>
       </c>
@@ -23176,53 +25111,53 @@
     <row r="45" ht="16.25" customHeight="1">
       <c r="B45" s="22" t="n"/>
       <c r="C45" s="22" t="n"/>
-      <c r="D45" s="80" t="inlineStr">
+      <c r="D45" s="81" t="inlineStr">
         <is>
           <t>DATOTAL</t>
         </is>
       </c>
-      <c r="E45" s="70">
+      <c r="E45" s="71">
         <f>SUM(E12:E44)</f>
         <v/>
       </c>
       <c r="F45" s="22" t="n"/>
       <c r="G45" s="22" t="n"/>
       <c r="H45" s="22" t="n"/>
-      <c r="I45" s="70">
+      <c r="I45" s="71">
         <f>SUM(I12:I44)</f>
         <v/>
       </c>
-      <c r="J45" s="70">
+      <c r="J45" s="71">
         <f>SUM(J12:J44)</f>
         <v/>
       </c>
-      <c r="K45" s="81">
+      <c r="K45" s="82">
         <f>SUM(K12:K44)</f>
         <v/>
       </c>
       <c r="O45" s="23" t="n"/>
-      <c r="P45" s="60" t="n"/>
-      <c r="Q45" s="73">
+      <c r="P45" s="61" t="n"/>
+      <c r="Q45" s="74">
         <f>SUM(Q12:Q44)</f>
         <v/>
       </c>
-      <c r="R45" s="70">
+      <c r="R45" s="71">
         <f>SUM(R12:R44)</f>
         <v/>
       </c>
-      <c r="S45" s="73">
+      <c r="S45" s="74">
         <f>SUM(S12:S44)</f>
         <v/>
       </c>
-      <c r="T45" s="70">
+      <c r="T45" s="71">
         <f>SUM(T12:T44)</f>
         <v/>
       </c>
-      <c r="U45" s="73">
+      <c r="U45" s="74">
         <f>SUM(U12:U44)</f>
         <v/>
       </c>
-      <c r="V45" s="81">
+      <c r="V45" s="82">
         <f>SUM(V12:V44)</f>
         <v/>
       </c>
@@ -23231,7 +25166,7 @@
       <c r="Y45" s="22" t="n"/>
       <c r="Z45" s="22" t="n"/>
       <c r="AA45" s="22" t="n"/>
-      <c r="AB45" s="62" t="n"/>
+      <c r="AB45" s="63" t="n"/>
       <c r="AC45" s="22" t="n"/>
       <c r="AD45" s="22" t="n"/>
       <c r="AE45" s="22" t="n"/>
@@ -23241,11 +25176,11 @@
       <c r="AI45" s="22" t="n"/>
       <c r="AJ45" s="51" t="n"/>
       <c r="AK45" s="51" t="n"/>
-      <c r="AL45" s="70">
+      <c r="AL45" s="71">
         <f>SUM(AL12:AL44)</f>
         <v/>
       </c>
-      <c r="AM45" s="81">
+      <c r="AM45" s="82">
         <f>SUM(AM12:AM44)</f>
         <v/>
       </c>
@@ -23319,30 +25254,30 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>EISA Section 438 — Direct Determination (Horton infiltration)</t>
         </is>
       </c>
-      <c r="B1" s="83" t="n"/>
-      <c r="C1" s="83" t="n"/>
-      <c r="D1" s="83" t="n"/>
-      <c r="E1" s="83" t="n"/>
-      <c r="F1" s="83" t="n"/>
-      <c r="G1" s="84" t="n"/>
+      <c r="B1" s="84" t="n"/>
+      <c r="C1" s="84" t="n"/>
+      <c r="D1" s="84" t="n"/>
+      <c r="E1" s="84" t="n"/>
+      <c r="F1" s="84" t="n"/>
+      <c r="G1" s="85" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>Project References</t>
         </is>
       </c>
-      <c r="B3" s="86" t="n"/>
-      <c r="C3" s="86" t="n"/>
-      <c r="D3" s="86" t="n"/>
-      <c r="E3" s="86" t="n"/>
-      <c r="F3" s="86" t="n"/>
-      <c r="G3" s="87" t="n"/>
+      <c r="B3" s="87" t="n"/>
+      <c r="C3" s="87" t="n"/>
+      <c r="D3" s="87" t="n"/>
+      <c r="E3" s="87" t="n"/>
+      <c r="F3" s="87" t="n"/>
+      <c r="G3" s="88" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -23401,17 +25336,17 @@
       <c r="G7" s="22" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>Horton Parameters (from PARAMS)</t>
         </is>
       </c>
-      <c r="B8" s="88" t="n"/>
-      <c r="C8" s="88" t="n"/>
-      <c r="D8" s="89" t="n"/>
-      <c r="E8" s="89" t="n"/>
-      <c r="F8" s="88" t="n"/>
-      <c r="G8" s="90" t="n"/>
+      <c r="B8" s="89" t="n"/>
+      <c r="C8" s="89" t="n"/>
+      <c r="D8" s="90" t="n"/>
+      <c r="E8" s="90" t="n"/>
+      <c r="F8" s="89" t="n"/>
+      <c r="G8" s="91" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -23522,45 +25457,45 @@
           <t>Pre-Construction Runoff (from SDA pre totals)</t>
         </is>
       </c>
-      <c r="B15" s="91" t="n"/>
-      <c r="C15" s="91" t="n"/>
-      <c r="D15" s="92" t="n"/>
-      <c r="E15" s="92" t="n"/>
-      <c r="F15" s="91" t="n"/>
-      <c r="G15" s="93" t="n"/>
+      <c r="B15" s="92" t="n"/>
+      <c r="C15" s="92" t="n"/>
+      <c r="D15" s="93" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="92" t="n"/>
+      <c r="G15" s="94" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="76" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="95" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="95" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D16" s="95" t="inlineStr">
+      <c r="D16" s="96" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E16" s="95" t="inlineStr">
+      <c r="E16" s="96" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F16" s="94" t="inlineStr">
+      <c r="F16" s="95" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G16" s="94" t="inlineStr">
+      <c r="G16" s="95" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -23572,7 +25507,7 @@
           <t>Impervious Vehicular</t>
         </is>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -23604,7 +25539,7 @@
           <t>Impervious Non-Vehicular</t>
         </is>
       </c>
-      <c r="B18" s="96" t="inlineStr">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -23636,7 +25571,7 @@
           <t>BMP</t>
         </is>
       </c>
-      <c r="B19" s="96" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -23668,7 +25603,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B20" s="96" t="inlineStr">
+      <c r="B20" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23700,7 +25635,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B21" s="96" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -23732,7 +25667,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
+      <c r="B22" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -23764,7 +25699,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B23" s="96" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -23796,7 +25731,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B24" s="96" t="inlineStr">
+      <c r="B24" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23828,7 +25763,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B25" s="96" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -23860,7 +25795,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B26" s="96" t="inlineStr">
+      <c r="B26" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -23892,7 +25827,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B27" s="96" t="inlineStr">
+      <c r="B27" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -23924,10 +25859,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="91" t="n"/>
-      <c r="C28" s="91" t="n"/>
-      <c r="D28" s="92" t="n"/>
-      <c r="E28" s="97" t="n"/>
+      <c r="B28" s="92" t="n"/>
+      <c r="C28" s="92" t="n"/>
+      <c r="D28" s="93" t="n"/>
+      <c r="E28" s="98" t="n"/>
       <c r="F28" s="21">
         <f>SUM(F17:F27)</f>
         <v/>
@@ -23951,45 +25886,45 @@
           <t>Post-Construction Runoff (from SDA post totals)</t>
         </is>
       </c>
-      <c r="B30" s="91" t="n"/>
-      <c r="C30" s="91" t="n"/>
-      <c r="D30" s="92" t="n"/>
-      <c r="E30" s="92" t="n"/>
-      <c r="F30" s="91" t="n"/>
-      <c r="G30" s="93" t="n"/>
+      <c r="B30" s="92" t="n"/>
+      <c r="C30" s="92" t="n"/>
+      <c r="D30" s="93" t="n"/>
+      <c r="E30" s="93" t="n"/>
+      <c r="F30" s="92" t="n"/>
+      <c r="G30" s="94" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="76" t="inlineStr">
+      <c r="A31" s="77" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B31" s="94" t="inlineStr">
+      <c r="B31" s="95" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C31" s="94" t="inlineStr">
+      <c r="C31" s="95" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="D31" s="95" t="inlineStr">
+      <c r="D31" s="96" t="inlineStr">
         <is>
           <t>Runoff HSG B (in)</t>
         </is>
       </c>
-      <c r="E31" s="95" t="inlineStr">
+      <c r="E31" s="96" t="inlineStr">
         <is>
           <t>Runoff HSG C (in)</t>
         </is>
       </c>
-      <c r="F31" s="94" t="inlineStr">
+      <c r="F31" s="95" t="inlineStr">
         <is>
           <t>Vol HSG B (CF)</t>
         </is>
       </c>
-      <c r="G31" s="94" t="inlineStr">
+      <c r="G31" s="95" t="inlineStr">
         <is>
           <t>Vol HSG C (CF)</t>
         </is>
@@ -24001,7 +25936,7 @@
           <t>Impervious Vehicular</t>
         </is>
       </c>
-      <c r="B32" s="96" t="inlineStr">
+      <c r="B32" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24033,7 +25968,7 @@
           <t>Impervious Non-Vehicular</t>
         </is>
       </c>
-      <c r="B33" s="96" t="inlineStr">
+      <c r="B33" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24065,7 +26000,7 @@
           <t>BMP</t>
         </is>
       </c>
-      <c r="B34" s="96" t="inlineStr">
+      <c r="B34" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24097,7 +26032,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B35" s="96" t="inlineStr">
+      <c r="B35" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24129,7 +26064,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B36" s="96" t="inlineStr">
+      <c r="B36" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -24161,7 +26096,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B37" s="96" t="inlineStr">
+      <c r="B37" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -24193,7 +26128,7 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B38" s="96" t="inlineStr">
+      <c r="B38" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -24225,7 +26160,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B39" s="96" t="inlineStr">
+      <c r="B39" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24257,7 +26192,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B40" s="96" t="inlineStr">
+      <c r="B40" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -24289,7 +26224,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B41" s="96" t="inlineStr">
+      <c r="B41" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -24321,7 +26256,7 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B42" s="96" t="inlineStr">
+      <c r="B42" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -24353,10 +26288,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="91" t="n"/>
-      <c r="C43" s="91" t="n"/>
-      <c r="D43" s="92" t="n"/>
-      <c r="E43" s="97" t="n"/>
+      <c r="B43" s="92" t="n"/>
+      <c r="C43" s="92" t="n"/>
+      <c r="D43" s="93" t="n"/>
+      <c r="E43" s="98" t="n"/>
       <c r="F43" s="21">
         <f>SUM(F32:F42)</f>
         <v/>
@@ -24375,30 +26310,30 @@
       <c r="G44" s="22" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="82" t="inlineStr">
+      <c r="A45" s="83" t="inlineStr">
         <is>
           <t>Compliance Check</t>
         </is>
       </c>
-      <c r="B45" s="98" t="n"/>
-      <c r="C45" s="99" t="n"/>
+      <c r="B45" s="99" t="n"/>
+      <c r="C45" s="100" t="n"/>
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="23" t="n"/>
       <c r="F45" s="22" t="n"/>
       <c r="G45" s="22" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="100" t="inlineStr">
+      <c r="A46" s="101" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B46" s="101" t="inlineStr">
+      <c r="B46" s="102" t="inlineStr">
         <is>
           <t>HSG B</t>
         </is>
       </c>
-      <c r="C46" s="101" t="inlineStr">
+      <c r="C46" s="102" t="inlineStr">
         <is>
           <t>HSG C</t>
         </is>
@@ -24536,28 +26471,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>EISA Section 438 — TR-55 CN Method (Method A primary)</t>
         </is>
       </c>
-      <c r="B1" s="83" t="n"/>
-      <c r="C1" s="83" t="n"/>
-      <c r="D1" s="83" t="n"/>
-      <c r="E1" s="83" t="n"/>
-      <c r="F1" s="84" t="n"/>
+      <c r="B1" s="84" t="n"/>
+      <c r="C1" s="84" t="n"/>
+      <c r="D1" s="84" t="n"/>
+      <c r="E1" s="84" t="n"/>
+      <c r="F1" s="85" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>Project References</t>
         </is>
       </c>
-      <c r="B3" s="86" t="n"/>
-      <c r="C3" s="86" t="n"/>
-      <c r="D3" s="86" t="n"/>
-      <c r="E3" s="86" t="n"/>
-      <c r="F3" s="87" t="n"/>
+      <c r="B3" s="87" t="n"/>
+      <c r="C3" s="87" t="n"/>
+      <c r="D3" s="87" t="n"/>
+      <c r="E3" s="87" t="n"/>
+      <c r="F3" s="88" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -24612,44 +26547,44 @@
       <c r="F7" s="22" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>Pre-Construction Runoff (Method A)</t>
         </is>
       </c>
-      <c r="B8" s="88" t="n"/>
-      <c r="C8" s="102" t="n"/>
-      <c r="D8" s="88" t="n"/>
-      <c r="E8" s="89" t="n"/>
-      <c r="F8" s="90" t="n"/>
+      <c r="B8" s="89" t="n"/>
+      <c r="C8" s="103" t="n"/>
+      <c r="D8" s="89" t="n"/>
+      <c r="E8" s="90" t="n"/>
+      <c r="F8" s="91" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="100" t="inlineStr">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B9" s="101" t="inlineStr">
+      <c r="B9" s="102" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C9" s="103" t="inlineStr">
+      <c r="C9" s="104" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D9" s="101" t="inlineStr">
+      <c r="D9" s="102" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E9" s="104" t="inlineStr">
+      <c r="E9" s="105" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F9" s="101" t="inlineStr">
+      <c r="F9" s="102" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -24661,12 +26596,12 @@
           <t>Impervious Vehicular</t>
         </is>
       </c>
-      <c r="B10" s="96" t="inlineStr">
+      <c r="B10" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C10" s="105" t="n">
+      <c r="C10" s="106" t="n">
         <v>98</v>
       </c>
       <c r="D10" s="21">
@@ -24688,12 +26623,12 @@
           <t>Impervious Non-Vehicular</t>
         </is>
       </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C11" s="105" t="n">
+      <c r="C11" s="106" t="n">
         <v>98</v>
       </c>
       <c r="D11" s="21">
@@ -24715,12 +26650,12 @@
           <t>BMP</t>
         </is>
       </c>
-      <c r="B12" s="96" t="inlineStr">
+      <c r="B12" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="79">
         <f>INDEX(PARAMS_CN,2,2)</f>
         <v/>
       </c>
@@ -24743,12 +26678,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="79">
         <f>INDEX(PARAMS_CN,3,2)</f>
         <v/>
       </c>
@@ -24771,12 +26706,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B14" s="96" t="inlineStr">
+      <c r="B14" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C14" s="78">
+      <c r="C14" s="79">
         <f>INDEX(PARAMS_CN,3,3)</f>
         <v/>
       </c>
@@ -24799,12 +26734,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B15" s="96" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C15" s="78">
+      <c r="C15" s="79">
         <f>INDEX(PARAMS_CN,3,4)</f>
         <v/>
       </c>
@@ -24827,12 +26762,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B16" s="96" t="inlineStr">
+      <c r="B16" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C16" s="78">
+      <c r="C16" s="79">
         <f>INDEX(PARAMS_CN,3,5)</f>
         <v/>
       </c>
@@ -24855,12 +26790,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B17" s="96" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="79">
         <f>INDEX(PARAMS_CN,4,2)</f>
         <v/>
       </c>
@@ -24883,12 +26818,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B18" s="96" t="inlineStr">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C18" s="78">
+      <c r="C18" s="79">
         <f>INDEX(PARAMS_CN,4,3)</f>
         <v/>
       </c>
@@ -24911,12 +26846,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B19" s="96" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C19" s="78">
+      <c r="C19" s="79">
         <f>INDEX(PARAMS_CN,4,4)</f>
         <v/>
       </c>
@@ -24939,12 +26874,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B20" s="96" t="inlineStr">
+      <c r="B20" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C20" s="78">
+      <c r="C20" s="79">
         <f>INDEX(PARAMS_CN,4,5)</f>
         <v/>
       </c>
@@ -24962,15 +26897,15 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="85" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="88" t="n"/>
-      <c r="C21" s="102" t="n"/>
-      <c r="D21" s="88" t="n"/>
-      <c r="E21" s="106" t="n"/>
+      <c r="B21" s="89" t="n"/>
+      <c r="C21" s="103" t="n"/>
+      <c r="D21" s="89" t="n"/>
+      <c r="E21" s="107" t="n"/>
       <c r="F21" s="21">
         <f>SUM(F10:F20)</f>
         <v/>
@@ -24984,44 +26919,44 @@
       <c r="F22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="85" t="inlineStr">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>Post-Construction Runoff (Method A)</t>
         </is>
       </c>
-      <c r="B23" s="88" t="n"/>
-      <c r="C23" s="102" t="n"/>
-      <c r="D23" s="88" t="n"/>
-      <c r="E23" s="89" t="n"/>
-      <c r="F23" s="90" t="n"/>
+      <c r="B23" s="89" t="n"/>
+      <c r="C23" s="103" t="n"/>
+      <c r="D23" s="89" t="n"/>
+      <c r="E23" s="90" t="n"/>
+      <c r="F23" s="91" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="100" t="inlineStr">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B24" s="101" t="inlineStr">
+      <c r="B24" s="102" t="inlineStr">
         <is>
           <t>HSG</t>
         </is>
       </c>
-      <c r="C24" s="103" t="inlineStr">
+      <c r="C24" s="104" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="D24" s="101" t="inlineStr">
+      <c r="D24" s="102" t="inlineStr">
         <is>
           <t>Area (SF)</t>
         </is>
       </c>
-      <c r="E24" s="104" t="inlineStr">
+      <c r="E24" s="105" t="inlineStr">
         <is>
           <t>Q (in)</t>
         </is>
       </c>
-      <c r="F24" s="101" t="inlineStr">
+      <c r="F24" s="102" t="inlineStr">
         <is>
           <t>Vol (CF)</t>
         </is>
@@ -25033,12 +26968,12 @@
           <t>Impervious Vehicular</t>
         </is>
       </c>
-      <c r="B25" s="96" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C25" s="105" t="n">
+      <c r="C25" s="106" t="n">
         <v>98</v>
       </c>
       <c r="D25" s="21">
@@ -25060,12 +26995,12 @@
           <t>Impervious Non-Vehicular</t>
         </is>
       </c>
-      <c r="B26" s="96" t="inlineStr">
+      <c r="B26" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C26" s="105" t="n">
+      <c r="C26" s="106" t="n">
         <v>98</v>
       </c>
       <c r="D26" s="21">
@@ -25087,12 +27022,12 @@
           <t>BMP</t>
         </is>
       </c>
-      <c r="B27" s="96" t="inlineStr">
+      <c r="B27" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="78">
+      <c r="C27" s="79">
         <f>INDEX(PARAMS_CN,2,2)</f>
         <v/>
       </c>
@@ -25115,12 +27050,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B28" s="96" t="inlineStr">
+      <c r="B28" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C28" s="78">
+      <c r="C28" s="79">
         <f>INDEX(PARAMS_CN,3,2)</f>
         <v/>
       </c>
@@ -25143,12 +27078,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B29" s="96" t="inlineStr">
+      <c r="B29" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C29" s="78">
+      <c r="C29" s="79">
         <f>INDEX(PARAMS_CN,3,3)</f>
         <v/>
       </c>
@@ -25171,12 +27106,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B30" s="96" t="inlineStr">
+      <c r="B30" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C30" s="78">
+      <c r="C30" s="79">
         <f>INDEX(PARAMS_CN,3,4)</f>
         <v/>
       </c>
@@ -25199,12 +27134,12 @@
           <t>Natural (Woods)</t>
         </is>
       </c>
-      <c r="B31" s="96" t="inlineStr">
+      <c r="B31" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C31" s="78">
+      <c r="C31" s="79">
         <f>INDEX(PARAMS_CN,3,5)</f>
         <v/>
       </c>
@@ -25227,12 +27162,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B32" s="96" t="inlineStr">
+      <c r="B32" s="97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C32" s="78">
+      <c r="C32" s="79">
         <f>INDEX(PARAMS_CN,4,2)</f>
         <v/>
       </c>
@@ -25255,12 +27190,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B33" s="96" t="inlineStr">
+      <c r="B33" s="97" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C33" s="78">
+      <c r="C33" s="79">
         <f>INDEX(PARAMS_CN,4,3)</f>
         <v/>
       </c>
@@ -25283,12 +27218,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B34" s="96" t="inlineStr">
+      <c r="B34" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C34" s="78">
+      <c r="C34" s="79">
         <f>INDEX(PARAMS_CN,4,4)</f>
         <v/>
       </c>
@@ -25311,12 +27246,12 @@
           <t>Compacted (Open Space)</t>
         </is>
       </c>
-      <c r="B35" s="96" t="inlineStr">
+      <c r="B35" s="97" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C35" s="78">
+      <c r="C35" s="79">
         <f>INDEX(PARAMS_CN,4,5)</f>
         <v/>
       </c>
@@ -25334,15 +27269,15 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="85" t="inlineStr">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="88" t="n"/>
-      <c r="C36" s="102" t="n"/>
-      <c r="D36" s="88" t="n"/>
-      <c r="E36" s="106" t="n"/>
+      <c r="B36" s="89" t="n"/>
+      <c r="C36" s="103" t="n"/>
+      <c r="D36" s="89" t="n"/>
+      <c r="E36" s="107" t="n"/>
       <c r="F36" s="21">
         <f>SUM(F25:F35)</f>
         <v/>
@@ -25356,12 +27291,12 @@
       <c r="F37" s="22" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="82" t="inlineStr">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>Compliance Check (Method A)</t>
         </is>
       </c>
-      <c r="B38" s="99" t="n"/>
+      <c r="B38" s="100" t="n"/>
       <c r="C38" s="51" t="n"/>
       <c r="D38" s="22" t="n"/>
       <c r="E38" s="23" t="n"/>
